--- a/docs/LA-Q_SF-ICPMS_TAPP_v2.xlsx
+++ b/docs/LA-Q_SF-ICPMS_TAPP_v2.xlsx
@@ -531,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y108"/>
+  <dimension ref="A1:AB108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -617,12 +617,27 @@
           <t>Mapping</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>schema path</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>matchComment</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>implementation notes</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Literature Assessment</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>Zhang et al. 2022
 (GCA 323)
@@ -632,7 +647,7 @@
 Florida State University</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>Chernonozhkin et al. 2021
 (Chem Geol 562)
@@ -642,7 +657,7 @@
 Ghent University</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>Chernonozhkin et al. 2021
 (Chem Geol 562)
@@ -654,7 +669,7 @@
 Ghent University</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>Chernonozhkin et al. 2021
 (Chem Geol 562)
@@ -664,7 +679,7 @@
 Ghent University</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>Mittlefehldt 2024
 Appendix A
@@ -674,7 +689,7 @@
 Johnson Space Center</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="U1" s="4" t="inlineStr">
         <is>
           <t>Nakanishi et al. 2022
 (GCA 319)
@@ -684,7 +699,7 @@
 Tokyo Institute of Technology</t>
         </is>
       </c>
-      <c r="S1" s="4" t="inlineStr">
+      <c r="V1" s="4" t="inlineStr">
         <is>
           <t>Navarro et al. 2024
 (ACS ESC 8)
@@ -694,7 +709,7 @@
 University of Campinas</t>
         </is>
       </c>
-      <c r="T1" s="4" t="inlineStr">
+      <c r="W1" s="4" t="inlineStr">
         <is>
           <t>Navarro et al. 2024
 (ACS ESC 8)
@@ -704,7 +719,7 @@
 University of Campinas</t>
         </is>
       </c>
-      <c r="U1" s="4" t="inlineStr">
+      <c r="X1" s="4" t="inlineStr">
         <is>
           <t>Liu et al. 2024
 (JAAS 39)
@@ -715,7 +730,7 @@
 Chinese Academy of Sciences</t>
         </is>
       </c>
-      <c r="V1" s="4" t="inlineStr">
+      <c r="Y1" s="4" t="inlineStr">
         <is>
           <t>Liu et al. 2025
 (GCA 393)
@@ -725,7 +740,7 @@
 Guangzhou Inst. Geochemistry</t>
         </is>
       </c>
-      <c r="W1" s="4" t="inlineStr">
+      <c r="Z1" s="4" t="inlineStr">
         <is>
           <t>Liu et al. 2025
 (GCA 393)
@@ -735,7 +750,7 @@
 Guangzhou Inst. Geochemistry</t>
         </is>
       </c>
-      <c r="X1" s="4" t="inlineStr">
+      <c r="AA1" s="4" t="inlineStr">
         <is>
           <t>Liu et al. 2016
 (M&amp;PS 51)
@@ -746,7 +761,7 @@
 Virginia Tech</t>
         </is>
       </c>
-      <c r="Y1" s="4" t="inlineStr">
+      <c r="AB1" s="4" t="inlineStr">
         <is>
           <t>Liu et al. 2016
 (M&amp;PS 51)
@@ -774,9 +789,6 @@
       <c r="I2" s="5" t="n"/>
       <c r="J2" s="5" t="n"/>
       <c r="K2" s="5" t="n"/>
-      <c r="L2" s="5" t="n"/>
-      <c r="M2" s="5" t="n"/>
-      <c r="N2" s="5" t="n"/>
       <c r="O2" s="5" t="n"/>
       <c r="P2" s="5" t="n"/>
       <c r="Q2" s="5" t="n"/>
@@ -786,12 +798,15 @@
       <c r="U2" s="5" t="n"/>
       <c r="V2" s="5" t="n"/>
       <c r="W2" s="5" t="n"/>
-      <c r="X2" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Y2" s="5" t="inlineStr">
+      <c r="X2" s="5" t="n"/>
+      <c r="Y2" s="5" t="n"/>
+      <c r="Z2" s="5" t="n"/>
+      <c r="AA2" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB2" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -845,68 +860,78 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L3" s="9" t="n"/>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:name</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>match. methodDefinition.schema:name is the short descriptive name for the method.</t>
+        </is>
+      </c>
+      <c r="O3" s="9" t="n"/>
+      <c r="P3" s="1" t="inlineStr">
         <is>
           <t>Zhang et al. (2022) Iron Meteorite LA-ICP-MS v1</t>
         </is>
       </c>
-      <c r="N3" s="1" t="inlineStr">
+      <c r="Q3" s="1" t="inlineStr">
         <is>
           <t>Chernonozhkin et al. (2021) Pallasite Olivine 2D Mapping v1</t>
         </is>
       </c>
-      <c r="O3" s="1" t="inlineStr">
+      <c r="R3" s="1" t="inlineStr">
         <is>
           <t>Chernonozhkin et al. (2021) Pallasite Olivine Multi-run Spot/Transect v1</t>
         </is>
       </c>
-      <c r="P3" s="1" t="inlineStr">
+      <c r="S3" s="1" t="inlineStr">
         <is>
           <t>Chernonozhkin et al. (2021) Pallasite Phosphate Spot v1</t>
         </is>
       </c>
-      <c r="Q3" s="1" t="inlineStr">
+      <c r="T3" s="1" t="inlineStr">
         <is>
           <t>Mittlefehldt (2024) Pallasite Olivine Spot v1</t>
         </is>
       </c>
-      <c r="R3" s="1" t="inlineStr">
+      <c r="U3" s="1" t="inlineStr">
         <is>
           <t>Nakanishi et al. (2022) CR Chondrite Metal HSE fs-LA-ICP-MS Spot v1</t>
         </is>
       </c>
-      <c r="S3" s="1" t="inlineStr">
+      <c r="V3" s="1" t="inlineStr">
         <is>
           <t>Navarro et al. (2024) Iron Meteorite Spot v1</t>
         </is>
       </c>
-      <c r="T3" s="1" t="inlineStr">
+      <c r="W3" s="1" t="inlineStr">
         <is>
           <t>Navarro et al. (2024) Iron Meteorite Raster Mapping v1</t>
         </is>
       </c>
-      <c r="U3" s="1" t="inlineStr">
+      <c r="X3" s="1" t="inlineStr">
         <is>
           <t>Liu et al. (2024) Extraterrestrial Flux Glass fs-LA-ICP-MS Spot v1</t>
         </is>
       </c>
-      <c r="V3" s="1" t="inlineStr">
+      <c r="Y3" s="1" t="inlineStr">
         <is>
           <t>Liu et al. (2025) Experimental Silicate Glass LA-ICP-MS Spot v1</t>
         </is>
       </c>
-      <c r="W3" s="1" t="inlineStr">
+      <c r="Z3" s="1" t="inlineStr">
         <is>
           <t>Liu et al. (2025) Experimental Sulfide LA-ICP-MS Spot v1</t>
         </is>
       </c>
-      <c r="X3" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Y3" s="1" t="inlineStr">
+      <c r="AA3" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB3" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -960,68 +985,84 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L4" s="9" t="n"/>
-      <c r="M4" s="1" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:measurementTechnique.schema:DefinedTerm.schema:name</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>match. methodDefinition.schema:measurementTechnique is a DefinedTerm; use .schema:termCode for the controlled-list code</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>schema:DefinedTerm.schema:termCode
+datatype: enum {LA-ICP-MS | LA-ICP-OES | LA-MC-ICP-MS | LA-ICP-ToF-MS | LA-ICP-MS/MS | Other: specify}</t>
+        </is>
+      </c>
+      <c r="O4" s="9" t="n"/>
+      <c r="P4" s="1" t="inlineStr">
         <is>
           <t>LA-SF-ICP-MS</t>
         </is>
       </c>
-      <c r="N4" s="1" t="inlineStr">
+      <c r="Q4" s="1" t="inlineStr">
         <is>
           <t>LA-SF-ICP-MS</t>
         </is>
       </c>
-      <c r="O4" s="1" t="inlineStr">
+      <c r="R4" s="1" t="inlineStr">
         <is>
           <t>LA-SF-ICP-MS</t>
         </is>
       </c>
-      <c r="P4" s="1" t="inlineStr">
+      <c r="S4" s="1" t="inlineStr">
         <is>
           <t>LA-SF-ICP-MS</t>
         </is>
       </c>
-      <c r="Q4" s="1" t="inlineStr">
+      <c r="T4" s="1" t="inlineStr">
         <is>
           <t>LA-SF-ICP-MS</t>
         </is>
       </c>
-      <c r="R4" s="1" t="inlineStr">
+      <c r="U4" s="1" t="inlineStr">
         <is>
           <t>fs-LA-Q-ICP-MS</t>
         </is>
       </c>
-      <c r="S4" s="1" t="inlineStr">
+      <c r="V4" s="1" t="inlineStr">
         <is>
           <t>LA-SF-ICP-MS</t>
         </is>
       </c>
-      <c r="T4" s="1" t="inlineStr">
+      <c r="W4" s="1" t="inlineStr">
         <is>
           <t>LA-SF-ICP-MS</t>
         </is>
       </c>
-      <c r="U4" s="1" t="inlineStr">
+      <c r="X4" s="1" t="inlineStr">
         <is>
           <t>fs-LA-Q-ICP-MS</t>
         </is>
       </c>
-      <c r="V4" s="1" t="inlineStr">
+      <c r="Y4" s="1" t="inlineStr">
         <is>
           <t>LA-Q-ICP-MS</t>
         </is>
       </c>
-      <c r="W4" s="1" t="inlineStr">
+      <c r="Z4" s="1" t="inlineStr">
         <is>
           <t>LA-Q-ICP-MS</t>
         </is>
       </c>
-      <c r="X4" s="1" t="inlineStr">
+      <c r="AA4" s="1" t="inlineStr">
         <is>
           <t>LA-ICP-MS (193 nm excimer laser + ICP-MS; top-level technique) [P4]</t>
         </is>
       </c>
-      <c r="Y4" s="1" t="inlineStr">
+      <c r="AB4" s="1" t="inlineStr">
         <is>
           <t>LA-ICP-MS (same as silicate protocol) [P4]</t>
         </is>
@@ -1075,68 +1116,78 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L5" s="9" t="n"/>
-      <c r="M5" s="1" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:creator.schema:Person | schema.Organization.schema:name</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>match. schema:creator is a Person or Organization; schema:name carries the author name (plus schema:identifier for ORCID).</t>
+        </is>
+      </c>
+      <c r="O5" s="9" t="n"/>
+      <c r="P5" s="1" t="inlineStr">
         <is>
           <t>Zhang, Chabot, Rubin, Humayun et al.</t>
         </is>
       </c>
-      <c r="N5" s="1" t="inlineStr">
+      <c r="Q5" s="1" t="inlineStr">
         <is>
           <t>Chernonozhkin, Pittarello, Goderis, Vanhaecke et al.</t>
         </is>
       </c>
-      <c r="O5" s="1" t="inlineStr">
+      <c r="R5" s="1" t="inlineStr">
         <is>
           <t>Chernonozhkin, Pittarello, Goderis, Vanhaecke et al.</t>
         </is>
       </c>
-      <c r="P5" s="1" t="inlineStr">
+      <c r="S5" s="1" t="inlineStr">
         <is>
           <t>Chernonozhkin, Pittarello, Goderis, Vanhaecke et al.</t>
         </is>
       </c>
-      <c r="Q5" s="1" t="inlineStr">
+      <c r="T5" s="1" t="inlineStr">
         <is>
           <t>Mittlefehldt</t>
         </is>
       </c>
-      <c r="R5" s="1" t="inlineStr">
+      <c r="U5" s="1" t="inlineStr">
         <is>
           <t>Nakanishi, Yokoyama, Okabayashi, Iwamori, Hirata</t>
         </is>
       </c>
-      <c r="S5" s="1" t="inlineStr">
+      <c r="V5" s="1" t="inlineStr">
         <is>
           <t>Navarro, Enzweiler, Crósta et al.</t>
         </is>
       </c>
-      <c r="T5" s="1" t="inlineStr">
+      <c r="W5" s="1" t="inlineStr">
         <is>
           <t>Navarro, Enzweiler, Crósta et al.</t>
         </is>
       </c>
-      <c r="U5" s="1" t="inlineStr">
+      <c r="X5" s="1" t="inlineStr">
         <is>
           <t>Liu, Xue, Li, Wang et al.</t>
         </is>
       </c>
-      <c r="V5" s="1" t="inlineStr">
+      <c r="Y5" s="1" t="inlineStr">
         <is>
           <t>Liu, Li, Xu, Xiong et al.</t>
         </is>
       </c>
-      <c r="W5" s="1" t="inlineStr">
+      <c r="Z5" s="1" t="inlineStr">
         <is>
           <t>Liu, Li, Xu, Xiong et al.</t>
         </is>
       </c>
-      <c r="X5" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Y5" s="1" t="inlineStr">
+      <c r="AA5" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB5" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1190,22 +1241,12 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L6" s="9" t="n"/>
-      <c r="M6" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N6" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O6" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>$Dataset.prov:wasGeneratedBy.schema:Agent/schema:Person.schema:name, schema:identifier</t>
+        </is>
+      </c>
+      <c r="O6" s="9" t="n"/>
       <c r="P6" s="1" t="inlineStr">
         <is>
           <t>N</t>
@@ -1248,10 +1289,25 @@
       </c>
       <c r="X6" s="1" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y6" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z6" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA6" s="1" t="inlineStr">
+        <is>
           <t>N (Allan Patchen and Luca Fedele assisted with data collection per acknowledgments; not explicitly named as analysts in methods) [P20-Ack]</t>
         </is>
       </c>
-      <c r="Y6" s="1" t="inlineStr">
+      <c r="AB6" s="1" t="inlineStr">
         <is>
           <t>N (same as silicate protocol) [P20-Ack]</t>
         </is>
@@ -1305,68 +1361,78 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L7" s="9" t="n"/>
-      <c r="M7" s="1" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:location.scheme:Place.schema:name</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>match. ada:laboratory extends spatialExtent (schema:Place); schema:name is the lab/facility name.</t>
+        </is>
+      </c>
+      <c r="O7" s="9" t="n"/>
+      <c r="P7" s="1" t="inlineStr">
         <is>
           <t>Plasma Analytical Facility, Florida State University, Tallahassee FL, USA</t>
         </is>
       </c>
-      <c r="N7" s="1" t="inlineStr">
+      <c r="Q7" s="1" t="inlineStr">
         <is>
           <t>Dept. of Chemistry, Atomic &amp; Mass Spectrometry, Ghent University, Belgium</t>
         </is>
       </c>
-      <c r="O7" s="1" t="inlineStr">
+      <c r="R7" s="1" t="inlineStr">
         <is>
           <t>Dept. of Chemistry, Atomic &amp; Mass Spectrometry, Ghent University, Belgium</t>
         </is>
       </c>
-      <c r="P7" s="1" t="inlineStr">
+      <c r="S7" s="1" t="inlineStr">
         <is>
           <t>Dept. of Chemistry, Atomic &amp; Mass Spectrometry, Ghent University, Belgium</t>
         </is>
       </c>
-      <c r="Q7" s="1" t="inlineStr">
+      <c r="T7" s="1" t="inlineStr">
         <is>
           <t>ICP-MS Laboratory, NASA Johnson Space Center, Houston TX, USA</t>
         </is>
       </c>
-      <c r="R7" s="1" t="inlineStr">
+      <c r="U7" s="1" t="inlineStr">
         <is>
           <t>Dept. of Earth and Planetary Sciences, Tokyo Institute of Technology, Japan</t>
         </is>
       </c>
-      <c r="S7" s="1" t="inlineStr">
+      <c r="V7" s="1" t="inlineStr">
         <is>
           <t>Isotope Geology Laboratory, University of Campinas (UNICAMP), Brazil</t>
         </is>
       </c>
-      <c r="T7" s="1" t="inlineStr">
+      <c r="W7" s="1" t="inlineStr">
         <is>
           <t>Isotope Geology Laboratory, University of Campinas (UNICAMP), Brazil</t>
         </is>
       </c>
-      <c r="U7" s="1" t="inlineStr">
+      <c r="X7" s="1" t="inlineStr">
         <is>
           <t>State Key Laboratory of Lithospheric Evolution and Environmental Coevolution, IGGCAS, Beijing, China</t>
         </is>
       </c>
-      <c r="V7" s="1" t="inlineStr">
+      <c r="Y7" s="1" t="inlineStr">
         <is>
           <t>State Key Laboratory of Isotope Geochemistry, Guangzhou Institute of Geochemistry, CAS, China</t>
         </is>
       </c>
-      <c r="W7" s="1" t="inlineStr">
+      <c r="Z7" s="1" t="inlineStr">
         <is>
           <t>State Key Laboratory of Isotope Geochemistry, Guangzhou Institute of Geochemistry, CAS, China</t>
         </is>
       </c>
-      <c r="X7" s="1" t="inlineStr">
+      <c r="AA7" s="1" t="inlineStr">
         <is>
           <t>Department of Geosciences, Virginia Tech [P4]</t>
         </is>
       </c>
-      <c r="Y7" s="1" t="inlineStr">
+      <c r="AB7" s="1" t="inlineStr">
         <is>
           <t>Department of Geosciences, Virginia Tech [P4]</t>
         </is>
@@ -1420,22 +1486,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L8" s="9" t="n"/>
-      <c r="M8" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N8" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O8" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:location.scheme:Place.schema:identifier</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>match. schema:Place schema:identifier (ROR or other PID) on ada:laboratory.</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="n"/>
       <c r="P8" s="1" t="inlineStr">
         <is>
           <t>N</t>
@@ -1482,6 +1543,21 @@
         </is>
       </c>
       <c r="Y8" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z8" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA8" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB8" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1535,22 +1611,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L9" s="9" t="n"/>
-      <c r="M9" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N9" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O9" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:datePublished</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>match. methodDefinition.schema:datePublished is explicitly described as 'ISO 8601 date when this method configuration was first used'.</t>
+        </is>
+      </c>
+      <c r="O9" s="9" t="n"/>
       <c r="P9" s="1" t="inlineStr">
         <is>
           <t>N</t>
@@ -1597,6 +1668,21 @@
         </is>
       </c>
       <c r="Y9" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z9" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA9" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB9" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1650,22 +1736,12 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L10" s="9" t="n"/>
-      <c r="M10" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N10" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O10" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>$Dataset.prov:wasGeneratedBy.schema:startDate</t>
+        </is>
+      </c>
+      <c r="O10" s="9" t="n"/>
       <c r="P10" s="1" t="inlineStr">
         <is>
           <t>N</t>
@@ -1712,6 +1788,21 @@
         </is>
       </c>
       <c r="Y10" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z10" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA10" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB10" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1765,22 +1856,12 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L11" s="9" t="n"/>
-      <c r="M11" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N11" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O11" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>$Dataset.prov:wasGeneratedBy.schema:endDate</t>
+        </is>
+      </c>
+      <c r="O11" s="9" t="n"/>
       <c r="P11" s="1" t="inlineStr">
         <is>
           <t>N</t>
@@ -1827,6 +1908,21 @@
         </is>
       </c>
       <c r="Y11" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z11" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA11" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB11" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1880,22 +1976,12 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L12" s="9" t="n"/>
-      <c r="M12" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N12" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O12" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:identifier</t>
+        </is>
+      </c>
+      <c r="O12" s="9" t="n"/>
       <c r="P12" s="1" t="inlineStr">
         <is>
           <t>N</t>
@@ -1942,6 +2028,21 @@
         </is>
       </c>
       <c r="Y12" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z12" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA12" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB12" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1999,68 +2100,83 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L13" s="9" t="n"/>
-      <c r="M13" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N13" s="1" t="inlineStr">
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:funding[].schema:MonetaryGrant.schema:name</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>match. schema:funding[] is an array of MonetaryGrant; also has schema:identifier (award number) and schema:funder (organisation).</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>put text in MonetaryGrant name unless can clearly parse identifier distinct from name.</t>
+        </is>
+      </c>
+      <c r="O13" s="9" t="n"/>
+      <c r="P13" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q13" s="1" t="inlineStr">
         <is>
           <t>Planet Topers (BELSPO Interuniversity Attraction Poles); FWO postdoctoral fellowship for SCh; FWO "Excellence of Science" (ET-HoME ID 30442502); FWO/BOF-UGent; Alexander von Humboldt Foundation; FWO/BELSPO/VUB for SG and PC</t>
         </is>
       </c>
-      <c r="O13" s="1" t="inlineStr">
+      <c r="R13" s="1" t="inlineStr">
         <is>
           <t>Planet Topers (BELSPO); FWO; Alexander von Humboldt Foundation; FWO/BOF-UGent</t>
         </is>
       </c>
-      <c r="P13" s="1" t="inlineStr">
+      <c r="S13" s="1" t="inlineStr">
         <is>
           <t>Planet Topers (BELSPO); FWO; Alexander von Humboldt Foundation; FWO/BOF-UGent</t>
         </is>
       </c>
-      <c r="Q13" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="R13" s="1" t="inlineStr">
+      <c r="T13" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U13" s="1" t="inlineStr">
         <is>
           <t>JSPS KAKENHI; Tokyo Institute of Technology</t>
         </is>
       </c>
-      <c r="S13" s="1" t="inlineStr">
+      <c r="V13" s="1" t="inlineStr">
         <is>
           <t>FAPESP (São Paulo Research Foundation); CNPq</t>
         </is>
       </c>
-      <c r="T13" s="1" t="inlineStr">
+      <c r="W13" s="1" t="inlineStr">
         <is>
           <t>FAPESP; CNPq</t>
         </is>
       </c>
-      <c r="U13" s="1" t="inlineStr">
+      <c r="X13" s="1" t="inlineStr">
         <is>
           <t>NSFC; Chinese Academy of Sciences</t>
         </is>
       </c>
-      <c r="V13" s="1" t="inlineStr">
+      <c r="Y13" s="1" t="inlineStr">
         <is>
           <t>Strategic Priority Research Program (B) CAS; NSFC 92062222, 42073057, 42250710679, 42250202, 42273023</t>
         </is>
       </c>
-      <c r="W13" s="1" t="inlineStr">
+      <c r="Z13" s="1" t="inlineStr">
         <is>
           <t>Strategic Priority Research Program (B) CAS; NSFC 92062222, 42073057, 42250710679, 42250202, 42273023</t>
         </is>
       </c>
-      <c r="X13" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Y13" s="1" t="inlineStr">
+      <c r="AA13" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB13" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2118,68 +2234,73 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L14" s="9" t="n"/>
-      <c r="M14" s="1" t="inlineStr">
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>$Dataset.schema:funding</t>
+        </is>
+      </c>
+      <c r="O14" s="9" t="n"/>
+      <c r="P14" s="1" t="inlineStr">
         <is>
           <t>NASA Grants 80NSSC19K1238 (BZ), 80NSSC19K1613 (NLC), 80NSSC18K0595 (MH), NNX17AE77G (AER); NSF Cooperative Agreement DMR-1644779 and State of Florida [Acknowledgements]</t>
         </is>
       </c>
-      <c r="N14" s="1" t="inlineStr">
+      <c r="Q14" s="1" t="inlineStr">
         <is>
           <t>Planet Topers (BELSPO); FWO; Alexander von Humboldt Foundation; FWO/BOF-UGent</t>
         </is>
       </c>
-      <c r="O14" s="1" t="inlineStr">
+      <c r="R14" s="1" t="inlineStr">
         <is>
           <t>Planet Topers (BELSPO); FWO; Alexander von Humboldt Foundation; FWO/BOF-UGent</t>
         </is>
       </c>
-      <c r="P14" s="1" t="inlineStr">
+      <c r="S14" s="1" t="inlineStr">
         <is>
           <t>Planet Topers (BELSPO); FWO; Alexander von Humboldt Foundation; FWO/BOF-UGent</t>
         </is>
       </c>
-      <c r="Q14" s="1" t="inlineStr">
+      <c r="T14" s="1" t="inlineStr">
         <is>
           <t>N (no funding section in this appendix document; funding would be in the parent paper which was not assessed)</t>
         </is>
       </c>
-      <c r="R14" s="1" t="inlineStr">
+      <c r="U14" s="1" t="inlineStr">
         <is>
           <t>JSPS Grant-in-Aid for Scientific Research (grants 26106002, 26220713, 16H04081, 19H00715, 19H01081, 20H04609)</t>
         </is>
       </c>
-      <c r="S14" s="1" t="inlineStr">
+      <c r="V14" s="1" t="inlineStr">
         <is>
           <t>M.S.N.: Educorp (Unicamp) and International Association of Geoanalysts for Geoanalysis 2022 presentation; J.E.: CNPq grant 316191/2021-3</t>
         </is>
       </c>
-      <c r="T14" s="1" t="inlineStr">
+      <c r="W14" s="1" t="inlineStr">
         <is>
           <t>M.S.N.: Educorp (Unicamp) and International Association of Geoanalysts; J.E.: CNPq grant 316191/2021-3</t>
         </is>
       </c>
-      <c r="U14" s="1" t="inlineStr">
+      <c r="X14" s="1" t="inlineStr">
         <is>
           <t>Strategy Priority Research Program (Category B) of Chinese Academy of Sciences (XDB0710000); NSFC 42073022</t>
         </is>
       </c>
-      <c r="V14" s="1" t="inlineStr">
+      <c r="Y14" s="1" t="inlineStr">
         <is>
           <t>Strategic Priority Research Program (B) of CAS (XDB0840200); NSFC 92062222, 42073057, 42250710679, 42250202, 42273023</t>
         </is>
       </c>
-      <c r="W14" s="1" t="inlineStr">
+      <c r="Z14" s="1" t="inlineStr">
         <is>
           <t>Strategic Priority Research Program (B) of CAS (XDB0840200); NSFC 92062222, 42073057, 42250710679, 42250202, 42273023</t>
         </is>
       </c>
-      <c r="X14" s="1" t="inlineStr">
+      <c r="AA14" s="1" t="inlineStr">
         <is>
           <t>NASA Cosmochemistry grants NNX11AG58G (to L.A.T.) and NNN13D465T (to Y.L.); NSF EAR-1226270 (to P.D.A.) and EAR-1019770 (to R.J.B.); Y.L. supported by Jet Propulsion Laboratory [P20-Ack]</t>
         </is>
       </c>
-      <c r="Y14" s="1" t="inlineStr">
+      <c r="AB14" s="1" t="inlineStr">
         <is>
           <t>Same as silicate protocol [P20-Ack]</t>
         </is>
@@ -2233,68 +2354,83 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L15" s="9" t="n"/>
-      <c r="M15" s="1" t="inlineStr">
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:relatedLink[].schema:linkRelationship[name =  'techniquePublication'].</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>match. schema:relatedLink[] is a labeledLink with schema:url and schema:name; fits DOIs/URLs of method publications.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>target URL to publication , target name should be title of publication</t>
+        </is>
+      </c>
+      <c r="O15" s="9" t="n"/>
+      <c r="P15" s="1" t="inlineStr">
         <is>
           <t>Zhang et al. (2022) GCA 323, 202–219; Humayun (2012) for standardization</t>
         </is>
       </c>
-      <c r="N15" s="1" t="inlineStr">
+      <c r="Q15" s="1" t="inlineStr">
         <is>
           <t>Chernonozhkin et al. (2021) Chem. Geol. 562; Liu et al. (2008) for IS method</t>
         </is>
       </c>
-      <c r="O15" s="1" t="inlineStr">
+      <c r="R15" s="1" t="inlineStr">
         <is>
           <t>Chernonozhkin et al. (2021) Chem. Geol. 562; Liu et al. (2008) for IS method</t>
         </is>
       </c>
-      <c r="P15" s="1" t="inlineStr">
+      <c r="S15" s="1" t="inlineStr">
         <is>
           <t>Chernonozhkin et al. (2021) Chem. Geol. 562; Liu et al. (2008) for IS method</t>
         </is>
       </c>
-      <c r="Q15" s="1" t="inlineStr">
+      <c r="T15" s="1" t="inlineStr">
         <is>
           <t>Mittlefehldt (2024) GCA; Lee (Rice University) Excel data reduction spreadsheet</t>
         </is>
       </c>
-      <c r="R15" s="1" t="inlineStr">
+      <c r="U15" s="1" t="inlineStr">
         <is>
           <t>Nakanishi et al. (2022) GCA 319, 254; Walker et al. (2008) for IVB standards</t>
         </is>
       </c>
-      <c r="S15" s="1" t="inlineStr">
+      <c r="V15" s="1" t="inlineStr">
         <is>
           <t>Navarro et al. (2024) ACS Earth Space Chem. 8, 281; Longerich et al. (1996)</t>
         </is>
       </c>
-      <c r="T15" s="1" t="inlineStr">
+      <c r="W15" s="1" t="inlineStr">
         <is>
           <t>Navarro et al. (2024) ACS Earth Space Chem. 8, 281; Longerich et al. (1996)</t>
         </is>
       </c>
-      <c r="U15" s="1" t="inlineStr">
+      <c r="X15" s="1" t="inlineStr">
         <is>
           <t>Liu et al. (2024) JAAS 39, 2728; Pettke et al. (2012) for LOD</t>
         </is>
       </c>
-      <c r="V15" s="1" t="inlineStr">
+      <c r="Y15" s="1" t="inlineStr">
         <is>
           <t>Liu et al. (2025) GCA 393, 170; Xu et al. (2022) for experimental protocol</t>
         </is>
       </c>
-      <c r="W15" s="1" t="inlineStr">
+      <c r="Z15" s="1" t="inlineStr">
         <is>
           <t>Liu et al. (2025) GCA 393, 170; Xu et al. (2022)</t>
         </is>
       </c>
-      <c r="X15" s="1" t="inlineStr">
+      <c r="AA15" s="1" t="inlineStr">
         <is>
           <t>Udry et al. (2012) and Pernet-Fisher et al. (2014) cited as broad references for the analytical procedure [P4]</t>
         </is>
       </c>
-      <c r="Y15" s="1" t="inlineStr">
+      <c r="AB15" s="1" t="inlineStr">
         <is>
           <t>Same as silicate protocol [P4]</t>
         </is>
@@ -2352,27 +2488,28 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L16" s="9" t="n"/>
-      <c r="M16" s="1" t="inlineStr">
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:relatedLink[].schema:linkRelationship[name =  'coupledTechnique'].schema:target.schema:name</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>range should be analytical technique vocabulary</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>schema:DefinedTerm.schema:termCode
+datatype: enum {EPMA | SIMS | ICP-MS (solution) | Noble Gas MS | Other: specify | None}</t>
+        </is>
+      </c>
+      <c r="O16" s="9" t="n"/>
+      <c r="P16" s="1" t="inlineStr">
         <is>
           <t>EPMA (Brown University CAMECA SX-100)</t>
         </is>
       </c>
-      <c r="N16" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O16" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P16" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="Q16" s="1" t="inlineStr">
         <is>
           <t>N</t>
@@ -2380,24 +2517,24 @@
       </c>
       <c r="R16" s="1" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S16" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T16" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U16" s="1" t="inlineStr">
+        <is>
           <t>EPMA (electron probe microanalysis)</t>
         </is>
       </c>
-      <c r="S16" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="T16" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="U16" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="V16" s="1" t="inlineStr">
         <is>
           <t>N</t>
@@ -2410,10 +2547,25 @@
       </c>
       <c r="X16" s="1" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y16" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z16" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA16" s="1" t="inlineStr">
+        <is>
           <t>EPMA (EMP) [P4]</t>
         </is>
       </c>
-      <c r="Y16" s="1" t="inlineStr">
+      <c r="AB16" s="1" t="inlineStr">
         <is>
           <t>EPMA (EMP) [P4]</t>
         </is>
@@ -2471,27 +2623,25 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L17" s="9" t="n"/>
-      <c r="M17" s="1" t="inlineStr">
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:relatedLink[].schema:linkRelationship[name =  'coupledTechnique'].schema:target.schema:description</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>386</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>text description of relationship</t>
+        </is>
+      </c>
+      <c r="O17" s="9" t="n"/>
+      <c r="P17" s="1" t="inlineStr">
         <is>
           <t>Quantitative analysis, mixed WDS/EDS element mapping, and characterization of mineral phases from NWA 1911 and Zinder [Section 2.5]</t>
         </is>
       </c>
-      <c r="N17" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O17" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P17" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="Q17" s="1" t="inlineStr">
         <is>
           <t>N</t>
@@ -2499,24 +2649,24 @@
       </c>
       <c r="R17" s="1" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S17" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T17" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U17" s="1" t="inlineStr">
+        <is>
           <t>EPMA used to measure Ni concentration at the exact LA-ICP-MS analysis spot location, required for internal standardization of HSE data [Section 2.3]</t>
         </is>
       </c>
-      <c r="S17" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="T17" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="U17" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="V17" s="1" t="inlineStr">
         <is>
           <t>N</t>
@@ -2529,10 +2679,25 @@
       </c>
       <c r="X17" s="1" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y17" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z17" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA17" s="1" t="inlineStr">
+        <is>
           <t>EPMA provides major element concentrations for comparison with LA-ICP-MS oxide-sum normalization results; agreement within &lt;10% verified [P4]</t>
         </is>
       </c>
-      <c r="Y17" s="1" t="inlineStr">
+      <c r="AB17" s="1" t="inlineStr">
         <is>
           <t>EPMA provides CaO concentration at exact analysis spot, used as internal standard for LA-ICP-MS data reduction (LA-ICP-MS 40Ca counts normalized to EMP CaO) [P4]</t>
         </is>
@@ -2590,22 +2755,12 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L18" s="9" t="n"/>
-      <c r="M18" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N18" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O18" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>$Dataset.schema:relatedLink[].schema:linkRelationship[name =  'coupledTechnique'].schema:target.schema:url</t>
+        </is>
+      </c>
+      <c r="O18" s="9" t="n"/>
       <c r="P18" s="1" t="inlineStr">
         <is>
           <t>N</t>
@@ -2652,6 +2807,21 @@
         </is>
       </c>
       <c r="Y18" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z18" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA18" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB18" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2709,22 +2879,12 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L19" s="9" t="n"/>
-      <c r="M19" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N19" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O19" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>$Dataset.schema:relatedLink[].schema:linkRelationship[name =  'coupledDataset'].schema:target</t>
+        </is>
+      </c>
+      <c r="O19" s="9" t="n"/>
       <c r="P19" s="1" t="inlineStr">
         <is>
           <t>N</t>
@@ -2771,6 +2931,21 @@
         </is>
       </c>
       <c r="Y19" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z19" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA19" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB19" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2793,9 +2968,6 @@
       <c r="I21" s="5" t="n"/>
       <c r="J21" s="5" t="n"/>
       <c r="K21" s="5" t="n"/>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
       <c r="O21" s="5" t="n"/>
       <c r="P21" s="5" t="n"/>
       <c r="Q21" s="5" t="n"/>
@@ -2805,12 +2977,15 @@
       <c r="U21" s="5" t="n"/>
       <c r="V21" s="5" t="n"/>
       <c r="W21" s="5" t="n"/>
-      <c r="X21" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Y21" s="5" t="inlineStr">
+      <c r="X21" s="5" t="n"/>
+      <c r="Y21" s="5" t="n"/>
+      <c r="Z21" s="5" t="n"/>
+      <c r="AA21" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB21" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2864,68 +3039,84 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L22" s="9" t="n"/>
-      <c r="M22" s="1" t="inlineStr">
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:object[].schema:DefinedTerm.schema.name</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>match. schema:object[] is an array of DefinedTerm or string describing target material (mineral phase, glass, oxide, etc.). Need vocabulary or target materials…</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>schema:DefinedTerm.schema:termCode
+datatype: enum {Silicate glass | Feldspar | Pyroxene | Olivine | Oxide | Sulfide | Carbonate | Phosphate | Native metal | Iron meteorite | Fluid inclusion | Melt inclusion | Whole rock | Other: specify}</t>
+        </is>
+      </c>
+      <c r="O22" s="9" t="n"/>
+      <c r="P22" s="1" t="inlineStr">
         <is>
           <t>Iron meteorite metal (kamacite + taenite); pyroxene-bearing pallasite metal</t>
         </is>
       </c>
-      <c r="N22" s="1" t="inlineStr">
+      <c r="Q22" s="1" t="inlineStr">
         <is>
           <t>Pallasite olivine ([Mg,Fe]₂SiO₄)</t>
         </is>
       </c>
-      <c r="O22" s="1" t="inlineStr">
+      <c r="R22" s="1" t="inlineStr">
         <is>
           <t>Pallasite olivine ([Mg,Fe]₂SiO₄)</t>
         </is>
       </c>
-      <c r="P22" s="1" t="inlineStr">
+      <c r="S22" s="1" t="inlineStr">
         <is>
           <t>Pallasite Ca-phosphate (merrillite, stanfieldite, farringtonite)</t>
         </is>
       </c>
-      <c r="Q22" s="1" t="inlineStr">
+      <c r="T22" s="1" t="inlineStr">
         <is>
           <t>Pallasite olivine ([Mg,Fe]₂SiO₄)</t>
         </is>
       </c>
-      <c r="R22" s="1" t="inlineStr">
+      <c r="U22" s="1" t="inlineStr">
         <is>
           <t>CR chondrite metal grains (interior, margin, and isolated types)</t>
         </is>
       </c>
-      <c r="S22" s="1" t="inlineStr">
+      <c r="V22" s="1" t="inlineStr">
         <is>
           <t>Iron meteorite metal (kamacite + taenite)</t>
         </is>
       </c>
-      <c r="T22" s="1" t="inlineStr">
+      <c r="W22" s="1" t="inlineStr">
         <is>
           <t>Iron meteorite metal (kamacite + plessite)</t>
         </is>
       </c>
-      <c r="U22" s="1" t="inlineStr">
+      <c r="X22" s="1" t="inlineStr">
         <is>
           <t>Li-borate flux fusion glass (extraterrestrial sample preparation)</t>
         </is>
       </c>
-      <c r="V22" s="1" t="inlineStr">
+      <c r="Y22" s="1" t="inlineStr">
         <is>
           <t>Experimental dacitic silicate glass (quench product)</t>
         </is>
       </c>
-      <c r="W22" s="1" t="inlineStr">
+      <c r="Z22" s="1" t="inlineStr">
         <is>
           <t>Experimental pyrrhotite (Fe₁₋ₓS) sulfide (quench product)</t>
         </is>
       </c>
-      <c r="X22" s="1" t="inlineStr">
+      <c r="AA22" s="1" t="inlineStr">
         <is>
           <t>Martian meteorite (Tissint) silicates, oxides, and glass: olivine, low-Ca pyroxene, augite, maskelynite, Fe-Ti-Cr oxides, shock melt glass, fusion crust [P4]</t>
         </is>
       </c>
-      <c r="Y22" s="1" t="inlineStr">
+      <c r="AB22" s="1" t="inlineStr">
         <is>
           <t>Martian meteorite (Tissint) phosphate: sodium-merrillite [P4, P12]</t>
         </is>
@@ -2979,68 +3170,83 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L23" s="9" t="n"/>
-      <c r="M23" s="1" t="inlineStr">
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:object[].schema:DefinedTerm.schema.name</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>match. schema:object[] is an array of DefinedTerm or string describing target object type. TBD-- map to sesar object type vocabulary</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>property:sampleFormAnalyticalSubstrateDefault dataType: string readOnly: False enum {In situ — polished thin section | In situ — polished epoxy mount | In situ — polished thick section | Pressed powder pellet | Li-borate fused glass disc | Nano-particulate pressed pellet | Liquid}</t>
+        </is>
+      </c>
+      <c r="O23" s="9" t="n"/>
+      <c r="P23" s="1" t="inlineStr">
         <is>
           <t>Polished metal slab (in situ)</t>
         </is>
       </c>
-      <c r="N23" s="1" t="inlineStr">
+      <c r="Q23" s="1" t="inlineStr">
         <is>
           <t>In situ — polished epoxy thick section (HELEX II two-volume cell)</t>
         </is>
       </c>
-      <c r="O23" s="1" t="inlineStr">
+      <c r="R23" s="1" t="inlineStr">
         <is>
           <t>In situ — polished epoxy thick section; pre-ablated before trace element run</t>
         </is>
       </c>
-      <c r="P23" s="1" t="inlineStr">
+      <c r="S23" s="1" t="inlineStr">
         <is>
           <t>In situ — polished epoxy thick section</t>
         </is>
       </c>
-      <c r="Q23" s="1" t="inlineStr">
+      <c r="T23" s="1" t="inlineStr">
         <is>
           <t>In situ — polished grain mount (olivine grain fragments)</t>
         </is>
       </c>
-      <c r="R23" s="1" t="inlineStr">
+      <c r="U23" s="1" t="inlineStr">
         <is>
           <t>In situ — polished epoxy thick section (petropoxy 154 resin, 0.5 µm diamond finish)</t>
         </is>
       </c>
-      <c r="S23" s="1" t="inlineStr">
+      <c r="V23" s="1" t="inlineStr">
         <is>
           <t>In situ — polished epoxy mount (~1 cm fragments in epoxy, etched with Nital)</t>
         </is>
       </c>
-      <c r="T23" s="1" t="inlineStr">
+      <c r="W23" s="1" t="inlineStr">
         <is>
           <t>In situ — polished epoxy mount (same Augusto Pestana fragment as spot protocol)</t>
         </is>
       </c>
-      <c r="U23" s="1" t="inlineStr">
+      <c r="X23" s="1" t="inlineStr">
         <is>
           <t>Li-borate flux fusion glass disc (10 mg sample + 350 mg Li₂B₄O₇, 35:1 dilution)</t>
         </is>
       </c>
-      <c r="V23" s="1" t="inlineStr">
+      <c r="Y23" s="1" t="inlineStr">
         <is>
           <t>In situ — polished epoxy mount (experimental capsule half-section)</t>
         </is>
       </c>
-      <c r="W23" s="1" t="inlineStr">
+      <c r="Z23" s="1" t="inlineStr">
         <is>
           <t>In situ — polished epoxy mount (same capsule section as glass protocol)</t>
         </is>
       </c>
-      <c r="X23" s="1" t="inlineStr">
+      <c r="AA23" s="1" t="inlineStr">
         <is>
           <t>In situ — polished thin section (Tissint sections: Tata-2-C3, Tata-3-C2, UT1, UT3) [P4, P5-P11]</t>
         </is>
       </c>
-      <c r="Y23" s="1" t="inlineStr">
+      <c r="AB23" s="1" t="inlineStr">
         <is>
           <t>In situ — polished thin section (same sections as silicate protocol) [P4]</t>
         </is>
@@ -3094,22 +3300,12 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L24" s="9" t="n"/>
-      <c r="M24" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N24" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O24" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>$Dataset.prov:wasGeneratedBy.schema:object[@type ="schema:Thing",            "https://w3id.org/isample/vocabulary/materialsampleobjecttype/materialsample"].schema:name</t>
+        </is>
+      </c>
+      <c r="O24" s="9" t="n"/>
       <c r="P24" s="1" t="inlineStr">
         <is>
           <t>N</t>
@@ -3152,10 +3348,25 @@
       </c>
       <c r="X24" s="1" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y24" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z24" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA24" s="1" t="inlineStr">
+        <is>
           <t>Tissint Martian meteorite [P4]</t>
         </is>
       </c>
-      <c r="Y24" s="1" t="inlineStr">
+      <c r="AB24" s="1" t="inlineStr">
         <is>
           <t>Tissint Martian meteorite [P4]</t>
         </is>
@@ -3209,22 +3420,12 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L25" s="9" t="n"/>
-      <c r="M25" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N25" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O25" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>$Dataset.prov:wasGeneratedBy.schema:object[@type = "schema:Thing",  "https://w3id.org/isample/vocabulary/materialsampleobjecttype/materialsample"].schema:identifier</t>
+        </is>
+      </c>
+      <c r="O25" s="9" t="n"/>
       <c r="P25" s="1" t="inlineStr">
         <is>
           <t>N</t>
@@ -3271,6 +3472,21 @@
         </is>
       </c>
       <c r="Y25" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z25" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA25" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB25" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -3324,68 +3540,83 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L26" s="9" t="n"/>
-      <c r="M26" s="1" t="inlineStr">
+      <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$MethodDefinition.schema:actionProcess.schema:step[][schema:name='samplePreparation'].schema:additionalProperty.schema:name </t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>two properties of sample preparation method</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>parameter:fusionFluxAndDilutionRatio dataType: string readOnly: True</t>
+        </is>
+      </c>
+      <c r="O26" s="9" t="n"/>
+      <c r="P26" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="N26" s="1" t="inlineStr">
+      <c r="Q26" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="O26" s="1" t="inlineStr">
+      <c r="R26" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="P26" s="1" t="inlineStr">
+      <c r="S26" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="Q26" s="1" t="inlineStr">
+      <c r="T26" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="R26" s="1" t="inlineStr">
+      <c r="U26" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S26" s="1" t="inlineStr">
+      <c r="V26" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="T26" s="1" t="inlineStr">
+      <c r="W26" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="U26" s="1" t="inlineStr">
+      <c r="X26" s="1" t="inlineStr">
         <is>
           <t>Li₂B₄O₇ flux; sample:flux = 1:35 (10 mg sample + 350 mg flux)</t>
         </is>
       </c>
-      <c r="V26" s="1" t="inlineStr">
+      <c r="Y26" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="W26" s="1" t="inlineStr">
+      <c r="Z26" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="X26" s="1" t="inlineStr">
+      <c r="AA26" s="1" t="inlineStr">
         <is>
           <t>N/A (in situ)</t>
         </is>
       </c>
-      <c r="Y26" s="1" t="inlineStr">
+      <c r="AB26" s="1" t="inlineStr">
         <is>
           <t>N/A (in situ)</t>
         </is>
@@ -3439,68 +3670,83 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L27" s="9" t="n"/>
-      <c r="M27" s="1" t="inlineStr">
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:actionProcess.schema:step[][schema:name='samplePreparation'].schema:description</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Sample preparation is a dedicated step (typically schema:position=1) in the actionProcess; schema:object is input, mostly likely the original sample. Schema:result is the product that will be used directly for analysis, e.g. polished thin section or epoxy mount; describe procedure in schema:step/schema:description</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>property:samplePreparationMethodDefault dataType: string readOnly: False</t>
+        </is>
+      </c>
+      <c r="O27" s="9" t="n"/>
+      <c r="P27" s="1" t="inlineStr">
         <is>
           <t>Polished metal slabs and thin sections; no acid treatment described</t>
         </is>
       </c>
-      <c r="N27" s="1" t="inlineStr">
+      <c r="Q27" s="1" t="inlineStr">
         <is>
           <t>PMG thick sections polished; HELEX II two-volume cell; C-coated for SEM then coating removed before LA</t>
         </is>
       </c>
-      <c r="O27" s="1" t="inlineStr">
+      <c r="R27" s="1" t="inlineStr">
         <is>
           <t>PMG thick sections polished; pre-ablation pass (2 J cm⁻², 20 Hz, 150 µm square, 300 µm s⁻¹) before trace element run</t>
         </is>
       </c>
-      <c r="P27" s="1" t="inlineStr">
+      <c r="S27" s="1" t="inlineStr">
         <is>
           <t>PMG thick sections polished; same as olivine mapping preparation</t>
         </is>
       </c>
-      <c r="Q27" s="1" t="inlineStr">
+      <c r="T27" s="1" t="inlineStr">
         <is>
           <t>Olivine grain fragments repeatedly washed in dilute HCl and triply distilled H₂O, hand-picked, polished grain mounts</t>
         </is>
       </c>
-      <c r="R27" s="1" t="inlineStr">
+      <c r="U27" s="1" t="inlineStr">
         <is>
           <t>Thick sections in petropoxy 154 resin, polished to 0.5 µm diamond paste, C-coated for EPMA then surface polished before LA</t>
         </is>
       </c>
-      <c r="S27" s="1" t="inlineStr">
+      <c r="V27" s="1" t="inlineStr">
         <is>
           <t>Fragments ~1 cm mounted in epoxy resin, polished, cleaned with ultrapure water</t>
         </is>
       </c>
-      <c r="T27" s="1" t="inlineStr">
+      <c r="W27" s="1" t="inlineStr">
         <is>
           <t>Same Augusto Pestana fragment etched with Nital solution (2% v/v HNO₃ in ethanol) to reveal kamacite and plessite</t>
         </is>
       </c>
-      <c r="U27" s="1" t="inlineStr">
+      <c r="X27" s="1" t="inlineStr">
         <is>
           <t>Li-borate fusion: 350 mg Li₂B₄O₇ + 10 mg powdered sample fused in Pt-Au crucible (M4 automatic fluxer); glass surface cleaned with ethanol before LA</t>
         </is>
       </c>
-      <c r="V27" s="1" t="inlineStr">
+      <c r="Y27" s="1" t="inlineStr">
         <is>
           <t>Experimental capsule longitudinally sectioned with wire saw; half mounted in epoxy for analysis</t>
         </is>
       </c>
-      <c r="W27" s="1" t="inlineStr">
+      <c r="Z27" s="1" t="inlineStr">
         <is>
           <t>Same capsule section as silicate glass; sulfide grains ≥20 µm selected by SEM-BSE</t>
         </is>
       </c>
-      <c r="X27" s="1" t="inlineStr">
+      <c r="AA27" s="1" t="inlineStr">
         <is>
           <t>N (not described; sections mentioned; polished implied) [P4]</t>
         </is>
       </c>
-      <c r="Y27" s="1" t="inlineStr">
+      <c r="AB27" s="1" t="inlineStr">
         <is>
           <t>N (same as silicate protocol) [P4]</t>
         </is>
@@ -3554,68 +3800,83 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L28" s="9" t="n"/>
-      <c r="M28" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N28" s="1" t="inlineStr">
+      <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$MethodDefinition.schema:actionProcess.schema:step[][schema:name='samplePreparation'].schema:additionalProperty.schema:name </t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> property of sample preparation method</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>parameter:preAblationSurfaceTreatment dataType: string readOnly: True</t>
+        </is>
+      </c>
+      <c r="O28" s="9" t="n"/>
+      <c r="P28" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q28" s="1" t="inlineStr">
         <is>
           <t>N (mapping; surface effects average out over large area)</t>
         </is>
       </c>
-      <c r="O28" s="1" t="inlineStr">
+      <c r="R28" s="1" t="inlineStr">
         <is>
           <t>Pre-ablation pass: 150 µm square, 2 J cm⁻², 20 Hz, 300 µm s⁻¹ scan before trace element spot run; removes surface contamination and re-deposited material</t>
         </is>
       </c>
-      <c r="P28" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q28" s="1" t="inlineStr">
+      <c r="S28" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T28" s="1" t="inlineStr">
         <is>
           <t>N (grains imaged by SEM to locate inclusion-free regions)</t>
         </is>
       </c>
-      <c r="R28" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="S28" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="T28" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="U28" s="1" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V28" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W28" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X28" s="1" t="inlineStr">
+        <is>
           <t>Surface cleaning with ethanol before analysis</t>
         </is>
       </c>
-      <c r="V28" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="W28" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="X28" s="1" t="inlineStr">
+      <c r="Y28" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z28" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA28" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
       </c>
-      <c r="Y28" s="1" t="inlineStr">
+      <c r="AB28" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
@@ -3638,9 +3899,6 @@
       <c r="I30" s="5" t="n"/>
       <c r="J30" s="5" t="n"/>
       <c r="K30" s="5" t="n"/>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
       <c r="O30" s="5" t="n"/>
       <c r="P30" s="5" t="n"/>
       <c r="Q30" s="5" t="n"/>
@@ -3650,12 +3908,15 @@
       <c r="U30" s="5" t="n"/>
       <c r="V30" s="5" t="n"/>
       <c r="W30" s="5" t="n"/>
-      <c r="X30" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Y30" s="5" t="inlineStr">
+      <c r="X30" s="5" t="n"/>
+      <c r="Y30" s="5" t="n"/>
+      <c r="Z30" s="5" t="n"/>
+      <c r="AA30" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB30" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -3713,68 +3974,83 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L31" s="9" t="n"/>
-      <c r="M31" s="1" t="inlineStr">
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:instrument[additionalType = 'Laser ablation system'].schema:manufacturer.schema:Organization.schema:name | .schema:instrument.schema:model.schema:name</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>match. CDIF instrument has manufacturer, and model</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>The laser ablation system that generates particles for the mass analyzer</t>
+        </is>
+      </c>
+      <c r="O31" s="9" t="n"/>
+      <c r="P31" s="1" t="inlineStr">
         <is>
           <t>ESI New Wave UP193FX (193 nm Nd:YAG frequency-quintupled solid state)</t>
         </is>
       </c>
-      <c r="N31" s="1" t="inlineStr">
+      <c r="Q31" s="1" t="inlineStr">
         <is>
           <t>Teledyne CETAC Technologies Analyte G2 (193 nm ArF excimer)</t>
         </is>
       </c>
-      <c r="O31" s="1" t="inlineStr">
+      <c r="R31" s="1" t="inlineStr">
         <is>
           <t>Teledyne CETAC Technologies Analyte G2 (193 nm ArF excimer)</t>
         </is>
       </c>
-      <c r="P31" s="1" t="inlineStr">
+      <c r="S31" s="1" t="inlineStr">
         <is>
           <t>Teledyne CETAC Technologies Analyte G2 (193 nm ArF excimer)</t>
         </is>
       </c>
-      <c r="Q31" s="1" t="inlineStr">
+      <c r="T31" s="1" t="inlineStr">
         <is>
           <t>New Wave UP-193 (solid state, 193 nm)</t>
         </is>
       </c>
-      <c r="R31" s="1" t="inlineStr">
+      <c r="U31" s="1" t="inlineStr">
         <is>
           <t>Cyber Laser IFRIT (Ti:sapphire fs UV laser, 260 nm)</t>
         </is>
       </c>
-      <c r="S31" s="1" t="inlineStr">
+      <c r="V31" s="1" t="inlineStr">
         <is>
           <t>Teledyne Excite 193 (193 nm ArF excimer)</t>
         </is>
       </c>
-      <c r="T31" s="1" t="inlineStr">
+      <c r="W31" s="1" t="inlineStr">
         <is>
           <t>Teledyne Excite 193 (193 nm ArF excimer)</t>
         </is>
       </c>
-      <c r="U31" s="1" t="inlineStr">
+      <c r="X31" s="1" t="inlineStr">
         <is>
           <t>Shanghai Chemlab GenesisGEO (high-repetition-rate fs laser, 343 nm)</t>
         </is>
       </c>
-      <c r="V31" s="1" t="inlineStr">
+      <c r="Y31" s="1" t="inlineStr">
         <is>
           <t>Resonetics 193 nm ArF excimer laser (coupled to Cetac Analyte HE system)</t>
         </is>
       </c>
-      <c r="W31" s="1" t="inlineStr">
+      <c r="Z31" s="1" t="inlineStr">
         <is>
           <t>Resonetics 193 nm ArF excimer laser (coupled to Cetac Analyte HE system; same system as glass protocol)</t>
         </is>
       </c>
-      <c r="X31" s="1" t="inlineStr">
+      <c r="AA31" s="1" t="inlineStr">
         <is>
           <t>GeoLasPro (193 nm Excimer laser-ablation system; manufacturer not stated by name; GeoLasPro is a Lambda Physik/Coherent product) [P4]</t>
         </is>
       </c>
-      <c r="Y31" s="1" t="inlineStr">
+      <c r="AB31" s="1" t="inlineStr">
         <is>
           <t>GeoLasPro 193 nm Excimer laser-ablation system (same as silicate protocol) [P4]</t>
         </is>
@@ -3828,68 +4104,83 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L32" s="9" t="n"/>
-      <c r="M32" s="1" t="inlineStr">
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:instrument.schema:manufacturer.schema:Organization.schema:name | .schema:instrument.schema:model.schema:name</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>match. CDIF instrument has manufacturer, and model</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>The mass analyzer system; input is from the interface cone, separating the high (atmospheric)  pressure part of the system from the low pressure (near vacuum) part of the sytem.</t>
+        </is>
+      </c>
+      <c r="O32" s="9" t="n"/>
+      <c r="P32" s="1" t="inlineStr">
         <is>
           <t>Thermo Fisher Scientific Element XR (SF-ICP-MS)</t>
         </is>
       </c>
-      <c r="N32" s="1" t="inlineStr">
+      <c r="Q32" s="1" t="inlineStr">
         <is>
           <t>Thermo Fisher Scientific Element XR (SF-ICP-MS)</t>
         </is>
       </c>
-      <c r="O32" s="1" t="inlineStr">
+      <c r="R32" s="1" t="inlineStr">
         <is>
           <t>Thermo Fisher Scientific Element XR (SF-ICP-MS)</t>
         </is>
       </c>
-      <c r="P32" s="1" t="inlineStr">
+      <c r="S32" s="1" t="inlineStr">
         <is>
           <t>Thermo Fisher Scientific Element XR (SF-ICP-MS)</t>
         </is>
       </c>
-      <c r="Q32" s="1" t="inlineStr">
+      <c r="T32" s="1" t="inlineStr">
         <is>
           <t>Thermo Fisher Scientific Element XR (SF-ICP-MS)</t>
         </is>
       </c>
-      <c r="R32" s="1" t="inlineStr">
+      <c r="U32" s="1" t="inlineStr">
         <is>
           <t>Thermo Scientific X-series 2 (Q-ICP-MS)</t>
         </is>
       </c>
-      <c r="S32" s="1" t="inlineStr">
+      <c r="V32" s="1" t="inlineStr">
         <is>
           <t>Thermo Fisher Scientific Element XR (SF-ICP-MS)</t>
         </is>
       </c>
-      <c r="T32" s="1" t="inlineStr">
+      <c r="W32" s="1" t="inlineStr">
         <is>
           <t>Thermo Fisher Scientific Element XR (SF-ICP-MS)</t>
         </is>
       </c>
-      <c r="U32" s="1" t="inlineStr">
+      <c r="X32" s="1" t="inlineStr">
         <is>
           <t>Agilent 8900 (Q-ICP-MS; ICP-MS/MS capable)</t>
         </is>
       </c>
-      <c r="V32" s="1" t="inlineStr">
+      <c r="Y32" s="1" t="inlineStr">
         <is>
           <t>Agilent 7900 (Q-ICP-MS)</t>
         </is>
       </c>
-      <c r="W32" s="1" t="inlineStr">
+      <c r="Z32" s="1" t="inlineStr">
         <is>
           <t>Agilent 7900 (Q-ICP-MS)</t>
         </is>
       </c>
-      <c r="X32" s="1" t="inlineStr">
+      <c r="AA32" s="1" t="inlineStr">
         <is>
           <t>Agilent 7500ce ICP-MS [P4]</t>
         </is>
       </c>
-      <c r="Y32" s="1" t="inlineStr">
+      <c r="AB32" s="1" t="inlineStr">
         <is>
           <t>Agilent 7500ce ICP-MS [P4]</t>
         </is>
@@ -3947,68 +4238,83 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L33" s="9" t="n"/>
-      <c r="M33" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N33" s="1" t="inlineStr">
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:instrument[additionalType='ICP Mass Spectrometer system']</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>match. Electron source/gun modelled as a sub-component of the instrument via schema:hasPart[]; classify the part via schema:additionalType (e.g. 'ElectronGun:FEG') and carry the label in schema:name.</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>property:icpMsType dataType: string readOnly: True enum {Single-collector quadrupole (Q-ICP-MS) | Single-collector sector-field (SF-ICP-MS) | Multi-collector sector-field (MC-ICP-MS) | Time-of-flight (ICP-ToF-MS) | Triple quadrupole (ICP-MS/MS)}</t>
+        </is>
+      </c>
+      <c r="O33" s="9" t="n"/>
+      <c r="P33" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q33" s="1" t="inlineStr">
         <is>
           <t>Double-focusing sector field ICP-MS (explicitly stated: "Thermo Scientific Element XR double-focusing sector field ICP-MS unit")</t>
         </is>
       </c>
-      <c r="O33" s="1" t="inlineStr">
+      <c r="R33" s="1" t="inlineStr">
         <is>
           <t>Double-focusing sector field ICP-MS (explicitly stated)</t>
         </is>
       </c>
-      <c r="P33" s="1" t="inlineStr">
+      <c r="S33" s="1" t="inlineStr">
         <is>
           <t>Double-focusing sector field ICP-MS (explicitly stated)</t>
         </is>
       </c>
-      <c r="Q33" s="1" t="inlineStr">
+      <c r="T33" s="1" t="inlineStr">
         <is>
           <t>Single-collector sector-field (SF-ICP-MS)</t>
         </is>
       </c>
-      <c r="R33" s="1" t="inlineStr">
+      <c r="U33" s="1" t="inlineStr">
         <is>
           <t>Single-collector quadrupole (Q-ICP-MS)</t>
         </is>
       </c>
-      <c r="S33" s="1" t="inlineStr">
+      <c r="V33" s="1" t="inlineStr">
         <is>
           <t>Sector field (SF-ICP-MS) (explicitly stated: "sector field inductively coupled plasma mass spectrometer")</t>
         </is>
       </c>
-      <c r="T33" s="1" t="inlineStr">
+      <c r="W33" s="1" t="inlineStr">
         <is>
           <t>Sector field (SF-ICP-MS) (explicitly stated)</t>
         </is>
       </c>
-      <c r="U33" s="1" t="inlineStr">
+      <c r="X33" s="1" t="inlineStr">
         <is>
           <t>N (ICP-MS type not stated; Agilent 8900 model named but "quadrupole" or "ICP-MS/MS" not used in paper)</t>
         </is>
       </c>
-      <c r="V33" s="1" t="inlineStr">
+      <c r="Y33" s="1" t="inlineStr">
         <is>
           <t>N (ICP-MS type not stated; Agilent 7900 model named but "quadrupole" not explicitly stated)</t>
         </is>
       </c>
-      <c r="W33" s="1" t="inlineStr">
+      <c r="Z33" s="1" t="inlineStr">
         <is>
           <t>N (ICP-MS type not stated)</t>
         </is>
       </c>
-      <c r="X33" s="1" t="inlineStr">
+      <c r="AA33" s="1" t="inlineStr">
         <is>
           <t>N (quadrupole implied by Agilent 7500ce model; not explicitly stated in paper) [P4]</t>
         </is>
       </c>
-      <c r="Y33" s="1" t="inlineStr">
+      <c r="AB33" s="1" t="inlineStr">
         <is>
           <t>N (same as silicate protocol) [P4]</t>
         </is>
@@ -4066,68 +4372,78 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L34" s="9" t="n"/>
-      <c r="M34" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N34" s="1" t="inlineStr">
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType = 'Interface Cone'</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>property:interfaceConeConfiguration dataType: string readOnly: True</t>
+        </is>
+      </c>
+      <c r="O34" s="9" t="n"/>
+      <c r="P34" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q34" s="1" t="inlineStr">
         <is>
           <t>Al standard sample cone (1.1 mm aperture); Al H-type skimmer (0.8 mm aperture)</t>
         </is>
       </c>
-      <c r="O34" s="1" t="inlineStr">
+      <c r="R34" s="1" t="inlineStr">
         <is>
           <t>Al standard sample cone (1.1 mm aperture); Al H-type skimmer (0.8 mm aperture)</t>
         </is>
       </c>
-      <c r="P34" s="1" t="inlineStr">
+      <c r="S34" s="1" t="inlineStr">
         <is>
           <t>Al standard sample cone (1.1 mm aperture); Al H-type skimmer (0.8 mm aperture)</t>
         </is>
       </c>
-      <c r="Q34" s="1" t="inlineStr">
+      <c r="T34" s="1" t="inlineStr">
         <is>
           <t>N (parameters lost)</t>
         </is>
       </c>
-      <c r="R34" s="1" t="inlineStr">
+      <c r="U34" s="1" t="inlineStr">
         <is>
           <t>Ni micro-skimmer cone Xs; Ni sampler cone</t>
         </is>
       </c>
-      <c r="S34" s="1" t="inlineStr">
+      <c r="V34" s="1" t="inlineStr">
         <is>
           <t>Ni sampler cone; Ni skimmer cone</t>
         </is>
       </c>
-      <c r="T34" s="1" t="inlineStr">
+      <c r="W34" s="1" t="inlineStr">
         <is>
           <t>Ni sampler cone; Ni skimmer cone</t>
         </is>
       </c>
-      <c r="U34" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V34" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="W34" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="X34" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
       <c r="Y34" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z34" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA34" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB34" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -4185,10 +4501,12 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L35" s="9" t="n"/>
-      <c r="M35" s="1" t="n"/>
-      <c r="N35" s="1" t="n"/>
-      <c r="O35" s="1" t="n"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>parameter:samplerAndSkimmerConeMaterial dataType: string readOnly: True</t>
+        </is>
+      </c>
+      <c r="O35" s="9" t="n"/>
       <c r="P35" s="1" t="n"/>
       <c r="Q35" s="1" t="n"/>
       <c r="R35" s="1" t="n"/>
@@ -4199,6 +4517,9 @@
       <c r="W35" s="1" t="n"/>
       <c r="X35" s="1" t="n"/>
       <c r="Y35" s="1" t="n"/>
+      <c r="Z35" s="1" t="n"/>
+      <c r="AA35" s="1" t="n"/>
+      <c r="AB35" s="1" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -4252,10 +4573,12 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L36" s="9" t="n"/>
-      <c r="M36" s="1" t="n"/>
-      <c r="N36" s="1" t="n"/>
-      <c r="O36" s="1" t="n"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>parameter:torchDepth dataType: string readOnly: True</t>
+        </is>
+      </c>
+      <c r="O36" s="9" t="n"/>
       <c r="P36" s="1" t="n"/>
       <c r="Q36" s="1" t="n"/>
       <c r="R36" s="1" t="n"/>
@@ -4266,6 +4589,9 @@
       <c r="W36" s="1" t="n"/>
       <c r="X36" s="1" t="n"/>
       <c r="Y36" s="1" t="n"/>
+      <c r="Z36" s="1" t="n"/>
+      <c r="AA36" s="1" t="n"/>
+      <c r="AB36" s="1" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -4315,22 +4641,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L37" s="9" t="n"/>
-      <c r="M37" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N37" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O37" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$MethodDefinition.schema:actionProcess.schema:step[][schema:name='dataAquisition'].schema:additionalProperty.schema:name </t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>property:guardElectrode dataType: string readOnly: True enum {On | Off | Not applicable (instrument does not have guard electrode)}</t>
+        </is>
+      </c>
+      <c r="O37" s="9" t="n"/>
       <c r="P37" s="1" t="inlineStr">
         <is>
           <t>N</t>
@@ -4348,35 +4669,50 @@
       </c>
       <c r="S37" s="1" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T37" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U37" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V37" s="1" t="inlineStr">
+        <is>
           <t>On (active)</t>
         </is>
       </c>
-      <c r="T37" s="1" t="inlineStr">
+      <c r="W37" s="1" t="inlineStr">
         <is>
           <t>On (active)</t>
         </is>
       </c>
-      <c r="U37" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V37" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="W37" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="X37" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
       <c r="Y37" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z37" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA37" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB37" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -4438,68 +4774,78 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L38" s="9" t="n"/>
-      <c r="M38" s="1" t="inlineStr">
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType = 'Mass Spectrometer'</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>property:massResolutionSettingDefault dataType: string readOnly: False</t>
+        </is>
+      </c>
+      <c r="O38" s="9" t="n"/>
+      <c r="P38" s="1" t="inlineStr">
         <is>
           <t>Low resolution (M/ΔM ≈ 400)</t>
         </is>
       </c>
-      <c r="N38" s="1" t="inlineStr">
+      <c r="Q38" s="1" t="inlineStr">
         <is>
           <t>Low resolution (M/ΔM = 300; cool plasma mapping)</t>
         </is>
       </c>
-      <c r="O38" s="1" t="inlineStr">
+      <c r="R38" s="1" t="inlineStr">
         <is>
           <t>Run 1: Medium resolution (M/ΔM = 4000) for major elements; Run 2: Low resolution (M/ΔM = 300) for trace elements</t>
         </is>
       </c>
-      <c r="P38" s="1" t="inlineStr">
+      <c r="S38" s="1" t="inlineStr">
         <is>
           <t>Low resolution (M/ΔM = 300)</t>
         </is>
       </c>
-      <c r="Q38" s="1" t="inlineStr">
+      <c r="T38" s="1" t="inlineStr">
         <is>
           <t>Medium resolution (m/Δm ≈ 4000)</t>
         </is>
       </c>
-      <c r="R38" s="1" t="inlineStr">
+      <c r="U38" s="1" t="inlineStr">
         <is>
           <t>Unit resolution (quadrupole fixed)</t>
         </is>
       </c>
-      <c r="S38" s="1" t="inlineStr">
+      <c r="V38" s="1" t="inlineStr">
         <is>
           <t>Low resolution (M/ΔM = 300)</t>
         </is>
       </c>
-      <c r="T38" s="1" t="inlineStr">
+      <c r="W38" s="1" t="inlineStr">
         <is>
           <t>Low resolution (M/ΔM = 300)</t>
         </is>
       </c>
-      <c r="U38" s="1" t="inlineStr">
+      <c r="X38" s="1" t="inlineStr">
         <is>
           <t>Unit resolution (quadrupole; ICP-MS/MS mode not specified)</t>
         </is>
       </c>
-      <c r="V38" s="1" t="inlineStr">
+      <c r="Y38" s="1" t="inlineStr">
         <is>
           <t>Unit resolution (quadrupole fixed)</t>
         </is>
       </c>
-      <c r="W38" s="1" t="inlineStr">
+      <c r="Z38" s="1" t="inlineStr">
         <is>
           <t>Unit resolution (quadrupole fixed)</t>
         </is>
       </c>
-      <c r="X38" s="1" t="inlineStr">
+      <c r="AA38" s="1" t="inlineStr">
         <is>
           <t>N (unit resolution implied for quadrupole; not explicitly stated) [P4]</t>
         </is>
       </c>
-      <c r="Y38" s="1" t="inlineStr">
+      <c r="AB38" s="1" t="inlineStr">
         <is>
           <t>N (same as silicate protocol) [P4]</t>
         </is>
@@ -4553,68 +4899,78 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L39" s="9" t="n"/>
-      <c r="M39" s="1" t="inlineStr">
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType = 'Detector'</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>property:detectorConfiguration dataType: string readOnly: True</t>
+        </is>
+      </c>
+      <c r="O39" s="9" t="n"/>
+      <c r="P39" s="1" t="inlineStr">
         <is>
           <t>Triple mode detection (pulse counting + analog + Faraday) at 65% duty cycle</t>
         </is>
       </c>
-      <c r="N39" s="1" t="inlineStr">
+      <c r="Q39" s="1" t="inlineStr">
         <is>
           <t>Triple mode detection (all analytical modes)</t>
         </is>
       </c>
-      <c r="O39" s="1" t="inlineStr">
+      <c r="R39" s="1" t="inlineStr">
         <is>
           <t>Triple mode detection; Faraday used for major elements in run 1</t>
         </is>
       </c>
-      <c r="P39" s="1" t="inlineStr">
+      <c r="S39" s="1" t="inlineStr">
         <is>
           <t>Triple mode detection</t>
         </is>
       </c>
-      <c r="Q39" s="1" t="inlineStr">
+      <c r="T39" s="1" t="inlineStr">
         <is>
           <t>N (parameters lost)</t>
         </is>
       </c>
-      <c r="R39" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="S39" s="1" t="inlineStr">
+      <c r="U39" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V39" s="1" t="inlineStr">
         <is>
           <t>Triple mode detector (pulse counting, analog, Faraday)</t>
         </is>
       </c>
-      <c r="T39" s="1" t="inlineStr">
+      <c r="W39" s="1" t="inlineStr">
         <is>
           <t>Triple mode detector (pulse counting, analog, Faraday)</t>
         </is>
       </c>
-      <c r="U39" s="1" t="inlineStr">
+      <c r="X39" s="1" t="inlineStr">
         <is>
           <t>Dual mode detector (30 ms / 10 ms dwell alternation)</t>
         </is>
       </c>
-      <c r="V39" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="W39" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="X39" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="Y39" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z39" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA39" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB39" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -4672,68 +5028,83 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L40" s="9" t="n"/>
-      <c r="M40" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N40" s="1" t="inlineStr">
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:instrument.schema:manufacturer.schema:Organization.schema:name | .schema:instrument.schema:model.schema:name</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>match. CDIF instrument has manufacturer, and model</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>property:laserWavelengthAndType dataType: string readOnly: True</t>
+        </is>
+      </c>
+      <c r="O40" s="9" t="n"/>
+      <c r="P40" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q40" s="1" t="inlineStr">
         <is>
           <t>193 nm ArF excimer; pulse duration ~5 ns</t>
         </is>
       </c>
-      <c r="O40" s="1" t="inlineStr">
+      <c r="R40" s="1" t="inlineStr">
         <is>
           <t>193 nm ArF excimer; pulse duration ~5 ns</t>
         </is>
       </c>
-      <c r="P40" s="1" t="inlineStr">
+      <c r="S40" s="1" t="inlineStr">
         <is>
           <t>193 nm ArF excimer; pulse duration ~5 ns</t>
         </is>
       </c>
-      <c r="Q40" s="1" t="inlineStr">
+      <c r="T40" s="1" t="inlineStr">
         <is>
           <t>193 nm solid-state (New Wave UP-193)</t>
         </is>
       </c>
-      <c r="R40" s="1" t="inlineStr">
+      <c r="U40" s="1" t="inlineStr">
         <is>
           <t>260 nm Ti:sapphire femtosecond UV; pulse duration ~220 fs (IFRIT system)</t>
         </is>
       </c>
-      <c r="S40" s="1" t="inlineStr">
+      <c r="V40" s="1" t="inlineStr">
         <is>
           <t>193 nm ArF excimer; pulse duration 4 ns</t>
         </is>
       </c>
-      <c r="T40" s="1" t="inlineStr">
+      <c r="W40" s="1" t="inlineStr">
         <is>
           <t>193 nm ArF excimer; pulse duration 4 ns</t>
         </is>
       </c>
-      <c r="U40" s="1" t="inlineStr">
+      <c r="X40" s="1" t="inlineStr">
         <is>
           <t>343 nm fs (GenesisGEO high-repetition-rate femtosecond laser)</t>
         </is>
       </c>
-      <c r="V40" s="1" t="inlineStr">
+      <c r="Y40" s="1" t="inlineStr">
         <is>
           <t>193 nm (CetacAnalyte HE; ns pulse)</t>
         </is>
       </c>
-      <c r="W40" s="1" t="inlineStr">
+      <c r="Z40" s="1" t="inlineStr">
         <is>
           <t>193 nm (CetacAnalyte HE; ns pulse)</t>
         </is>
       </c>
-      <c r="X40" s="1" t="inlineStr">
+      <c r="AA40" s="1" t="inlineStr">
         <is>
           <t>193 nm Excimer (ArF excimer) [P4]</t>
         </is>
       </c>
-      <c r="Y40" s="1" t="inlineStr">
+      <c r="AB40" s="1" t="inlineStr">
         <is>
           <t>193 nm Excimer (ArF excimer) [P4]</t>
         </is>
@@ -4787,22 +5158,22 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L41" s="9" t="n"/>
-      <c r="M41" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N41" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O41" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.bios:computationalTool[]</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>match. bios:computationalTool[] with ada:toolRole='acquisition' captures the acquisition/automation software; schema:name, schema:version, and schema:url are siblings.</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>toolRole = acquisition</t>
+        </is>
+      </c>
+      <c r="O41" s="9" t="n"/>
       <c r="P41" s="1" t="inlineStr">
         <is>
           <t>N</t>
@@ -4849,6 +5220,21 @@
         </is>
       </c>
       <c r="Y41" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z41" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA41" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB41" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -4906,68 +5292,83 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L42" s="9" t="n"/>
-      <c r="M42" s="1" t="inlineStr">
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.bios:computationalTool[]</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>match. Same container as row 20 with ada:toolRole='reduction' for matrix-correction/data-reduction software.</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>toolRole = data reduction</t>
+        </is>
+      </c>
+      <c r="O42" s="9" t="n"/>
+      <c r="P42" s="1" t="inlineStr">
         <is>
           <t>N (paper only states "standardization techniques followed those of Humayun (2012)"; no software named)</t>
         </is>
       </c>
-      <c r="N42" s="1" t="inlineStr">
+      <c r="Q42" s="1" t="inlineStr">
         <is>
           <t>In-house MatLab script (Appendix C1)</t>
         </is>
       </c>
-      <c r="O42" s="1" t="inlineStr">
+      <c r="R42" s="1" t="inlineStr">
         <is>
           <t>In-house MatLab script (Appendix C2)</t>
         </is>
       </c>
-      <c r="P42" s="1" t="inlineStr">
+      <c r="S42" s="1" t="inlineStr">
         <is>
           <t>In-house MatLab script (Appendix C3)</t>
         </is>
       </c>
-      <c r="Q42" s="1" t="inlineStr">
+      <c r="T42" s="1" t="inlineStr">
         <is>
           <t>Excel spreadsheets developed by C.-T. A. Lee (Rice University)</t>
         </is>
       </c>
-      <c r="R42" s="1" t="inlineStr">
+      <c r="U42" s="1" t="inlineStr">
         <is>
           <t>N (in-house reduction implied)</t>
         </is>
       </c>
-      <c r="S42" s="1" t="inlineStr">
+      <c r="V42" s="1" t="inlineStr">
         <is>
           <t>iolite 4.5.7 with 3D Trace Elements DRS</t>
         </is>
       </c>
-      <c r="T42" s="1" t="inlineStr">
+      <c r="W42" s="1" t="inlineStr">
         <is>
           <t>iolite 4.5.7 with 3D Trace Elements DRS</t>
         </is>
       </c>
-      <c r="U42" s="1" t="inlineStr">
+      <c r="X42" s="1" t="inlineStr">
         <is>
           <t>Iolite 4 (Paton et al. 2011)</t>
         </is>
       </c>
-      <c r="V42" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="W42" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="X42" s="1" t="inlineStr">
+      <c r="Y42" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z42" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA42" s="1" t="inlineStr">
         <is>
           <t>AMS ver. 1.0 (Mutchler et al. 2008; Analysis Management System, stand-alone software) [P4]</t>
         </is>
       </c>
-      <c r="Y42" s="1" t="inlineStr">
+      <c r="AB42" s="1" t="inlineStr">
         <is>
           <t>AMS ver. 1.0 (Mutchler et al. 2008) [P4]</t>
         </is>
@@ -5025,68 +5426,78 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L43" s="9" t="n"/>
-      <c r="M43" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N43" s="1" t="inlineStr">
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType = 'Ablation Cell'</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>parameter:ablationCellType dataType: string readOnly: True</t>
+        </is>
+      </c>
+      <c r="O43" s="9" t="n"/>
+      <c r="P43" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q43" s="1" t="inlineStr">
         <is>
           <t>HELEX II two-volume ablation cell</t>
         </is>
       </c>
-      <c r="O43" s="1" t="inlineStr">
+      <c r="R43" s="1" t="inlineStr">
         <is>
           <t>HELEX II two-volume ablation cell</t>
         </is>
       </c>
-      <c r="P43" s="1" t="inlineStr">
+      <c r="S43" s="1" t="inlineStr">
         <is>
           <t>HELEX II two-volume ablation cell</t>
         </is>
       </c>
-      <c r="Q43" s="1" t="inlineStr">
+      <c r="T43" s="1" t="inlineStr">
         <is>
           <t>N (standard cell; parameters lost)</t>
         </is>
       </c>
-      <c r="R43" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="S43" s="1" t="inlineStr">
+      <c r="U43" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V43" s="1" t="inlineStr">
         <is>
           <t>HelEx II two-volume sample cell</t>
         </is>
       </c>
-      <c r="T43" s="1" t="inlineStr">
+      <c r="W43" s="1" t="inlineStr">
         <is>
           <t>HelEx II two-volume sample cell</t>
         </is>
       </c>
-      <c r="U43" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V43" s="1" t="inlineStr">
+      <c r="X43" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y43" s="1" t="inlineStr">
         <is>
           <t>Cetac Analyte HE system (stated as the laser ablation system coupled to Agilent 7900)</t>
         </is>
       </c>
-      <c r="W43" s="1" t="inlineStr">
+      <c r="Z43" s="1" t="inlineStr">
         <is>
           <t>Cetac Analyte HE system (same as silicate glass protocol)</t>
         </is>
       </c>
-      <c r="X43" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Y43" s="1" t="inlineStr">
+      <c r="AA43" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB43" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -5109,9 +5520,6 @@
       <c r="I45" s="5" t="n"/>
       <c r="J45" s="5" t="n"/>
       <c r="K45" s="5" t="n"/>
-      <c r="L45" s="5" t="n"/>
-      <c r="M45" s="5" t="n"/>
-      <c r="N45" s="5" t="n"/>
       <c r="O45" s="5" t="n"/>
       <c r="P45" s="5" t="n"/>
       <c r="Q45" s="5" t="n"/>
@@ -5121,12 +5529,15 @@
       <c r="U45" s="5" t="n"/>
       <c r="V45" s="5" t="n"/>
       <c r="W45" s="5" t="n"/>
-      <c r="X45" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Y45" s="5" t="inlineStr">
+      <c r="X45" s="5" t="n"/>
+      <c r="Y45" s="5" t="n"/>
+      <c r="Z45" s="5" t="n"/>
+      <c r="AA45" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB45" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -5184,14 +5595,16 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L46" s="9" t="inlineStr">
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>property:analyticalMode dataType: string readOnly: True enum {Spot | Transect | Mapping | Spot; Transect}</t>
+        </is>
+      </c>
+      <c r="O46" s="9" t="inlineStr">
         <is>
           <t>Literature Assessment</t>
         </is>
       </c>
-      <c r="M46" s="1" t="n"/>
-      <c r="N46" s="1" t="n"/>
-      <c r="O46" s="1" t="n"/>
       <c r="P46" s="1" t="n"/>
       <c r="Q46" s="1" t="n"/>
       <c r="R46" s="1" t="n"/>
@@ -5202,6 +5615,9 @@
       <c r="W46" s="1" t="n"/>
       <c r="X46" s="1" t="n"/>
       <c r="Y46" s="1" t="n"/>
+      <c r="Z46" s="1" t="n"/>
+      <c r="AA46" s="1" t="n"/>
+      <c r="AB46" s="1" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -5255,68 +5671,80 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L47" s="9" t="n"/>
-      <c r="M47" s="1" t="inlineStr">
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:spotGeometry</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>property:spotGeometryDefault
+  dataType: schema:propertyValueSpecification
+  readOnly: False</t>
+        </is>
+      </c>
+      <c r="O47" s="9" t="n"/>
+      <c r="P47" s="1" t="inlineStr">
         <is>
           <t>Raster: 50 µm circular beam spot; Spot (Ge): 150 µm circular</t>
         </is>
       </c>
-      <c r="N47" s="1" t="inlineStr">
+      <c r="Q47" s="1" t="inlineStr">
         <is>
           <t>20×20 µm square</t>
         </is>
       </c>
-      <c r="O47" s="1" t="inlineStr">
+      <c r="R47" s="1" t="inlineStr">
         <is>
           <t>Run 1 (major): 30 µm circular; Run 2 (trace): 130 µm circular</t>
         </is>
       </c>
-      <c r="P47" s="1" t="inlineStr">
+      <c r="S47" s="1" t="inlineStr">
         <is>
           <t>110 µm circular (spot mode)</t>
         </is>
       </c>
-      <c r="Q47" s="1" t="inlineStr">
+      <c r="T47" s="1" t="inlineStr">
         <is>
           <t>75 µm circular</t>
         </is>
       </c>
-      <c r="R47" s="1" t="inlineStr">
+      <c r="U47" s="1" t="inlineStr">
         <is>
           <t>30 µm circular</t>
         </is>
       </c>
-      <c r="S47" s="1" t="inlineStr">
+      <c r="V47" s="1" t="inlineStr">
         <is>
           <t>150 µm circular</t>
         </is>
       </c>
-      <c r="T47" s="1" t="inlineStr">
+      <c r="W47" s="1" t="inlineStr">
         <is>
           <t>150 µm square (mapping mode)</t>
         </is>
       </c>
-      <c r="U47" s="1" t="inlineStr">
+      <c r="X47" s="1" t="inlineStr">
         <is>
           <t>100×100 µm square (stated as 100 µm diameter spot at 1 Hz)</t>
         </is>
       </c>
-      <c r="V47" s="1" t="inlineStr">
+      <c r="Y47" s="1" t="inlineStr">
         <is>
           <t>40 µm circular (silicate glass)</t>
         </is>
       </c>
-      <c r="W47" s="1" t="inlineStr">
+      <c r="Z47" s="1" t="inlineStr">
         <is>
           <t>20 µm circular (sulfide; grain sizes &gt;20 µm selected)</t>
         </is>
       </c>
-      <c r="X47" s="1" t="inlineStr">
+      <c r="AA47" s="1" t="inlineStr">
         <is>
           <t>24 and 32 µm diameter (commonly used for silicates and glass); 90 µm (some olivine analyses to evaluate low REE signal sampling) [P4]</t>
         </is>
       </c>
-      <c r="Y47" s="1" t="inlineStr">
+      <c r="AB47" s="1" t="inlineStr">
         <is>
           <t>~24 µm diameter [P4]</t>
         </is>
@@ -5374,68 +5802,83 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L48" s="9" t="n"/>
-      <c r="M48" s="1" t="inlineStr">
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:spotPath, ada:ablationMode</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>property:spotPath
+  dataType: schema:propertyValue 
+  readOnly: True
+property:ablationMode
+  dataType: schema:propertyValue 
+  readOnly: True</t>
+        </is>
+      </c>
+      <c r="O48" s="9" t="n"/>
+      <c r="P48" s="1" t="inlineStr">
         <is>
           <t>Raster area (2D mapping) for most irons; Spot (stationary) for Ge analysis on 5 irons</t>
         </is>
       </c>
-      <c r="N48" s="1" t="inlineStr">
+      <c r="Q48" s="1" t="inlineStr">
         <is>
           <t>Raster area (2D elemental mapping)</t>
         </is>
       </c>
-      <c r="O48" s="1" t="inlineStr">
+      <c r="R48" s="1" t="inlineStr">
         <is>
           <t>Transect (line scan, run 1) + Spot (run 2 on same location after pre-ablation)</t>
         </is>
       </c>
-      <c r="P48" s="1" t="inlineStr">
+      <c r="S48" s="1" t="inlineStr">
         <is>
           <t>Spot (stationary)</t>
         </is>
       </c>
-      <c r="Q48" s="1" t="inlineStr">
+      <c r="T48" s="1" t="inlineStr">
         <is>
           <t>Spot (stationary)</t>
         </is>
       </c>
-      <c r="R48" s="1" t="inlineStr">
+      <c r="U48" s="1" t="inlineStr">
         <is>
           <t>Spot (stationary)</t>
         </is>
       </c>
-      <c r="S48" s="1" t="inlineStr">
+      <c r="V48" s="1" t="inlineStr">
         <is>
           <t>Spot (stationary)</t>
         </is>
       </c>
-      <c r="T48" s="1" t="inlineStr">
+      <c r="W48" s="1" t="inlineStr">
         <is>
           <t>Raster area (2D elemental mapping)</t>
         </is>
       </c>
-      <c r="U48" s="1" t="inlineStr">
+      <c r="X48" s="1" t="inlineStr">
         <is>
           <t>Spot (stationary; single spot at 1 Hz)</t>
         </is>
       </c>
-      <c r="V48" s="1" t="inlineStr">
+      <c r="Y48" s="1" t="inlineStr">
         <is>
           <t>N (ablation mode not explicitly stated; "beam diameter" terminology used but "spot" or "spot mode" not written)</t>
         </is>
       </c>
-      <c r="W48" s="1" t="inlineStr">
+      <c r="Z48" s="1" t="inlineStr">
         <is>
           <t>N (ablation mode not explicitly stated)</t>
         </is>
       </c>
-      <c r="X48" s="1" t="inlineStr">
+      <c r="AA48" s="1" t="inlineStr">
         <is>
           <t>Spot (stationary) [P4]</t>
         </is>
       </c>
-      <c r="Y48" s="1" t="inlineStr">
+      <c r="AB48" s="1" t="inlineStr">
         <is>
           <t>Spot (stationary) [P4]</t>
         </is>
@@ -5489,22 +5932,19 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L49" s="9" t="n"/>
-      <c r="M49" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N49" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O49" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>$.ada:methodParameters[]</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>parameter:laserEnergy
+  dataType: propertyValueSpecification
+  readOnly: False</t>
+        </is>
+      </c>
+      <c r="O49" s="9" t="n"/>
       <c r="P49" s="1" t="inlineStr">
         <is>
           <t>N</t>
@@ -5547,10 +5987,25 @@
       </c>
       <c r="X49" s="1" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y49" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z49" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA49" s="1" t="inlineStr">
+        <is>
           <t>150 mJ output energy [P4]</t>
         </is>
       </c>
-      <c r="Y49" s="1" t="inlineStr">
+      <c r="AB49" s="1" t="inlineStr">
         <is>
           <t>150 mJ output energy [P4]</t>
         </is>
@@ -5608,68 +6063,80 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L50" s="9" t="n"/>
-      <c r="M50" s="1" t="inlineStr">
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:laserFluence</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>property: laserFluenceDefault
+  readOnly: False
+  dataType: schema:propertyValueSpecification</t>
+        </is>
+      </c>
+      <c r="O50" s="9" t="n"/>
+      <c r="P50" s="1" t="inlineStr">
         <is>
           <t>N (no fluence reported; energy density characterized as "sufficient to resolve Ge from background argide")</t>
         </is>
       </c>
-      <c r="N50" s="1" t="inlineStr">
+      <c r="Q50" s="1" t="inlineStr">
         <is>
           <t>5–7 J cm⁻²</t>
         </is>
       </c>
-      <c r="O50" s="1" t="inlineStr">
+      <c r="R50" s="1" t="inlineStr">
         <is>
           <t>Run 1 (major): 4.72 J cm⁻²; Run 2 (trace): 4.72 J cm⁻²</t>
         </is>
       </c>
-      <c r="P50" s="1" t="inlineStr">
+      <c r="S50" s="1" t="inlineStr">
         <is>
           <t>3.5 J cm⁻²</t>
         </is>
       </c>
-      <c r="Q50" s="1" t="inlineStr">
+      <c r="T50" s="1" t="inlineStr">
         <is>
           <t>N (parameters lost)</t>
         </is>
       </c>
-      <c r="R50" s="1" t="inlineStr">
+      <c r="U50" s="1" t="inlineStr">
         <is>
           <t>12 J cm⁻²</t>
         </is>
       </c>
-      <c r="S50" s="1" t="inlineStr">
+      <c r="V50" s="1" t="inlineStr">
         <is>
           <t>7 J cm⁻²</t>
         </is>
       </c>
-      <c r="T50" s="1" t="inlineStr">
+      <c r="W50" s="1" t="inlineStr">
         <is>
           <t>7 J cm⁻²</t>
         </is>
       </c>
-      <c r="U50" s="1" t="inlineStr">
+      <c r="X50" s="1" t="inlineStr">
         <is>
           <t>6.79 J cm⁻²</t>
         </is>
       </c>
-      <c r="V50" s="1" t="inlineStr">
+      <c r="Y50" s="1" t="inlineStr">
         <is>
           <t>~2.5 J cm⁻² (stated as "energy of ~2.5 J/cm²")</t>
         </is>
       </c>
-      <c r="W50" s="1" t="inlineStr">
+      <c r="Z50" s="1" t="inlineStr">
         <is>
           <t>~2.5 J cm⁻²</t>
         </is>
       </c>
-      <c r="X50" s="1" t="inlineStr">
+      <c r="AA50" s="1" t="inlineStr">
         <is>
           <t>7–10 J/m² (stated in paper; units as written; likely a typographic error for J/cm²) [P4]</t>
         </is>
       </c>
-      <c r="Y50" s="1" t="inlineStr">
+      <c r="AB50" s="1" t="inlineStr">
         <is>
           <t>7–10 J/m² (same as silicate protocol) [P4]</t>
         </is>
@@ -5727,22 +6194,19 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L51" s="9" t="n"/>
-      <c r="M51" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N51" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O51" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>$.ada:methodParameters[]</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>parameter: LaserBeamEnergyProfile
+  dataType: schema:propertyValueSpecification
+  readOnly: False</t>
+        </is>
+      </c>
+      <c r="O51" s="9" t="n"/>
       <c r="P51" s="1" t="inlineStr">
         <is>
           <t>N</t>
@@ -5789,6 +6253,21 @@
         </is>
       </c>
       <c r="Y51" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z51" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA51" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB51" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -5846,68 +6325,80 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L52" s="9" t="n"/>
-      <c r="M52" s="1" t="inlineStr">
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:laserRepetitionRate</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>property:  BeamDamageMinimization. 
+  dataType:  schema:propertyValueSpecification
+  readOnly: False</t>
+        </is>
+      </c>
+      <c r="O52" s="9" t="n"/>
+      <c r="P52" s="1" t="inlineStr">
         <is>
           <t>Raster: 50 Hz; Spot (Ge): 50 Hz</t>
         </is>
       </c>
-      <c r="N52" s="1" t="inlineStr">
+      <c r="Q52" s="1" t="inlineStr">
         <is>
           <t>20 Hz</t>
         </is>
       </c>
-      <c r="O52" s="1" t="inlineStr">
+      <c r="R52" s="1" t="inlineStr">
         <is>
           <t>Run 1 (major): 20 Hz; Run 2 (trace): 40 Hz</t>
         </is>
       </c>
-      <c r="P52" s="1" t="inlineStr">
+      <c r="S52" s="1" t="inlineStr">
         <is>
           <t>20 Hz</t>
         </is>
       </c>
-      <c r="Q52" s="1" t="inlineStr">
+      <c r="T52" s="1" t="inlineStr">
         <is>
           <t>N (parameters lost)</t>
         </is>
       </c>
-      <c r="R52" s="1" t="inlineStr">
+      <c r="U52" s="1" t="inlineStr">
         <is>
           <t>20 Hz</t>
         </is>
       </c>
-      <c r="S52" s="1" t="inlineStr">
+      <c r="V52" s="1" t="inlineStr">
         <is>
           <t>10 Hz</t>
         </is>
       </c>
-      <c r="T52" s="1" t="inlineStr">
+      <c r="W52" s="1" t="inlineStr">
         <is>
           <t>10 Hz</t>
         </is>
       </c>
-      <c r="U52" s="1" t="inlineStr">
+      <c r="X52" s="1" t="inlineStr">
         <is>
           <t>1 Hz</t>
         </is>
       </c>
-      <c r="V52" s="1" t="inlineStr">
+      <c r="Y52" s="1" t="inlineStr">
         <is>
           <t>7 Hz</t>
         </is>
       </c>
-      <c r="W52" s="1" t="inlineStr">
+      <c r="Z52" s="1" t="inlineStr">
         <is>
           <t>7 Hz</t>
         </is>
       </c>
-      <c r="X52" s="1" t="inlineStr">
+      <c r="AA52" s="1" t="inlineStr">
         <is>
           <t>5 Hz [P4]</t>
         </is>
       </c>
-      <c r="Y52" s="1" t="inlineStr">
+      <c r="AB52" s="1" t="inlineStr">
         <is>
           <t>5 Hz [P4]</t>
         </is>
@@ -5965,68 +6456,80 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L53" s="9" t="n"/>
-      <c r="M53" s="1" t="inlineStr">
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>$.ada:methodParameters[].schema:description</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>parameter: LaserPulseDuration
+  dataType:  schema:propertyValueSpecification
+  readOnly: True</t>
+        </is>
+      </c>
+      <c r="O53" s="9" t="n"/>
+      <c r="P53" s="1" t="inlineStr">
         <is>
           <t>N (UP193FX; ns solid-state; pulse duration not reported)</t>
         </is>
       </c>
-      <c r="N53" s="1" t="inlineStr">
+      <c r="Q53" s="1" t="inlineStr">
         <is>
           <t>~5 ns (ArF excimer)</t>
         </is>
       </c>
-      <c r="O53" s="1" t="inlineStr">
+      <c r="R53" s="1" t="inlineStr">
         <is>
           <t>~5 ns (ArF excimer)</t>
         </is>
       </c>
-      <c r="P53" s="1" t="inlineStr">
+      <c r="S53" s="1" t="inlineStr">
         <is>
           <t>~5 ns (ArF excimer)</t>
         </is>
       </c>
-      <c r="Q53" s="1" t="inlineStr">
+      <c r="T53" s="1" t="inlineStr">
         <is>
           <t>N (parameters lost)</t>
         </is>
       </c>
-      <c r="R53" s="1" t="inlineStr">
+      <c r="U53" s="1" t="inlineStr">
         <is>
           <t>~220 fs (Ti:sapphire IFRIT system)</t>
         </is>
       </c>
-      <c r="S53" s="1" t="inlineStr">
+      <c r="V53" s="1" t="inlineStr">
         <is>
           <t>4 ns (ArF excimer Excite 193)</t>
         </is>
       </c>
-      <c r="T53" s="1" t="inlineStr">
+      <c r="W53" s="1" t="inlineStr">
         <is>
           <t>4 ns (ArF excimer Excite 193)</t>
         </is>
       </c>
-      <c r="U53" s="1" t="inlineStr">
+      <c r="X53" s="1" t="inlineStr">
         <is>
           <t>Femtosecond (exact value not stated; GenesisGEO fs laser)</t>
         </is>
       </c>
-      <c r="V53" s="1" t="inlineStr">
+      <c r="Y53" s="1" t="inlineStr">
         <is>
           <t>N (ns; CetacAnalyte HE; pulse duration not reported)</t>
         </is>
       </c>
-      <c r="W53" s="1" t="inlineStr">
+      <c r="Z53" s="1" t="inlineStr">
         <is>
           <t>N (ns; CetacAnalyte HE)</t>
         </is>
       </c>
-      <c r="X53" s="1" t="inlineStr">
+      <c r="AA53" s="1" t="inlineStr">
         <is>
           <t>N (ns excimer system; pulse duration not stated) [P4]</t>
         </is>
       </c>
-      <c r="Y53" s="1" t="inlineStr">
+      <c r="AB53" s="1" t="inlineStr">
         <is>
           <t>N (same as silicate protocol) [P4]</t>
         </is>
@@ -6080,68 +6583,80 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L54" s="9" t="n"/>
-      <c r="M54" s="1" t="inlineStr">
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:ablationSpotDuration</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>property:  AblationSpotDuration. 
+  dataType:  schema:propertyValueSpecification
+  readOnly: False</t>
+        </is>
+      </c>
+      <c r="O54" s="9" t="n"/>
+      <c r="P54" s="1" t="inlineStr">
         <is>
           <t>N/A (raster) / 20 s (spot Ge at 50 Hz)</t>
         </is>
       </c>
-      <c r="N54" s="1" t="inlineStr">
+      <c r="Q54" s="1" t="inlineStr">
         <is>
           <t>N/A (mapping mode)</t>
         </is>
       </c>
-      <c r="O54" s="1" t="inlineStr">
+      <c r="R54" s="1" t="inlineStr">
         <is>
           <t>N/A (line scan run 1) / N/A (spot run 2 — duration set by 34 runs covering 400 µm + washout, not a fixed spot duration)</t>
         </is>
       </c>
-      <c r="P54" s="1" t="inlineStr">
+      <c r="S54" s="1" t="inlineStr">
         <is>
           <t>20 s spot ablation (plus 10 s washout); 25 cycles acquisition</t>
         </is>
       </c>
-      <c r="Q54" s="1" t="inlineStr">
+      <c r="T54" s="1" t="inlineStr">
         <is>
           <t>N (parameters lost)</t>
         </is>
       </c>
-      <c r="R54" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="S54" s="1" t="inlineStr">
+      <c r="U54" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V54" s="1" t="inlineStr">
         <is>
           <t>40 s on-sample ablation (after 20 s background measurement)</t>
         </is>
       </c>
-      <c r="T54" s="1" t="inlineStr">
+      <c r="W54" s="1" t="inlineStr">
         <is>
           <t>N/A (mapping mode)</t>
         </is>
       </c>
-      <c r="U54" s="1" t="inlineStr">
+      <c r="X54" s="1" t="inlineStr">
         <is>
           <t>45 s ablation (after 25 s gas blank; 25 s washout between analyses)</t>
         </is>
       </c>
-      <c r="V54" s="1" t="inlineStr">
+      <c r="Y54" s="1" t="inlineStr">
         <is>
           <t>~40 s (inferred from typical CetacAnalyte HE protocol for glass)</t>
         </is>
       </c>
-      <c r="W54" s="1" t="inlineStr">
+      <c r="Z54" s="1" t="inlineStr">
         <is>
           <t>~40 s (same protocol; grain size &gt;20 µm selected)</t>
         </is>
       </c>
-      <c r="X54" s="1" t="inlineStr">
+      <c r="AA54" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
       </c>
-      <c r="Y54" s="1" t="inlineStr">
+      <c r="AB54" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
@@ -6195,68 +6710,83 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L55" s="9" t="n"/>
-      <c r="M55" s="1" t="inlineStr">
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>$.ada:methodParameters[]</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>parameter: StageTranslationSpeed
+  dataType:  schema:propertyValueSpecification
+  readOnly: False
+parameter: StepSize
+  dataType:  schema:propertyValueSpecification
+  readOnly: False</t>
+        </is>
+      </c>
+      <c r="O55" s="9" t="n"/>
+      <c r="P55" s="1" t="inlineStr">
         <is>
           <t>10 µm s⁻¹ (raster scan); N/A (spot Ge)</t>
         </is>
       </c>
-      <c r="N55" s="1" t="inlineStr">
+      <c r="Q55" s="1" t="inlineStr">
         <is>
           <t>9 µm s⁻¹ (continuous raster)</t>
         </is>
       </c>
-      <c r="O55" s="1" t="inlineStr">
+      <c r="R55" s="1" t="inlineStr">
         <is>
           <t>10 µm s⁻¹ (line scan run 1); spot mode (run 2)</t>
         </is>
       </c>
-      <c r="P55" s="1" t="inlineStr">
+      <c r="S55" s="1" t="inlineStr">
         <is>
           <t>N/A (spot mode)</t>
         </is>
       </c>
-      <c r="Q55" s="1" t="inlineStr">
+      <c r="T55" s="1" t="inlineStr">
         <is>
           <t>N/A (spot mode)</t>
         </is>
       </c>
-      <c r="R55" s="1" t="inlineStr">
+      <c r="U55" s="1" t="inlineStr">
         <is>
           <t>N/A (spot mode)</t>
         </is>
       </c>
-      <c r="S55" s="1" t="inlineStr">
+      <c r="V55" s="1" t="inlineStr">
         <is>
           <t>N/A (spot mode)</t>
         </is>
       </c>
-      <c r="T55" s="1" t="inlineStr">
+      <c r="W55" s="1" t="inlineStr">
         <is>
           <t>10 µm s⁻¹ (continuous raster scan)</t>
         </is>
       </c>
-      <c r="U55" s="1" t="inlineStr">
+      <c r="X55" s="1" t="inlineStr">
         <is>
           <t>N/A (spot mode)</t>
         </is>
       </c>
-      <c r="V55" s="1" t="inlineStr">
+      <c r="Y55" s="1" t="inlineStr">
         <is>
           <t>N/A (spot mode)</t>
         </is>
       </c>
-      <c r="W55" s="1" t="inlineStr">
+      <c r="Z55" s="1" t="inlineStr">
         <is>
           <t>N/A (spot mode)</t>
         </is>
       </c>
-      <c r="X55" s="1" t="inlineStr">
+      <c r="AA55" s="1" t="inlineStr">
         <is>
           <t>N/A (spot analysis)</t>
         </is>
       </c>
-      <c r="Y55" s="1" t="inlineStr">
+      <c r="AB55" s="1" t="inlineStr">
         <is>
           <t>N/A (spot analysis)</t>
         </is>
@@ -6310,68 +6840,78 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L56" s="9" t="n"/>
-      <c r="M56" s="1" t="inlineStr">
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:rasterLineSpacing</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>property:rasterLineSpacingDefault dataType: string readOnly: False</t>
+        </is>
+      </c>
+      <c r="O56" s="9" t="n"/>
+      <c r="P56" s="1" t="inlineStr">
         <is>
           <t>N (line spacing not explicitly stated; 50 µm spot scanned at 10 µm s⁻¹)</t>
         </is>
       </c>
-      <c r="N56" s="1" t="inlineStr">
+      <c r="Q56" s="1" t="inlineStr">
         <is>
           <t>20 µm (contiguous; 20×20 µm square spot = line spacing equals spot width)</t>
         </is>
       </c>
-      <c r="O56" s="1" t="inlineStr">
+      <c r="R56" s="1" t="inlineStr">
         <is>
           <t>N/A (line scan + spot; not 2D mapping)</t>
         </is>
       </c>
-      <c r="P56" s="1" t="inlineStr">
+      <c r="S56" s="1" t="inlineStr">
         <is>
           <t>N/A (spot mode)</t>
         </is>
       </c>
-      <c r="Q56" s="1" t="inlineStr">
+      <c r="T56" s="1" t="inlineStr">
         <is>
           <t>N/A (spot mode)</t>
         </is>
       </c>
-      <c r="R56" s="1" t="inlineStr">
+      <c r="U56" s="1" t="inlineStr">
         <is>
           <t>N/A (spot mode)</t>
         </is>
       </c>
-      <c r="S56" s="1" t="inlineStr">
+      <c r="V56" s="1" t="inlineStr">
         <is>
           <t>N/A (spot mode)</t>
         </is>
       </c>
-      <c r="T56" s="1" t="inlineStr">
+      <c r="W56" s="1" t="inlineStr">
         <is>
           <t>N (line spacing not stated; 150 µm spot at 10 µm s⁻¹)</t>
         </is>
       </c>
-      <c r="U56" s="1" t="inlineStr">
+      <c r="X56" s="1" t="inlineStr">
         <is>
           <t>N/A (spot mode)</t>
         </is>
       </c>
-      <c r="V56" s="1" t="inlineStr">
+      <c r="Y56" s="1" t="inlineStr">
         <is>
           <t>N/A (spot mode)</t>
         </is>
       </c>
-      <c r="W56" s="1" t="inlineStr">
+      <c r="Z56" s="1" t="inlineStr">
         <is>
           <t>N/A (spot mode)</t>
         </is>
       </c>
-      <c r="X56" s="1" t="inlineStr">
+      <c r="AA56" s="1" t="inlineStr">
         <is>
           <t>N/A (spot analysis)</t>
         </is>
       </c>
-      <c r="Y56" s="1" t="inlineStr">
+      <c r="AB56" s="1" t="inlineStr">
         <is>
           <t>N/A (spot analysis)</t>
         </is>
@@ -6429,68 +6969,78 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L57" s="9" t="n"/>
-      <c r="M57" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N57" s="1" t="inlineStr">
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:carrierGas;  $MethodDefinition.ada:carrierGasFlowRate</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>property:carrierGasAndFlowRateDefault dataType: string readOnly: False</t>
+        </is>
+      </c>
+      <c r="O57" s="9" t="n"/>
+      <c r="P57" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q57" s="1" t="inlineStr">
         <is>
           <t>He: MFC-1 (cell) 0.200–0.260 l min⁻¹; MFC-2 (cup) 0.220–0.385 l min⁻¹</t>
         </is>
       </c>
-      <c r="O57" s="1" t="inlineStr">
+      <c r="R57" s="1" t="inlineStr">
         <is>
           <t>He: MFC-1 0.19 l min⁻¹; MFC-2 0.22 l min⁻¹</t>
         </is>
       </c>
-      <c r="P57" s="1" t="inlineStr">
+      <c r="S57" s="1" t="inlineStr">
         <is>
           <t>He: MFC-1 0.270 l min⁻¹; MFC-2 0.250 l min⁻¹</t>
         </is>
       </c>
-      <c r="Q57" s="1" t="inlineStr">
+      <c r="T57" s="1" t="inlineStr">
         <is>
           <t>N (parameters lost)</t>
         </is>
       </c>
-      <c r="R57" s="1" t="inlineStr">
+      <c r="U57" s="1" t="inlineStr">
         <is>
           <t>Carrier gas flow: 0.6 L/min; species not named (carrier gas identity not stated in Table 1 or text)</t>
         </is>
       </c>
-      <c r="S57" s="1" t="inlineStr">
+      <c r="V57" s="1" t="inlineStr">
         <is>
           <t>He: 0.6 l min⁻¹ (MFC 1) + 0.7 l min⁻¹ (MFC 2) in HelEx II cell; combined with Ar makeup via T-piece near torch</t>
         </is>
       </c>
-      <c r="T57" s="1" t="inlineStr">
+      <c r="W57" s="1" t="inlineStr">
         <is>
           <t>He: 0.6 l min⁻¹ (MFC 1) + 0.7 l min⁻¹ (MFC 2) in HelEx II cell</t>
         </is>
       </c>
-      <c r="U57" s="1" t="inlineStr">
+      <c r="X57" s="1" t="inlineStr">
         <is>
           <t>He: 0.7 l min⁻¹ (chamber) + 0.1 l min⁻¹ (cup gas)</t>
         </is>
       </c>
-      <c r="V57" s="1" t="inlineStr">
+      <c r="Y57" s="1" t="inlineStr">
         <is>
           <t>He (flow rate not stated; carrier gas with N₂ or Ar mixed for sensitivity optimization)</t>
         </is>
       </c>
-      <c r="W57" s="1" t="inlineStr">
+      <c r="Z57" s="1" t="inlineStr">
         <is>
           <t>He (flow rate not stated; same system as glass protocol)</t>
         </is>
       </c>
-      <c r="X57" s="1" t="inlineStr">
+      <c r="AA57" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
       </c>
-      <c r="Y57" s="1" t="inlineStr">
+      <c r="AB57" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
@@ -6548,68 +7098,81 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L58" s="9" t="n"/>
-      <c r="M58" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N58" s="1" t="inlineStr">
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>$.ada:methodParameters[]</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parameter: MakeUpGasAddition
+  dataType:  schema:propertyValueSpecification
+  readOnly: False
+</t>
+        </is>
+      </c>
+      <c r="O58" s="9" t="n"/>
+      <c r="P58" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q58" s="1" t="inlineStr">
         <is>
           <t>Ar make-up: 0.81–0.99 l min⁻¹ (mapping); N₂ explicitly not added</t>
         </is>
       </c>
-      <c r="O58" s="1" t="inlineStr">
+      <c r="R58" s="1" t="inlineStr">
         <is>
           <t>Ar make-up: 0.947 l min⁻¹ (run 1 and run 2); N₂ not added</t>
         </is>
       </c>
-      <c r="P58" s="1" t="inlineStr">
+      <c r="S58" s="1" t="inlineStr">
         <is>
           <t>Ar make-up: 0.96 l min⁻¹; N₂ not added</t>
         </is>
       </c>
-      <c r="Q58" s="1" t="inlineStr">
+      <c r="T58" s="1" t="inlineStr">
         <is>
           <t>N (parameters lost)</t>
         </is>
       </c>
-      <c r="R58" s="1" t="inlineStr">
+      <c r="U58" s="1" t="inlineStr">
         <is>
           <t>Ar make-up: 0.9–1.2 l min⁻¹; Ar auxiliary: 0.6–1.2 l min⁻¹</t>
         </is>
       </c>
-      <c r="S58" s="1" t="inlineStr">
+      <c r="V58" s="1" t="inlineStr">
         <is>
           <t>Ar make-up gas (combined via T-piece in sample transport line near torch; flow rate not stated separately)</t>
         </is>
       </c>
-      <c r="T58" s="1" t="inlineStr">
+      <c r="W58" s="1" t="inlineStr">
         <is>
           <t>Ar make-up gas (same as spot protocol)</t>
         </is>
       </c>
-      <c r="U58" s="1" t="inlineStr">
+      <c r="X58" s="1" t="inlineStr">
         <is>
           <t>N (gas not separately specified beyond total plasma flow)</t>
         </is>
       </c>
-      <c r="V58" s="1" t="inlineStr">
+      <c r="Y58" s="1" t="inlineStr">
         <is>
           <t>N₂ or Ar mixed into He carrier for sensitivity optimization (amounts not stated)</t>
         </is>
       </c>
-      <c r="W58" s="1" t="inlineStr">
+      <c r="Z58" s="1" t="inlineStr">
         <is>
           <t>N₂ or Ar mixed (same protocol as glass)</t>
         </is>
       </c>
-      <c r="X58" s="1" t="inlineStr">
+      <c r="AA58" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
       </c>
-      <c r="Y58" s="1" t="inlineStr">
+      <c r="AB58" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
@@ -6667,68 +7230,81 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L59" s="9" t="n"/>
-      <c r="M59" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N59" s="1" t="inlineStr">
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>$.ada:methodParameters[]</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parameter: AuxGasFlowRate
+  dataType:  schema:propertyValueSpecification
+  readOnly: False
+</t>
+        </is>
+      </c>
+      <c r="O59" s="9" t="n"/>
+      <c r="P59" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q59" s="1" t="inlineStr">
         <is>
           <t>Cool: 15 l min⁻¹ Ar; Auxiliary: 0.81 l min⁻¹ (mapping)</t>
         </is>
       </c>
-      <c r="O59" s="1" t="inlineStr">
+      <c r="R59" s="1" t="inlineStr">
         <is>
           <t>Cool: 15 l min⁻¹ Ar; Auxiliary: 0.90 l min⁻¹ (run 1 and run 2)</t>
         </is>
       </c>
-      <c r="P59" s="1" t="inlineStr">
+      <c r="S59" s="1" t="inlineStr">
         <is>
           <t>Cool: 15 l min⁻¹ Ar; Auxiliary: 0.85 l min⁻¹</t>
         </is>
       </c>
-      <c r="Q59" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="R59" s="1" t="inlineStr">
+      <c r="T59" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U59" s="1" t="inlineStr">
         <is>
           <t>Cool gas: 12–13 l min⁻¹ Ar; Auxiliary: 0.6–1.2 l min⁻¹</t>
         </is>
       </c>
-      <c r="S59" s="1" t="inlineStr">
+      <c r="V59" s="1" t="inlineStr">
         <is>
           <t>Plasma gas: 16 l min⁻¹; Auxiliary: 0.9 l min⁻¹; Nebulizer gas (from table): 1.1 l min⁻¹</t>
         </is>
       </c>
-      <c r="T59" s="1" t="inlineStr">
+      <c r="W59" s="1" t="inlineStr">
         <is>
           <t>Plasma gas: 16 l min⁻¹; Auxiliary: 0.9 l min⁻¹</t>
         </is>
       </c>
-      <c r="U59" s="1" t="inlineStr">
+      <c r="X59" s="1" t="inlineStr">
         <is>
           <t>Plasma gas flow: 15 l min⁻¹; Auxiliary gas: 0.85 l min⁻¹</t>
         </is>
       </c>
-      <c r="V59" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="W59" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="X59" s="1" t="inlineStr">
+      <c r="Y59" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z59" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA59" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
       </c>
-      <c r="Y59" s="1" t="inlineStr">
+      <c r="AB59" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
@@ -6782,68 +7358,78 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L60" s="9" t="n"/>
-      <c r="M60" s="1" t="inlineStr">
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:rfPower</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>property:rfPower dataType: number readOnly: True</t>
+        </is>
+      </c>
+      <c r="O60" s="9" t="n"/>
+      <c r="P60" s="1" t="inlineStr">
         <is>
           <t>N (not reported)</t>
         </is>
       </c>
-      <c r="N60" s="1" t="inlineStr">
+      <c r="Q60" s="1" t="inlineStr">
         <is>
           <t>800 W (cool plasma for mapping)</t>
         </is>
       </c>
-      <c r="O60" s="1" t="inlineStr">
+      <c r="R60" s="1" t="inlineStr">
         <is>
           <t>1000 W (run 1 major elements + run 2 trace elements)</t>
         </is>
       </c>
-      <c r="P60" s="1" t="inlineStr">
+      <c r="S60" s="1" t="inlineStr">
         <is>
           <t>1000 W</t>
         </is>
       </c>
-      <c r="Q60" s="1" t="inlineStr">
+      <c r="T60" s="1" t="inlineStr">
         <is>
           <t>N (parameters lost)</t>
         </is>
       </c>
-      <c r="R60" s="1" t="inlineStr">
+      <c r="U60" s="1" t="inlineStr">
         <is>
           <t>1400 W</t>
         </is>
       </c>
-      <c r="S60" s="1" t="inlineStr">
+      <c r="V60" s="1" t="inlineStr">
         <is>
           <t>1200 W</t>
         </is>
       </c>
-      <c r="T60" s="1" t="inlineStr">
+      <c r="W60" s="1" t="inlineStr">
         <is>
           <t>1200 W</t>
         </is>
       </c>
-      <c r="U60" s="1" t="inlineStr">
+      <c r="X60" s="1" t="inlineStr">
         <is>
           <t>1550 W</t>
         </is>
       </c>
-      <c r="V60" s="1" t="inlineStr">
+      <c r="Y60" s="1" t="inlineStr">
         <is>
           <t>N (Agilent 7900; standard conditions implied)</t>
         </is>
       </c>
-      <c r="W60" s="1" t="inlineStr">
+      <c r="Z60" s="1" t="inlineStr">
         <is>
           <t>N (same instrument)</t>
         </is>
       </c>
-      <c r="X60" s="1" t="inlineStr">
+      <c r="AA60" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
       </c>
-      <c r="Y60" s="1" t="inlineStr">
+      <c r="AB60" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
@@ -6901,42 +7487,37 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L61" s="9" t="n"/>
-      <c r="M61" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N61" s="1" t="inlineStr">
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:plasmaThermalMode</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>property:plasmaThermalMode dataType: string readOnly: True enum {Normal plasma (&gt;1000 W RF) | Cool plasma (≤900 W RF)}</t>
+        </is>
+      </c>
+      <c r="O61" s="9" t="n"/>
+      <c r="P61" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q61" s="1" t="inlineStr">
         <is>
           <t>Cool plasma (800 W RF) to reduce Ar-based argide interferences on ⁶⁰Ni and ⁷¹Ga</t>
         </is>
       </c>
-      <c r="O61" s="1" t="inlineStr">
+      <c r="R61" s="1" t="inlineStr">
         <is>
           <t>Normal plasma (1000 W RF)</t>
         </is>
       </c>
-      <c r="P61" s="1" t="inlineStr">
+      <c r="S61" s="1" t="inlineStr">
         <is>
           <t>Normal plasma (1000 W RF)</t>
         </is>
       </c>
-      <c r="Q61" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="R61" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="S61" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="T61" s="1" t="inlineStr">
         <is>
           <t>N</t>
@@ -6959,10 +7540,25 @@
       </c>
       <c r="X61" s="1" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y61" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z61" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA61" s="1" t="inlineStr">
+        <is>
           <t>N (not stated) [P4]</t>
         </is>
       </c>
-      <c r="Y61" s="1" t="inlineStr">
+      <c r="AB61" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
@@ -7020,68 +7616,81 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L62" s="9" t="n"/>
-      <c r="M62" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N62" s="1" t="inlineStr">
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>$.ada:methodParameters[]</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parameter: SignalSmoothing
+  dataType:  schema:propertyValueSpecification
+  readOnly: False
+</t>
+        </is>
+      </c>
+      <c r="O62" s="9" t="n"/>
+      <c r="P62" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q62" s="1" t="inlineStr">
         <is>
           <t>None (no signal smoothing device; N₂ not added)</t>
         </is>
       </c>
-      <c r="O62" s="1" t="inlineStr">
+      <c r="R62" s="1" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="P62" s="1" t="inlineStr">
+      <c r="S62" s="1" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q62" s="1" t="inlineStr">
+      <c r="T62" s="1" t="inlineStr">
         <is>
           <t>N (parameters lost)</t>
         </is>
       </c>
-      <c r="R62" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="S62" s="1" t="inlineStr">
+      <c r="U62" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V62" s="1" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="T62" s="1" t="inlineStr">
+      <c r="W62" s="1" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="U62" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V62" s="1" t="inlineStr">
+      <c r="X62" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y62" s="1" t="inlineStr">
         <is>
           <t>N (CetacAnalyte HE; smoothing status not reported)</t>
         </is>
       </c>
-      <c r="W62" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="X62" s="1" t="inlineStr">
+      <c r="Z62" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA62" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
       </c>
-      <c r="Y62" s="1" t="inlineStr">
+      <c r="AB62" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
@@ -7139,68 +7748,81 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L63" s="9" t="n"/>
-      <c r="M63" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N63" s="1" t="inlineStr">
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>$.ada:methodParameters[]</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parameter: ICPlasmaTuning
+  dataType:  schema:propertyValueSpecification
+  readOnly: False
+</t>
+        </is>
+      </c>
+      <c r="O63" s="9" t="n"/>
+      <c r="P63" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q63" s="1" t="inlineStr">
         <is>
           <t>Daily tuning; cool plasma conditions optimized; N₂ explicitly not added to avoid N-based interferences</t>
         </is>
       </c>
-      <c r="O63" s="1" t="inlineStr">
+      <c r="R63" s="1" t="inlineStr">
         <is>
           <t>Same instrument as mapping; tuning optimized per run (different RF power and resolution settings per run)</t>
         </is>
       </c>
-      <c r="P63" s="1" t="inlineStr">
+      <c r="S63" s="1" t="inlineStr">
         <is>
           <t>Same instrument as olivine runs; tuned for normal plasma conditions</t>
         </is>
       </c>
-      <c r="Q63" s="1" t="inlineStr">
+      <c r="T63" s="1" t="inlineStr">
         <is>
           <t>N (parameters lost)</t>
         </is>
       </c>
-      <c r="R63" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="S63" s="1" t="inlineStr">
+      <c r="U63" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V63" s="1" t="inlineStr">
         <is>
           <t>ICP and laser settings optimized daily for optimum signal intensity and low oxide formation (factory specifications; mass calibration and detector cross-calibration checked and redone if required)</t>
         </is>
       </c>
-      <c r="T63" s="1" t="inlineStr">
+      <c r="W63" s="1" t="inlineStr">
         <is>
           <t>Same as spot protocol</t>
         </is>
       </c>
-      <c r="U63" s="1" t="inlineStr">
+      <c r="X63" s="1" t="inlineStr">
         <is>
           <t>Gas flows optimized via spot ablation of NIST SRM 612 to obtain maximum signal intensities while maintaining ThO/Th &lt;0.3% and U/Th at 0.95–1.05</t>
         </is>
       </c>
-      <c r="V63" s="1" t="inlineStr">
+      <c r="Y63" s="1" t="inlineStr">
         <is>
           <t>N (standard daily optimization implied)</t>
         </is>
       </c>
-      <c r="W63" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="X63" s="1" t="inlineStr">
+      <c r="Z63" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA63" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
       </c>
-      <c r="Y63" s="1" t="inlineStr">
+      <c r="AB63" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
@@ -7254,68 +7876,79 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L64" s="9" t="n"/>
-      <c r="M64" s="1" t="inlineStr">
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:oxideProductionMethod
+$MethodDefinition.ada:oxideProductionThreshold</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>property:oxideProductionMethodAndThreshold dataType: string readOnly: True</t>
+        </is>
+      </c>
+      <c r="O64" s="9" t="n"/>
+      <c r="P64" s="1" t="inlineStr">
         <is>
           <t>N (not reported; no oxide proxy threshold stated)</t>
         </is>
       </c>
-      <c r="N64" s="1" t="inlineStr">
+      <c r="Q64" s="1" t="inlineStr">
         <is>
           <t>ThO⁺/Th⁺ (mass 248/232); threshold not explicitly stated but minimized by cool plasma</t>
         </is>
       </c>
-      <c r="O64" s="1" t="inlineStr">
+      <c r="R64" s="1" t="inlineStr">
         <is>
           <t>N (normal plasma; no threshold stated for runs 1 and 2)</t>
         </is>
       </c>
-      <c r="P64" s="1" t="inlineStr">
+      <c r="S64" s="1" t="inlineStr">
         <is>
           <t>N (normal plasma; no threshold stated)</t>
         </is>
       </c>
-      <c r="Q64" s="1" t="inlineStr">
+      <c r="T64" s="1" t="inlineStr">
         <is>
           <t>N (parameters lost)</t>
         </is>
       </c>
-      <c r="R64" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="S64" s="1" t="inlineStr">
+      <c r="U64" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V64" s="1" t="inlineStr">
         <is>
           <t>N (factory optimization criterion; exact threshold not stated)</t>
         </is>
       </c>
-      <c r="T64" s="1" t="inlineStr">
+      <c r="W64" s="1" t="inlineStr">
         <is>
           <t>N (same as spot protocol)</t>
         </is>
       </c>
-      <c r="U64" s="1" t="inlineStr">
+      <c r="X64" s="1" t="inlineStr">
         <is>
           <t>ThO⁺/Th⁺ (mass 248/232) &lt;0.3%; U/Th monitored at 0.95–1.05</t>
         </is>
       </c>
-      <c r="V64" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="W64" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="X64" s="1" t="inlineStr">
+      <c r="Y64" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z64" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA64" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
       </c>
-      <c r="Y64" s="1" t="inlineStr">
+      <c r="AB64" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
@@ -7369,22 +8002,17 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L65" s="9" t="n"/>
-      <c r="M65" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N65" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O65" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>$Dataset.dqv:hasQualityMeasurement.dqv:isMeasurementOf='Measured oxide production ratio'.dqv:value</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>parameter:oxideProduction dataType: string readOnly: False</t>
+        </is>
+      </c>
+      <c r="O65" s="9" t="n"/>
       <c r="P65" s="1" t="inlineStr">
         <is>
           <t>N</t>
@@ -7412,25 +8040,40 @@
       </c>
       <c r="U65" s="1" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V65" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W65" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X65" s="1" t="inlineStr">
+        <is>
           <t>ThO/Th = measured at &lt;0.3%; U/Th = 0.95–1.05 (on NIST SRM 612)</t>
         </is>
       </c>
-      <c r="V65" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="W65" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="X65" s="1" t="inlineStr">
+      <c r="Y65" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z65" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA65" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
       </c>
-      <c r="Y65" s="1" t="inlineStr">
+      <c r="AB65" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
@@ -7488,10 +8131,12 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L66" s="9" t="n"/>
-      <c r="M66" s="1" t="n"/>
-      <c r="N66" s="1" t="n"/>
-      <c r="O66" s="1" t="n"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>parameter:doublyChargedSpeciesMonitor dataType: string readOnly: True</t>
+        </is>
+      </c>
+      <c r="O66" s="9" t="n"/>
       <c r="P66" s="1" t="n"/>
       <c r="Q66" s="1" t="n"/>
       <c r="R66" s="1" t="n"/>
@@ -7502,6 +8147,9 @@
       <c r="W66" s="1" t="n"/>
       <c r="X66" s="1" t="n"/>
       <c r="Y66" s="1" t="n"/>
+      <c r="Z66" s="1" t="n"/>
+      <c r="AA66" s="1" t="n"/>
+      <c r="AB66" s="1" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -7555,10 +8203,12 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L67" s="9" t="n"/>
-      <c r="M67" s="1" t="n"/>
-      <c r="N67" s="1" t="n"/>
-      <c r="O67" s="1" t="n"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>parameter:doublyChargedSpeciesProduction dataType: string readOnly: True</t>
+        </is>
+      </c>
+      <c r="O67" s="9" t="n"/>
       <c r="P67" s="1" t="n"/>
       <c r="Q67" s="1" t="n"/>
       <c r="R67" s="1" t="n"/>
@@ -7569,6 +8219,9 @@
       <c r="W67" s="1" t="n"/>
       <c r="X67" s="1" t="n"/>
       <c r="Y67" s="1" t="n"/>
+      <c r="Z67" s="1" t="n"/>
+      <c r="AA67" s="1" t="n"/>
+      <c r="AB67" s="1" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -7618,22 +8271,22 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L68" s="9" t="n"/>
-      <c r="M68" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N68" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O68" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>$.ada:methodParameters[]</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>parameter: WarmUpTime
+  dataType:  schema:propertyValue
+  readOnly: True
+parameter: SessionDurationLimit
+  dataType:  schema:propertyValue
+  readOnly: True</t>
+        </is>
+      </c>
+      <c r="O68" s="9" t="n"/>
       <c r="P68" s="1" t="inlineStr">
         <is>
           <t>N</t>
@@ -7676,10 +8329,25 @@
       </c>
       <c r="X68" s="1" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y68" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z68" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA68" s="1" t="inlineStr">
+        <is>
           <t>N (not stated) [P4]</t>
         </is>
       </c>
-      <c r="Y68" s="1" t="inlineStr">
+      <c r="AB68" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
@@ -7733,68 +8401,81 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L69" s="9" t="n"/>
-      <c r="M69" s="1" t="inlineStr">
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>$.ada:methodParameters[]</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parameter: DriftMonitorFrequency
+  dataType:  schema:propertyValueSpecification
+  readOnly: False
+</t>
+        </is>
+      </c>
+      <c r="O69" s="9" t="n"/>
+      <c r="P69" s="1" t="inlineStr">
         <is>
           <t>Standards at start and end of session; external bracketing</t>
         </is>
       </c>
-      <c r="N69" s="1" t="inlineStr">
+      <c r="Q69" s="1" t="inlineStr">
         <is>
           <t>Each GRM analyzed 3–5× before and 3–5× after sample analyses (all GRMs at start and end of session)</t>
         </is>
       </c>
-      <c r="O69" s="1" t="inlineStr">
+      <c r="R69" s="1" t="inlineStr">
         <is>
           <t>Same as mapping protocol; GRMs at start and end</t>
         </is>
       </c>
-      <c r="P69" s="1" t="inlineStr">
+      <c r="S69" s="1" t="inlineStr">
         <is>
           <t>MPI-DING and USGS GRMs measured at beginning and repeatedly at end of each session</t>
         </is>
       </c>
-      <c r="Q69" s="1" t="inlineStr">
+      <c r="T69" s="1" t="inlineStr">
         <is>
           <t>N (parameters lost)</t>
         </is>
       </c>
-      <c r="R69" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="S69" s="1" t="inlineStr">
+      <c r="U69" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V69" s="1" t="inlineStr">
         <is>
           <t>NIST SRM 612 and North Chile measured bracketing every 15 unknowns: 3×STD → 3×STD → 10×unknowns → repeat</t>
         </is>
       </c>
-      <c r="T69" s="1" t="inlineStr">
+      <c r="W69" s="1" t="inlineStr">
         <is>
           <t>NIST SRM 612 and North Chile at start and end of mapping session (30 min map; 3 measurements each before and after)</t>
         </is>
       </c>
-      <c r="U69" s="1" t="inlineStr">
+      <c r="X69" s="1" t="inlineStr">
         <is>
           <t>NIST SRM 612 and 614 measured as external standards within session; BHVO-2 and other GRMs as unknowns</t>
         </is>
       </c>
-      <c r="V69" s="1" t="inlineStr">
+      <c r="Y69" s="1" t="inlineStr">
         <is>
           <t>NIST 610 as primary; NIST 612 and BCR-2G as monitoring standards</t>
         </is>
       </c>
-      <c r="W69" s="1" t="inlineStr">
+      <c r="Z69" s="1" t="inlineStr">
         <is>
           <t>Same bracketing as silicate glass protocol</t>
         </is>
       </c>
-      <c r="X69" s="1" t="inlineStr">
+      <c r="AA69" s="1" t="inlineStr">
         <is>
           <t>NIST 610 glass standard analyzed before and after every session [P4]</t>
         </is>
       </c>
-      <c r="Y69" s="1" t="inlineStr">
+      <c r="AB69" s="1" t="inlineStr">
         <is>
           <t>NIST 610 analyzed before and after every session (same as silicate protocol) [P4]</t>
         </is>
@@ -7848,68 +8529,78 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L70" s="9" t="n"/>
-      <c r="M70" s="1" t="inlineStr">
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:analysisSequence</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>property:analysisSequenceDefault dataType: string readOnly: False</t>
+        </is>
+      </c>
+      <c r="O70" s="9" t="n"/>
+      <c r="P70" s="1" t="inlineStr">
         <is>
           <t>Standards at start of session → raster unknowns → repeat → standards at end; separate session for Ge spot analyses</t>
         </is>
       </c>
-      <c r="N70" s="1" t="inlineStr">
+      <c r="Q70" s="1" t="inlineStr">
         <is>
           <t>(i) Gas blanks → (ii) all glass GRMs for external calibration → (iii) 1–3 cosmic spherule unknowns → (iv) blanks → (v) all glass GRMs again</t>
         </is>
       </c>
-      <c r="O70" s="1" t="inlineStr">
+      <c r="R70" s="1" t="inlineStr">
         <is>
           <t>GRM block (3–5×) → unknowns → GRM block (3–5×); same structure for run 1 and run 2</t>
         </is>
       </c>
-      <c r="P70" s="1" t="inlineStr">
+      <c r="S70" s="1" t="inlineStr">
         <is>
           <t>MPI-DING and USGS GRMs at beginning → unknowns → repeated GRM at end</t>
         </is>
       </c>
-      <c r="Q70" s="1" t="inlineStr">
+      <c r="T70" s="1" t="inlineStr">
         <is>
           <t>BCR-2g, BHVO-2g, BIR-1g measured as calibration standards; Marjalahti as in-session control</t>
         </is>
       </c>
-      <c r="R70" s="1" t="inlineStr">
+      <c r="U70" s="1" t="inlineStr">
         <is>
           <t>IVB meteorite standards (Warburton Range external + Tawallah Valley secondary) measured alongside unknowns; exact bracketing not described</t>
         </is>
       </c>
-      <c r="S70" s="1" t="inlineStr">
+      <c r="V70" s="1" t="inlineStr">
         <is>
           <t>NIST SRM 612(×3) → North Chile(×3) → unknowns(×10) → NIST SRM 612(×2) → North Chile(×2) → unknowns(×10) → … (bracketing every 15)</t>
         </is>
       </c>
-      <c r="T70" s="1" t="inlineStr">
+      <c r="W70" s="1" t="inlineStr">
         <is>
           <t>Background (1 min) → NIST SRM 612(×3) → North Chile(×3) → unknown map (30 min) → North Chile(×3) → NIST SRM 612(×3) → background</t>
         </is>
       </c>
-      <c r="U70" s="1" t="inlineStr">
+      <c r="X70" s="1" t="inlineStr">
         <is>
           <t>Gas blank (25 s) → ablation (45 s) → washout (25 s); NIST 612 and 614 as external standards; BHVO-2 and 6 GRMs measured as unknowns</t>
         </is>
       </c>
-      <c r="V70" s="1" t="inlineStr">
+      <c r="Y70" s="1" t="inlineStr">
         <is>
           <t>NIST 610 as primary standard measured in session; NIST 612 and BCR-2G as monitoring standards; unknowns bracketed by standards</t>
         </is>
       </c>
-      <c r="W70" s="1" t="inlineStr">
+      <c r="Z70" s="1" t="inlineStr">
         <is>
           <t>Same bracketing as silicate glass protocol</t>
         </is>
       </c>
-      <c r="X70" s="1" t="inlineStr">
+      <c r="AA70" s="1" t="inlineStr">
         <is>
           <t>NIST 610 glass standard analyzed before and after every session; unknowns in between [P4]</t>
         </is>
       </c>
-      <c r="Y70" s="1" t="inlineStr">
+      <c r="AB70" s="1" t="inlineStr">
         <is>
           <t>Same as silicate protocol [P4]</t>
         </is>
@@ -7967,68 +8658,78 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L71" s="9" t="n"/>
-      <c r="M71" s="1" t="inlineStr">
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:analytes</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>list of target analytes</t>
+        </is>
+      </c>
+      <c r="O71" s="9" t="n"/>
+      <c r="P71" s="1" t="inlineStr">
         <is>
           <t>³¹P, ⁵¹V, ⁵³Cr, ⁵⁵Mn, ⁵⁷Fe, ⁵⁹Co, ⁶⁰Ni, ⁶³Cu, ⁷¹Ga, ⁷⁴Ge, ⁷⁵As, ⁹⁵Mo, ¹⁰²Ru, ¹⁰³Rh, ¹⁰⁶Pd, ¹²⁰Sn, ¹²¹Sb, ¹⁸²W, ¹⁸⁵Re, ¹⁹⁰Os, ¹⁹³Ir, ¹⁹⁵Pt, ¹⁹⁷Au (23 elements; 31P, 51V, 53Cr, 55Mn, 57Fe, 59Co, 60Ni, 63Cu, 71Ga for spot Ge runs)</t>
         </is>
       </c>
-      <c r="N71" s="1" t="inlineStr">
+      <c r="Q71" s="1" t="inlineStr">
         <is>
           <t>²⁵Mg, ²⁷Al, ²⁹Si, ³¹P, ⁴⁵Sc, ⁵¹V, ⁵³Cr, ⁵⁵Mn, ⁵⁷Fe, ⁶⁰Ni, ⁷¹Ga, ¹³⁹La, ¹⁵³Eu, ¹⁹⁵Pt (14 nuclides)</t>
         </is>
       </c>
-      <c r="O71" s="1" t="inlineStr">
+      <c r="R71" s="1" t="inlineStr">
         <is>
           <t>Run 1 (major): ²⁵Mg, ²⁹Si, ³¹P, ⁴⁴Ca, ⁵³Cr, ⁵⁵Mn, ⁵⁷Fe (7 nuclides; medium resolution); Run 2 (trace): ⁷Li, ⁴⁵Sc, ⁵¹V, ⁵³Cr, ⁵⁹Co, ⁶⁰Ni, ⁶³Cu, ⁶⁶Zn, ⁸⁹Y, ⁹⁰Zr, ⁹³Nb, ¹³³Cs, ¹³⁷Ba, ¹³⁹La–¹⁷⁵Lu (all REE), ¹⁸⁰Hf, ¹⁸¹Ta, ¹⁸²W, ¹⁸⁵Re, ¹⁹³Ir, ¹⁹⁵Pt, ¹⁹⁷Au, ²³²Th, ²³⁸U (36 nuclides)</t>
         </is>
       </c>
-      <c r="P71" s="1" t="inlineStr">
+      <c r="S71" s="1" t="inlineStr">
         <is>
           <t>²³Na, ²⁵Mg, ²⁷Al, ²⁹Si, ³¹P, ³⁹K, ⁴⁴Ca, ⁴⁵Sc, ⁴⁷Ti, ⁵¹V, ⁵³Cr, ⁵⁵Mn, ⁵⁷Fe, ⁵⁹Co, ⁶⁰Ni, ⁶³Cu, ⁶⁶Zn, ⁸⁵Rb, ⁸⁸Sr, ⁸⁹Y, ⁹⁰Zr, ⁹³Nb, ¹³³Cs, ¹³⁷Ba, ¹³⁹La–¹⁷⁵Lu (all REE), ¹⁸⁰Hf, ¹⁸¹Ta, ²⁰⁸Pb, ²³²Th, ²³⁸U (43 nuclides)</t>
         </is>
       </c>
-      <c r="Q71" s="1" t="inlineStr">
+      <c r="T71" s="1" t="inlineStr">
         <is>
           <t>²⁵Mg, ²⁷Al, ³¹P, ⁴³Ca, ⁴⁴Ca, ⁴⁵Sc, ⁴⁷Ti, ⁴⁹Ti, ⁵¹V, ⁵²Cr, ⁵³Cr, ⁵⁹Co, ⁶⁰Ni, ⁶¹Ni, ⁶²Ni, ⁶⁴Zn, ⁶⁶Zn, ⁶⁹Ga, ⁷¹Ga (19 nuclides)</t>
         </is>
       </c>
-      <c r="R71" s="1" t="inlineStr">
+      <c r="U71" s="1" t="inlineStr">
         <is>
           <t>⁵⁹Co, ¹⁰¹Ru, ¹⁰³Rh, ¹⁰⁵Pd, ¹⁸⁵Re, ¹⁸⁹Os, ¹⁹³Ir, ¹⁹⁵Pt, ¹⁹⁷Au (9 HSE isotopes); ²⁴Mg, ²⁹Si, ³¹P, ³³S monitored for inclusion detection; ⁶¹Ni as internal standard</t>
         </is>
       </c>
-      <c r="S71" s="1" t="inlineStr">
+      <c r="V71" s="1" t="inlineStr">
         <is>
           <t>⁵²Cr, ⁵⁷Fe, ⁵⁹Co, ⁶¹Ni, ⁶⁵Cu, ⁶⁹Ga, ⁷²Ge, ⁷⁵As, ⁹⁹Ru, ¹⁰³Rh, ¹⁰⁵Pd, ¹⁸²W, ¹⁸⁵Re, ¹⁸⁹Os, ¹⁹³Ir, ¹⁹⁵Pt, ¹⁹⁷Au (17 isotopes); low relative abundance isotopes chosen for Ni and Fe (analog mode)</t>
         </is>
       </c>
-      <c r="T71" s="1" t="inlineStr">
+      <c r="W71" s="1" t="inlineStr">
         <is>
           <t>⁵²Cr, ⁵⁷Fe, ⁵⁹Co, ⁶¹Ni, ⁶⁵Cu, ⁶⁹Ga, ⁷²Ge, ⁷⁵As, ⁹⁹Ru, ¹⁰³Rh, ¹⁰⁵Pd, ¹⁸²W, ¹⁸⁵Re, ¹⁸⁹Os, ¹⁹³Ir, ¹⁹⁵Pt, ¹⁹⁷Au (same 17 isotopes as spot protocol)</t>
         </is>
       </c>
-      <c r="U71" s="1" t="inlineStr">
+      <c r="X71" s="1" t="inlineStr">
         <is>
           <t>²¹Sc, ⁵¹V, ⁵²Cr, ⁵⁹Co, ⁶⁰Ni, ⁶³Cu, ⁶⁶Zn, ⁶⁹Ga, ⁸⁵Rb, ⁸⁸Sr, ⁸⁹Y, ⁹⁰Zr, ⁹³Nb, ¹³³Cs, ¹³⁷Ba, ¹³⁹La, ¹⁴⁰Ce, ¹⁴¹Pr, ¹⁴⁶Nd, ¹⁴⁷Sm, ¹⁵³Eu, ¹⁵⁷Gd, ¹⁵⁹Tb, ¹⁶³Dy, ¹⁶⁵Ho, ¹⁶⁶Er, ¹⁶⁹Tm, ¹⁷²Yb, ¹⁷⁵Lu, ¹⁷⁸Hf, ¹⁸¹Ta, ²³²Th, ²³⁸U (32 trace elements)</t>
         </is>
       </c>
-      <c r="V71" s="1" t="inlineStr">
+      <c r="Y71" s="1" t="inlineStr">
         <is>
           <t>¹⁹⁷Au, ⁶³Cu (primary targets); all detected via Agilent 7900 (exact isotope list not fully stated)</t>
         </is>
       </c>
-      <c r="W71" s="1" t="inlineStr">
+      <c r="Z71" s="1" t="inlineStr">
         <is>
           <t>¹⁹⁷Au, ⁶³Cu (primary targets; Si and Fe from EMP as internal standards)</t>
         </is>
       </c>
-      <c r="X71" s="1" t="inlineStr">
+      <c r="AA71" s="1" t="inlineStr">
         <is>
           <t>N (not explicitly listed in methods; results text mentions Sc, V, Ti, Co, Ni, REEs measured in silicates; full isotope list not stated) [P4, P7, P11]</t>
         </is>
       </c>
-      <c r="Y71" s="1" t="inlineStr">
+      <c r="AB71" s="1" t="inlineStr">
         <is>
           <t>N (not explicitly listed in methods; merrillite REE La-Lu at 14–414 ppm range mentioned in results; full isotope list not stated) [P12]</t>
         </is>
@@ -8090,68 +8791,85 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L72" s="9" t="n"/>
-      <c r="M72" s="1" t="inlineStr">
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>$.ada:analyteTemplate.ada:analyteColumns[]</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Items marked 'Analyte Specific' in column G of this table become entries in the ada:analyteColumns Array.  </t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>analyteColumn: spectrometerDwellTime 
+  datatype: numeric
+  readOnly:false</t>
+        </is>
+      </c>
+      <c r="O72" s="9" t="n"/>
+      <c r="P72" s="1" t="inlineStr">
         <is>
           <t>N (dwell times not reported)</t>
         </is>
       </c>
-      <c r="N72" s="1" t="inlineStr">
+      <c r="Q72" s="1" t="inlineStr">
         <is>
           <t>0.01 s (10 ms) per nuclide; samples per peak: 10; duty cycle time: 1.944 s (14 nuclides)</t>
         </is>
       </c>
-      <c r="O72" s="1" t="inlineStr">
+      <c r="R72" s="1" t="inlineStr">
         <is>
           <t>Run 1 (major): 0.01 s per nuclide; samples per peak: 18; duty cycle: 2.069 s; Run 2 (trace): 0.01 s per nuclide; samples per peak: 7; duty cycle: 2.062 s</t>
         </is>
       </c>
-      <c r="P72" s="1" t="inlineStr">
+      <c r="S72" s="1" t="inlineStr">
         <is>
           <t>0.01 s per nuclide; samples per peak: 5; duty cycle: 1.813 s; mass window 150% for ²³Na–⁴⁷Ti, 100% for all other nuclides</t>
         </is>
       </c>
-      <c r="Q72" s="1" t="inlineStr">
+      <c r="T72" s="1" t="inlineStr">
         <is>
           <t>N (parameters lost; 10–50 ms varies by isotope per paper text)</t>
         </is>
       </c>
-      <c r="R72" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="S72" s="1" t="inlineStr">
+      <c r="U72" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V72" s="1" t="inlineStr">
         <is>
           <t>0.02 s per isotope; 100 samples per peak; 10 runs; 60 passes; total measurement time 120 s per analysis</t>
         </is>
       </c>
-      <c r="T72" s="1" t="inlineStr">
+      <c r="W72" s="1" t="inlineStr">
         <is>
           <t>0.02 s per isotope; 100 samples per peak (same as spot protocol)</t>
         </is>
       </c>
-      <c r="U72" s="1" t="inlineStr">
+      <c r="X72" s="1" t="inlineStr">
         <is>
           <t>30 ms (most isotopes) / 10 ms (alternate; dual detector mode)</t>
         </is>
       </c>
-      <c r="V72" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="W72" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="X72" s="1" t="inlineStr">
+      <c r="Y72" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z72" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA72" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
       </c>
-      <c r="Y72" s="1" t="inlineStr">
+      <c r="AB72" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
@@ -8205,68 +8923,78 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L73" s="9" t="n"/>
-      <c r="M73" s="1" t="inlineStr">
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:backgroundCountTime</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>property:backgroundCountTimeDefault dataType: number readOnly: False</t>
+        </is>
+      </c>
+      <c r="O73" s="9" t="n"/>
+      <c r="P73" s="1" t="inlineStr">
         <is>
           <t>N (gas blank measured before analyses but duration not reported)</t>
         </is>
       </c>
-      <c r="N73" s="1" t="inlineStr">
+      <c r="Q73" s="1" t="inlineStr">
         <is>
           <t>Scans for gas blank: 10 per line (before each mapping line); 80 scans during ablation</t>
         </is>
       </c>
-      <c r="O73" s="1" t="inlineStr">
+      <c r="R73" s="1" t="inlineStr">
         <is>
           <t>Run 1: 5 gas blank scans; 24 ablation scans; Run 2: 5 gas blank scans; 24 ablation scans</t>
         </is>
       </c>
-      <c r="P73" s="1" t="inlineStr">
+      <c r="S73" s="1" t="inlineStr">
         <is>
           <t>8 gas blank scans; 11 ablation scans (25 cycles measurement: 15 s blank + 20 s ablation + 10 s washout)</t>
         </is>
       </c>
-      <c r="Q73" s="1" t="inlineStr">
+      <c r="T73" s="1" t="inlineStr">
         <is>
           <t>N (parameters lost; gas blank measured before each analysis per paper text)</t>
         </is>
       </c>
-      <c r="R73" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="S73" s="1" t="inlineStr">
+      <c r="U73" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V73" s="1" t="inlineStr">
         <is>
           <t>20 s background measurement (laser shutter closed) before each 40 s ablation</t>
         </is>
       </c>
-      <c r="T73" s="1" t="inlineStr">
+      <c r="W73" s="1" t="inlineStr">
         <is>
           <t>60 s background measurement before mapping session start; 3 measurements each for NIST and North Chile after background</t>
         </is>
       </c>
-      <c r="U73" s="1" t="inlineStr">
+      <c r="X73" s="1" t="inlineStr">
         <is>
           <t>25 s gas blank before each ablation</t>
         </is>
       </c>
-      <c r="V73" s="1" t="inlineStr">
+      <c r="Y73" s="1" t="inlineStr">
         <is>
           <t>N (gas blank measured but duration not explicitly stated)</t>
         </is>
       </c>
-      <c r="W73" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="X73" s="1" t="inlineStr">
+      <c r="Z73" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA73" s="1" t="inlineStr">
         <is>
           <t>50 s (background counted for 50 s before each LA-ICP-MS analysis) [P4]</t>
         </is>
       </c>
-      <c r="Y73" s="1" t="inlineStr">
+      <c r="AB73" s="1" t="inlineStr">
         <is>
           <t>50 s (same as silicate protocol) [P4]</t>
         </is>
@@ -8320,18 +9048,31 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L74" s="9" t="n"/>
-      <c r="M74" s="1" t="inlineStr">
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>$.ada:methodParameters[]</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parameter: DriftMonitorFrequency
+  dataType:  schema:propertyValue
+  readOnly: True
+</t>
+        </is>
+      </c>
+      <c r="O74" s="9" t="n"/>
+      <c r="P74" s="1" t="inlineStr">
         <is>
           <t>N (single raster acquisition; Ge spot separate session)</t>
         </is>
       </c>
-      <c r="N74" s="1" t="inlineStr">
+      <c r="Q74" s="1" t="inlineStr">
         <is>
           <t>N/A (mapping; no sequential multi-run)</t>
         </is>
       </c>
-      <c r="O74" s="1" t="inlineStr">
+      <c r="R74" s="1" t="inlineStr">
         <is>
           <t>Three-stage sequential design on same olivine location:
 (1) Pre-ablation pass (2 J cm⁻², 150 µm square, 300 µm s⁻¹) to remove surface contamination;
@@ -8339,52 +9080,52 @@
 (3) Run 2 — trace elements (130 µm circular, LR M/ΔM=300, 40 Hz, 36 nuclides; Cr from run 1 as IS)</t>
         </is>
       </c>
-      <c r="P74" s="1" t="inlineStr">
+      <c r="S74" s="1" t="inlineStr">
         <is>
           <t>Single spot analysis run per location (25 cycles: 15 s blank + 20 s ablation + 10 s washout); 3 replicates</t>
         </is>
       </c>
-      <c r="Q74" s="1" t="inlineStr">
+      <c r="T74" s="1" t="inlineStr">
         <is>
           <t>Single spot per location (75 µm circular)</t>
         </is>
       </c>
-      <c r="R74" s="1" t="inlineStr">
+      <c r="U74" s="1" t="inlineStr">
         <is>
           <t>Single spot per location (30 µm circular)</t>
         </is>
       </c>
-      <c r="S74" s="1" t="inlineStr">
+      <c r="V74" s="1" t="inlineStr">
         <is>
           <t>Single acquisition run (20 spot analyses per sample under repeatability conditions)</t>
         </is>
       </c>
-      <c r="T74" s="1" t="inlineStr">
+      <c r="W74" s="1" t="inlineStr">
         <is>
           <t>N/A (mapping)</t>
         </is>
       </c>
-      <c r="U74" s="1" t="inlineStr">
+      <c r="X74" s="1" t="inlineStr">
         <is>
           <t>Single spot per location (45 s ablation at 1 Hz)</t>
         </is>
       </c>
-      <c r="V74" s="1" t="inlineStr">
+      <c r="Y74" s="1" t="inlineStr">
         <is>
           <t>Single spot per location (~40 s ablation at 7 Hz)</t>
         </is>
       </c>
-      <c r="W74" s="1" t="inlineStr">
+      <c r="Z74" s="1" t="inlineStr">
         <is>
           <t>Single spot per location (sulfides; same acquisition parameters as glass but 20 µm spot)</t>
         </is>
       </c>
-      <c r="X74" s="1" t="inlineStr">
+      <c r="AA74" s="1" t="inlineStr">
         <is>
           <t>Single spot analysis per location [P4]</t>
         </is>
       </c>
-      <c r="Y74" s="1" t="inlineStr">
+      <c r="AB74" s="1" t="inlineStr">
         <is>
           <t>Single spot analysis per location [P4]</t>
         </is>
@@ -8438,22 +9179,32 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L75" s="9" t="n"/>
-      <c r="M75" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N75" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O75" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>for map area spatial reference: $Dataset.schema.object[$type = schema:Thing].schema.name = 'mapped area description'/schema.description
+for spot location: ada:analyteColumns and $Dataset.schema.object[$type = schema:Thing].schema.name = 'spot sptial reference'/schema.description</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>if is X, Y  coordinates of spot, is analysis Level; if is  coordinates locating a mapped area, is DataSet level text. 
+Spot spatial reference defines the origin, axis orientation, and scael for the spot coordinates.</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>analyteColumn:  spotXCoordinate
+  datatype: numeric
+  readOnly:false
+analyteColumn: spotYCoordinate 
+  datatype: numeric
+  readOnly:false
+analyteColumn: spotIdentifier
+  datatype: text
+  readOnly:false</t>
+        </is>
+      </c>
+      <c r="O75" s="9" t="n"/>
       <c r="P75" s="1" t="inlineStr">
         <is>
           <t>N</t>
@@ -8500,6 +9251,21 @@
         </is>
       </c>
       <c r="Y75" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z75" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA75" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB75" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -8553,68 +9319,78 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L76" s="9" t="n"/>
-      <c r="M76" s="1" t="inlineStr">
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>$Dataset.prov:wasGeneratedBy.schema:additionalProperty [name = 'numberOfReplicates'].schema:value</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>parameter:numberOfReplicates dataType: integer readOnly: False</t>
+        </is>
+      </c>
+      <c r="O76" s="9" t="n"/>
+      <c r="P76" s="1" t="inlineStr">
         <is>
           <t>N (number not stated explicitly; multiple irons analyzed)</t>
         </is>
       </c>
-      <c r="N76" s="1" t="inlineStr">
+      <c r="Q76" s="1" t="inlineStr">
         <is>
           <t>N (single map per olivine crystal section per sample)</t>
         </is>
       </c>
-      <c r="O76" s="1" t="inlineStr">
+      <c r="R76" s="1" t="inlineStr">
         <is>
           <t>3 replicate analyses per grain (3× run 1 + 3× run 2 on same location)</t>
         </is>
       </c>
-      <c r="P76" s="1" t="inlineStr">
+      <c r="S76" s="1" t="inlineStr">
         <is>
           <t>Multiple phosphate grains per meteorite; number varies by section</t>
         </is>
       </c>
-      <c r="Q76" s="1" t="inlineStr">
+      <c r="T76" s="1" t="inlineStr">
         <is>
           <t>N (variable number of spots per sample)</t>
         </is>
       </c>
-      <c r="R76" s="1" t="inlineStr">
+      <c r="U76" s="1" t="inlineStr">
         <is>
           <t>N (variable number of spots per grain; Mg, Si, P, S monitored to check for inclusions)</t>
         </is>
       </c>
-      <c r="S76" s="1" t="inlineStr">
+      <c r="V76" s="1" t="inlineStr">
         <is>
           <t>20 spot analyses per meteorite under repeatability conditions; additional measurements on different days</t>
         </is>
       </c>
-      <c r="T76" s="1" t="inlineStr">
+      <c r="W76" s="1" t="inlineStr">
         <is>
           <t>1 map per meteorite (single 30-min mapping acquisition)</t>
         </is>
       </c>
-      <c r="U76" s="1" t="inlineStr">
+      <c r="X76" s="1" t="inlineStr">
         <is>
           <t>9 spot analyses in grid pattern for homogeneity testing; multiple analyses per fusion glass disk</t>
         </is>
       </c>
-      <c r="V76" s="1" t="inlineStr">
+      <c r="Y76" s="1" t="inlineStr">
         <is>
           <t>N (variable per run)</t>
         </is>
       </c>
-      <c r="W76" s="1" t="inlineStr">
+      <c r="Z76" s="1" t="inlineStr">
         <is>
           <t>N (grain size &gt;20 µm selected; number of analyzed grains variable)</t>
         </is>
       </c>
-      <c r="X76" s="1" t="inlineStr">
+      <c r="AA76" s="1" t="inlineStr">
         <is>
           <t>N (not stated)</t>
         </is>
       </c>
-      <c r="Y76" s="1" t="inlineStr">
+      <c r="AB76" s="1" t="inlineStr">
         <is>
           <t>N (not stated)</t>
         </is>
@@ -8668,68 +9444,78 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L77" s="9" t="n"/>
-      <c r="M77" s="1" t="inlineStr">
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>$Dataset.prov:wasGeneratedBy.schema:additionalProperty [name = 'TransectLength'].schema:value</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>parameter:transectLength dataType: number readOnly: False</t>
+        </is>
+      </c>
+      <c r="O77" s="9" t="n"/>
+      <c r="P77" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="N77" s="1" t="inlineStr">
+      <c r="Q77" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="O77" s="1" t="inlineStr">
+      <c r="R77" s="1" t="inlineStr">
         <is>
           <t>Line scan length: 400 µm (runs 1 and 2; 34 runs adjusted to measure 400 µm line + blank + washout)</t>
         </is>
       </c>
-      <c r="P77" s="1" t="inlineStr">
+      <c r="S77" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="Q77" s="1" t="inlineStr">
+      <c r="T77" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="R77" s="1" t="inlineStr">
+      <c r="U77" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S77" s="1" t="inlineStr">
+      <c r="V77" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="T77" s="1" t="inlineStr">
+      <c r="W77" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="U77" s="1" t="inlineStr">
+      <c r="X77" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="V77" s="1" t="inlineStr">
+      <c r="Y77" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="W77" s="1" t="inlineStr">
+      <c r="Z77" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="X77" s="1" t="inlineStr">
+      <c r="AA77" s="1" t="inlineStr">
         <is>
           <t>N/A (spot analysis)</t>
         </is>
       </c>
-      <c r="Y77" s="1" t="inlineStr">
+      <c r="AB77" s="1" t="inlineStr">
         <is>
           <t>N/A (spot analysis)</t>
         </is>
@@ -8783,68 +9569,78 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L78" s="9" t="n"/>
-      <c r="M78" s="1" t="inlineStr">
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>$Dataset.prov:wasGeneratedBy.schema:additionalProperty [name = 'MappingArea'].schema:value</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>parameter:mappingArea dataType: string readOnly: False</t>
+        </is>
+      </c>
+      <c r="O78" s="9" t="n"/>
+      <c r="P78" s="1" t="inlineStr">
         <is>
           <t>Raster over "a few millimeters" of polished iron slab surface (area not precisely stated)</t>
         </is>
       </c>
-      <c r="N78" s="1" t="inlineStr">
+      <c r="Q78" s="1" t="inlineStr">
         <is>
           <t>Each map: 1450×600 µm = 870,000 µm²; total of 8 PMG olivines mapped</t>
         </is>
       </c>
-      <c r="O78" s="1" t="inlineStr">
+      <c r="R78" s="1" t="inlineStr">
         <is>
           <t>N/A (line scan + spot; not 2D raster)</t>
         </is>
       </c>
-      <c r="P78" s="1" t="inlineStr">
+      <c r="S78" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="Q78" s="1" t="inlineStr">
+      <c r="T78" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="R78" s="1" t="inlineStr">
+      <c r="U78" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S78" s="1" t="inlineStr">
+      <c r="V78" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="T78" s="1" t="inlineStr">
+      <c r="W78" s="1" t="inlineStr">
         <is>
           <t>Augusto Pestana: 30 min mapping session (area not explicitly stated; 150 µm spot at 10 µm s⁻¹)</t>
         </is>
       </c>
-      <c r="U78" s="1" t="inlineStr">
+      <c r="X78" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="V78" s="1" t="inlineStr">
+      <c r="Y78" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="W78" s="1" t="inlineStr">
+      <c r="Z78" s="1" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="X78" s="1" t="inlineStr">
+      <c r="AA78" s="1" t="inlineStr">
         <is>
           <t>N/A (spot analysis)</t>
         </is>
       </c>
-      <c r="Y78" s="1" t="inlineStr">
+      <c r="AB78" s="1" t="inlineStr">
         <is>
           <t>N/A (spot analysis)</t>
         </is>
@@ -8867,9 +9663,6 @@
       <c r="I80" s="5" t="n"/>
       <c r="J80" s="5" t="n"/>
       <c r="K80" s="5" t="n"/>
-      <c r="L80" s="5" t="n"/>
-      <c r="M80" s="5" t="n"/>
-      <c r="N80" s="5" t="n"/>
       <c r="O80" s="5" t="n"/>
       <c r="P80" s="5" t="n"/>
       <c r="Q80" s="5" t="n"/>
@@ -8879,12 +9672,15 @@
       <c r="U80" s="5" t="n"/>
       <c r="V80" s="5" t="n"/>
       <c r="W80" s="5" t="n"/>
-      <c r="X80" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Y80" s="5" t="inlineStr">
+      <c r="X80" s="5" t="n"/>
+      <c r="Y80" s="5" t="n"/>
+      <c r="Z80" s="5" t="n"/>
+      <c r="AA80" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB80" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -8942,68 +9738,78 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L81" s="9" t="n"/>
-      <c r="M81" s="1" t="inlineStr">
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:internalStandardApproach</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>property:internalStandardApproach dataType: string readOnly: True</t>
+        </is>
+      </c>
+      <c r="O81" s="9" t="n"/>
+      <c r="P81" s="1" t="inlineStr">
         <is>
           <t>Standardization techniques followed those of Humayun (2012) [Section 2.2; specific IS approach not restated in this paper]</t>
         </is>
       </c>
-      <c r="N81" s="1" t="inlineStr">
+      <c r="Q81" s="1" t="inlineStr">
         <is>
           <t>Sum-of-major-oxide normalization: MgO+FeO+SiO₂+P₂O₅ = 100 wt% per pixel (Liu et al. 2008 approach; no EPMA required for IS)</t>
         </is>
       </c>
-      <c r="O81" s="1" t="inlineStr">
+      <c r="R81" s="1" t="inlineStr">
         <is>
           <t>Run 1 (major elements): sum-of-oxide normalization (MgO+FeO+SiO₂+P₂O₅=100 wt%; Liu et al. 2008); Run 2 (trace elements): single element IS from Run 1 (⁵³Cr concentration from major element run used as IS for trace element run)</t>
         </is>
       </c>
-      <c r="P81" s="1" t="inlineStr">
+      <c r="S81" s="1" t="inlineStr">
         <is>
           <t>Sum-of-major-oxide normalization to 100 wt% (Liu et al. 2008; Appendix C3)</t>
         </is>
       </c>
-      <c r="Q81" s="1" t="inlineStr">
+      <c r="T81" s="1" t="inlineStr">
         <is>
           <t>Single element from EPMA: ²⁵Mg; the EMPA data used as the standardizing values</t>
         </is>
       </c>
-      <c r="R81" s="1" t="inlineStr">
+      <c r="U81" s="1" t="inlineStr">
         <is>
           <t>Single element externally measured by EPMA: ⁶¹Ni concentration from EPMA at exact analysis location used as IS</t>
         </is>
       </c>
-      <c r="S81" s="1" t="inlineStr">
+      <c r="V81" s="1" t="inlineStr">
         <is>
           <t>Fe+Ni+Co sum normalization to 100% using iolite 3D Trace Elements DRS (eliminates need for independent EPMA IS)</t>
         </is>
       </c>
-      <c r="T81" s="1" t="inlineStr">
+      <c r="W81" s="1" t="inlineStr">
         <is>
           <t>Fe+Ni+Co sum normalization to 100% (same DRS as spot protocol; mandatory for multi-phase mapping without prior IS knowledge)</t>
         </is>
       </c>
-      <c r="U81" s="1" t="inlineStr">
+      <c r="X81" s="1" t="inlineStr">
         <is>
           <t>Two internal standards: Si from XRF SiO₂ (for Co, Ni, Cu, Zn); Al from XRF Al₂O₃ (for all other trace elements); non-matrix-matched external standards (NIST 612 + 614) used; fs laser minimizes matrix effects</t>
         </is>
       </c>
-      <c r="V81" s="1" t="inlineStr">
+      <c r="Y81" s="1" t="inlineStr">
         <is>
           <t>Single element from EMP: Si (SiO₂ from EMP for silicate glass); NIST 610 as external standard</t>
         </is>
       </c>
-      <c r="W81" s="1" t="inlineStr">
+      <c r="Z81" s="1" t="inlineStr">
         <is>
           <t>Single element from EMP: Fe (FeOT from EMP for sulfide); NIST 610 as external standard</t>
         </is>
       </c>
-      <c r="X81" s="1" t="inlineStr">
+      <c r="AA81" s="1" t="inlineStr">
         <is>
           <t>Normalization to 100 wt% oxide total (for silicates and oxides) [P4]</t>
         </is>
       </c>
-      <c r="Y81" s="1" t="inlineStr">
+      <c r="AB81" s="1" t="inlineStr">
         <is>
           <t>Single element IS: EMP CaO concentration used; LA-ICP-MS 40Ca counts normalized to CaO from EMP analysis at the same spot [P4]</t>
         </is>
@@ -9061,68 +9867,78 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L82" s="9" t="n"/>
-      <c r="M82" s="1" t="inlineStr">
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:InternalStandardElement[]</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>property:internalStandardElement dataType: string readOnly: True</t>
+        </is>
+      </c>
+      <c r="O82" s="9" t="n"/>
+      <c r="P82" s="1" t="inlineStr">
         <is>
           <t>N (not stated in this paper; standardization follows Humayun (2012))</t>
         </is>
       </c>
-      <c r="N82" s="1" t="inlineStr">
+      <c r="Q82" s="1" t="inlineStr">
         <is>
           <t>No single IS element; oxide sum normalization (MgO+FeO+SiO₂+P₂O₅) used as virtual IS per pixel</t>
         </is>
       </c>
-      <c r="O82" s="1" t="inlineStr">
+      <c r="R82" s="1" t="inlineStr">
         <is>
           <t>Run 1: No single IS; oxide sum normalization; Run 2: ⁵³Cr (concentration from Run 1 major-element analysis on 30 µm spot used as IS for 130 µm spot trace element run)</t>
         </is>
       </c>
-      <c r="P82" s="1" t="inlineStr">
+      <c r="S82" s="1" t="inlineStr">
         <is>
           <t>No single IS; oxide sum normalization to 100 wt%</t>
         </is>
       </c>
-      <c r="Q82" s="1" t="inlineStr">
+      <c r="T82" s="1" t="inlineStr">
         <is>
           <t>²⁵Mg (indexing element; Mg concentration from EMPA)</t>
         </is>
       </c>
-      <c r="R82" s="1" t="inlineStr">
+      <c r="U82" s="1" t="inlineStr">
         <is>
           <t>⁶¹Ni; concentration from EPMA measured at exact analysis spot location</t>
         </is>
       </c>
-      <c r="S82" s="1" t="inlineStr">
+      <c r="V82" s="1" t="inlineStr">
         <is>
           <t>No single IS; Fe+Ni+Co mass fractions normalized to 100% via iolite 3D DRS (yield correction factors applied for NIST SRM 612 relative to North Chile)</t>
         </is>
       </c>
-      <c r="T82" s="1" t="inlineStr">
+      <c r="W82" s="1" t="inlineStr">
         <is>
           <t>No single IS; Fe+Ni+Co=100% normalization (same as spot protocol)</t>
         </is>
       </c>
-      <c r="U82" s="1" t="inlineStr">
+      <c r="X82" s="1" t="inlineStr">
         <is>
           <t>Si (SiO₂ from XRF) for Co, Ni, Cu, Zn; Al (Al₂O₃ from XRF) for all other 28 trace elements</t>
         </is>
       </c>
-      <c r="V82" s="1" t="inlineStr">
+      <c r="Y82" s="1" t="inlineStr">
         <is>
           <t>Si from EMP (SiO₂ wt% for silicate glass)</t>
         </is>
       </c>
-      <c r="W82" s="1" t="inlineStr">
+      <c r="Z82" s="1" t="inlineStr">
         <is>
           <t>Fe from EMP (FeOT wt% for sulfide)</t>
         </is>
       </c>
-      <c r="X82" s="1" t="inlineStr">
+      <c r="AA82" s="1" t="inlineStr">
         <is>
           <t>None (oxide sum normalization, 100 wt% total) [P4]</t>
         </is>
       </c>
-      <c r="Y82" s="1" t="inlineStr">
+      <c r="AB82" s="1" t="inlineStr">
         <is>
           <t>40Ca; CaO wt% from EMP at the analysis spot [P4]</t>
         </is>
@@ -9184,10 +10000,12 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L83" s="9" t="n"/>
-      <c r="M83" s="1" t="n"/>
-      <c r="N83" s="1" t="n"/>
-      <c r="O83" s="1" t="n"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>property:perAnalyteCalibrationStrategy dataType: string readOnly: True</t>
+        </is>
+      </c>
+      <c r="O83" s="9" t="n"/>
       <c r="P83" s="1" t="n"/>
       <c r="Q83" s="1" t="n"/>
       <c r="R83" s="1" t="n"/>
@@ -9198,6 +10016,9 @@
       <c r="W83" s="1" t="n"/>
       <c r="X83" s="1" t="n"/>
       <c r="Y83" s="1" t="n"/>
+      <c r="Z83" s="1" t="n"/>
+      <c r="AA83" s="1" t="n"/>
+      <c r="AB83" s="1" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -9247,68 +10068,78 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L84" s="9" t="n"/>
-      <c r="M84" s="1" t="inlineStr">
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:elementalFractionalCorretion</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>property:elementalFractionationCorrection dataType: string readOnly: True</t>
+        </is>
+      </c>
+      <c r="O84" s="9" t="n"/>
+      <c r="P84" s="1" t="inlineStr">
         <is>
           <t>Multi-point external calibration using series of iron meteorite reference materials (North Chile Filomena as primary standard for Fe/Co/Ni/Cu/Ga/Ge/As/W/Au; Hoba for Ru/Rh/Pd/Re/Os/Ir/Pt; NIST SRM 1263a V-Cr steel for V/Cr/Fe/Co/Ni/Cu/As/Mo/W/Au)</t>
         </is>
       </c>
-      <c r="N84" s="1" t="inlineStr">
+      <c r="Q84" s="1" t="inlineStr">
         <is>
           <t>Internal normalization to MgO+FeO+SiO₂+P₂O₅ oxide sum corrects for point-to-point ablation yield variation; additional pixel-by-pixel normalization fixes oxide sum to 100 wt%</t>
         </is>
       </c>
-      <c r="O84" s="1" t="inlineStr">
+      <c r="R84" s="1" t="inlineStr">
         <is>
           <t>Run 1: Oxide sum normalization corrects for ablation yield variation; external calibration using glass GRMs (NIST + USGS + MPI-DING); Run 2: Cr from run 1 as IS corrects for ablation yield; external calibration with expanded glass GRM set</t>
         </is>
       </c>
-      <c r="P84" s="1" t="inlineStr">
+      <c r="S84" s="1" t="inlineStr">
         <is>
           <t>Oxide sum normalization to 100 wt% corrects for ablation yield and matrix effects; external calibration with MPI-DING and USGS glass GRMs</t>
         </is>
       </c>
-      <c r="Q84" s="1" t="inlineStr">
+      <c r="T84" s="1" t="inlineStr">
         <is>
           <t>External calibration using BCR-2g, BHVO-2g, BIR-1g; ²⁵Mg IS from EPMA corrects for ablation yield variation; no explicit downhole fractionation correction described</t>
         </is>
       </c>
-      <c r="R84" s="1" t="inlineStr">
+      <c r="U84" s="1" t="inlineStr">
         <is>
           <t>External calibration using calibration curve method with IVB iron meteorite standards; ⁶¹Ni as IS from EPMA corrects for ablation yield differences between sample and standard</t>
         </is>
       </c>
-      <c r="S84" s="1" t="inlineStr">
+      <c r="V84" s="1" t="inlineStr">
         <is>
           <t>External calibration using North Chile iron meteorite + NIST SRM 612 glass (yield correction applied in iolite 3D DRS for NIST relative to North Chile); ordinary least-squares fitting per 15 min calibration block; Fe+Ni+Co normalization eliminates need for independent EPMA IS</t>
         </is>
       </c>
-      <c r="T84" s="1" t="inlineStr">
+      <c r="W84" s="1" t="inlineStr">
         <is>
           <t>Same calibration approach as spot protocol (iolite 3D DRS; same yield correction)</t>
         </is>
       </c>
-      <c r="U84" s="1" t="inlineStr">
+      <c r="X84" s="1" t="inlineStr">
         <is>
           <t>Femtosecond laser substantially reduces elemental fractionation and matrix effects (stated); non-matrix-matched external standards (NIST 612 + 614) used successfully with fs laser (verified by GRM accuracy assessment)</t>
         </is>
       </c>
-      <c r="V84" s="1" t="inlineStr">
+      <c r="Y84" s="1" t="inlineStr">
         <is>
           <t>Femtosecond laser reduces LIEF; NIST 610 external standard; Si IS from EMP corrects for ablation yield</t>
         </is>
       </c>
-      <c r="W84" s="1" t="inlineStr">
+      <c r="Z84" s="1" t="inlineStr">
         <is>
           <t>Femtosecond laser reduces LIEF; NIST 610 external standard; Fe IS from EMP corrects for ablation yield; micronuggets identified from Au signal spikes and excluded from integration</t>
         </is>
       </c>
-      <c r="X84" s="1" t="inlineStr">
+      <c r="AA84" s="1" t="inlineStr">
         <is>
           <t>External calibration using NIST 610 glass standard analyzed before and after session; oxide-sum normalization corrects for ablation yield variation; no explicit downhole fractionation correction described [P4]</t>
         </is>
       </c>
-      <c r="Y84" s="1" t="inlineStr">
+      <c r="AB84" s="1" t="inlineStr">
         <is>
           <t>External calibration using NIST 610; EMP CaO as IS corrects for ablation yield; no explicit downhole correction described [P4]</t>
         </is>
@@ -9362,68 +10193,81 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L85" s="9" t="n"/>
-      <c r="M85" s="1" t="inlineStr">
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>$.ada:methodParameters[]</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parameter: UncertaintyPropagationMethos
+  dataType:  schema:propertyValueSpecification
+  readOnly: False
+</t>
+        </is>
+      </c>
+      <c r="O85" s="9" t="n"/>
+      <c r="P85" s="1" t="inlineStr">
         <is>
           <t>Standard deviation (SD) across individual integration cycles of raster scans; uncertainty propagation not formally described</t>
         </is>
       </c>
-      <c r="N85" s="1" t="inlineStr">
+      <c r="Q85" s="1" t="inlineStr">
         <is>
           <t>Longerich et al. (1996) equation (3SD/S × √(1/Nb + 1/Na))</t>
         </is>
       </c>
-      <c r="O85" s="1" t="inlineStr">
+      <c r="R85" s="1" t="inlineStr">
         <is>
           <t>Longerich et al. (1996) for LOD; uncertainty for concentrations not formally described</t>
         </is>
       </c>
-      <c r="P85" s="1" t="inlineStr">
+      <c r="S85" s="1" t="inlineStr">
         <is>
           <t>Longerich et al. (1996) for LOD; uncertainty not formally described</t>
         </is>
       </c>
-      <c r="Q85" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="R85" s="1" t="inlineStr">
+      <c r="T85" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U85" s="1" t="inlineStr">
         <is>
           <t>2SE of individual spot measurements reported</t>
         </is>
       </c>
-      <c r="S85" s="1" t="inlineStr">
+      <c r="V85" s="1" t="inlineStr">
         <is>
           <t>N (iolite 4 computes uncertainty internally via Longerich et al. 1996)</t>
         </is>
       </c>
-      <c r="T85" s="1" t="inlineStr">
+      <c r="W85" s="1" t="inlineStr">
         <is>
           <t>N (same as spot protocol)</t>
         </is>
       </c>
-      <c r="U85" s="1" t="inlineStr">
+      <c r="X85" s="1" t="inlineStr">
         <is>
           <t>N (Iolite 4 internal uncertainty propagation implied)</t>
         </is>
       </c>
-      <c r="V85" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="W85" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="X85" s="1" t="inlineStr">
+      <c r="Y85" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z85" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA85" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
       </c>
-      <c r="Y85" s="1" t="inlineStr">
+      <c r="AB85" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
@@ -9477,68 +10321,81 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L86" s="9" t="n"/>
-      <c r="M86" s="1" t="inlineStr">
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>$.ada:methodParameters[]</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parameter: MatrixOffseCorrection
+  dataType:  schema:propertyValue
+  readOnly: True
+</t>
+        </is>
+      </c>
+      <c r="O86" s="9" t="n"/>
+      <c r="P86" s="1" t="inlineStr">
         <is>
           <t>N (no matrix offset correction; iron meteorite standards used to minimize matrix mismatch)</t>
         </is>
       </c>
-      <c r="N86" s="1" t="inlineStr">
+      <c r="Q86" s="1" t="inlineStr">
         <is>
           <t>N (oxide sum normalization approach is inherently matrix-independent within olivine composition range)</t>
         </is>
       </c>
-      <c r="O86" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P86" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q86" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="R86" s="1" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S86" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T86" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U86" s="1" t="inlineStr">
+        <is>
           <t>N (fs laser minimizes LIEF; IVB iron meteorite standards used as matrix-matched reference)</t>
         </is>
       </c>
-      <c r="S86" s="1" t="inlineStr">
+      <c r="V86" s="1" t="inlineStr">
         <is>
           <t>N (yield correction in iolite DRS addresses relative sensitivity differences between NIST SRM 612 and North Chile)</t>
         </is>
       </c>
-      <c r="T86" s="1" t="inlineStr">
+      <c r="W86" s="1" t="inlineStr">
         <is>
           <t>N (same as spot protocol)</t>
         </is>
       </c>
-      <c r="U86" s="1" t="inlineStr">
+      <c r="X86" s="1" t="inlineStr">
         <is>
           <t>N (fs laser minimizes matrix effects)</t>
         </is>
       </c>
-      <c r="V86" s="1" t="inlineStr">
+      <c r="Y86" s="1" t="inlineStr">
         <is>
           <t>N (fs laser)</t>
         </is>
       </c>
-      <c r="W86" s="1" t="inlineStr">
+      <c r="Z86" s="1" t="inlineStr">
         <is>
           <t>N (fs laser)</t>
         </is>
       </c>
-      <c r="X86" s="1" t="inlineStr">
+      <c r="AA86" s="1" t="inlineStr">
         <is>
           <t>N (not stated; agreement within &lt;10% between oxide-sum normalization and EMP-based IS noted as validation) [P4]</t>
         </is>
       </c>
-      <c r="Y86" s="1" t="inlineStr">
+      <c r="AB86" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
@@ -9592,68 +10449,78 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L87" s="9" t="n"/>
-      <c r="M87" s="1" t="inlineStr">
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:integrationIntrervalMethod</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>property:signalIntegrationIntervalMethod dataType: string readOnly: True</t>
+        </is>
+      </c>
+      <c r="O87" s="9" t="n"/>
+      <c r="P87" s="1" t="inlineStr">
         <is>
           <t>N (raster averages; selection method not described)</t>
         </is>
       </c>
-      <c r="N87" s="1" t="inlineStr">
+      <c r="Q87" s="1" t="inlineStr">
         <is>
           <t>Manual visual inspection of time-resolved signal per line; anomalous spikes (inclusions, cracks, veinlets) excluded; P-rich veinlet regions identified and excluded from olivine averages</t>
         </is>
       </c>
-      <c r="O87" s="1" t="inlineStr">
+      <c r="R87" s="1" t="inlineStr">
         <is>
           <t>Time-resolved signals inspected manually; unstable intervals at start and end discarded; Cr heterogeneities and inclusion signals (elevated P, Ca, Co, Ni) identified and excluded from integration</t>
         </is>
       </c>
-      <c r="P87" s="1" t="inlineStr">
+      <c r="S87" s="1" t="inlineStr">
         <is>
           <t>Anomalous time steps excluded (inclusions, cracks, heterogeneity); manual inspection</t>
         </is>
       </c>
-      <c r="Q87" s="1" t="inlineStr">
+      <c r="T87" s="1" t="inlineStr">
         <is>
           <t>Time steps with enhanced P, Ca, Co, Ni, Zn count rates (indicating inclusions or cracks) excluded from integration; manual inspection</t>
         </is>
       </c>
-      <c r="R87" s="1" t="inlineStr">
+      <c r="U87" s="1" t="inlineStr">
         <is>
           <t>Time-resolved signals monitored; analyses with elevated Mg, Si, P, S (inclusion indicators) excluded; stable signal intervals used for integration</t>
         </is>
       </c>
-      <c r="S87" s="1" t="inlineStr">
+      <c r="V87" s="1" t="inlineStr">
         <is>
           <t>Time-resolved LA-ICP-MS signals inspected per analysis; background interval (20 s) and ablation interval (40 s) selected; no automated spike exclusion described</t>
         </is>
       </c>
-      <c r="T87" s="1" t="inlineStr">
+      <c r="W87" s="1" t="inlineStr">
         <is>
           <t>Same procedure as spot protocol; signal integration for mapping not separately described</t>
         </is>
       </c>
-      <c r="U87" s="1" t="inlineStr">
+      <c r="X87" s="1" t="inlineStr">
         <is>
           <t>Time-resolved signals inspected visually; flux blank contributions to pollution elements (V, Co, Zn, Ba, La, Ce, Ta, U) identified and subtracted; 9-spot grid homogeneity tested before analysis</t>
         </is>
       </c>
-      <c r="V87" s="1" t="inlineStr">
+      <c r="Y87" s="1" t="inlineStr">
         <is>
           <t>Time-resolved LA-ICP-MS signal inspected; micronuggets identified from spikes in Au signal and excluded from integration to obtain smooth signals (verified by Fig. 1 in paper)</t>
         </is>
       </c>
-      <c r="W87" s="1" t="inlineStr">
+      <c r="Z87" s="1" t="inlineStr">
         <is>
           <t>Same approach as glass; micronugget identification from Au signal spikes critical for sulfide analyses</t>
         </is>
       </c>
-      <c r="X87" s="1" t="inlineStr">
+      <c r="AA87" s="1" t="inlineStr">
         <is>
           <t>Time-lapse plots of each spot examined; only the plateau region used to quantify trace element abundances [P4]</t>
         </is>
       </c>
-      <c r="Y87" s="1" t="inlineStr">
+      <c r="AB87" s="1" t="inlineStr">
         <is>
           <t>Time-lapse plots examined; only plateau region used (same as silicate protocol) [P4]</t>
         </is>
@@ -9707,68 +10574,78 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L88" s="9" t="n"/>
-      <c r="M88" s="1" t="inlineStr">
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>$Dataset.prov:wasGeneratedBy.schema:additionalProperty [name = 'SignalIntegrationTime'].schema:value</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>parameter:signalIntegrationTime dataType: number readOnly: False</t>
+        </is>
+      </c>
+      <c r="O88" s="9" t="n"/>
+      <c r="P88" s="1" t="inlineStr">
         <is>
           <t>N/A (mapping) / ~20 s (Ge spots: 20 s ablation at 50 Hz)</t>
         </is>
       </c>
-      <c r="N88" s="1" t="inlineStr">
+      <c r="Q88" s="1" t="inlineStr">
         <is>
           <t>N/A (mapping)</t>
         </is>
       </c>
-      <c r="O88" s="1" t="inlineStr">
+      <c r="R88" s="1" t="inlineStr">
         <is>
           <t>Run 1: ~50 s (34 runs covering 400 µm line + 10 s blank + washout); Run 2: same structure; actual integrated signal window within run not separately stated</t>
         </is>
       </c>
-      <c r="P88" s="1" t="inlineStr">
+      <c r="S88" s="1" t="inlineStr">
         <is>
           <t>20 s (spot ablation time; full ablation interval used for integration after exclusion of anomalous steps)</t>
         </is>
       </c>
-      <c r="Q88" s="1" t="inlineStr">
+      <c r="T88" s="1" t="inlineStr">
         <is>
           <t>N (parameters lost)</t>
         </is>
       </c>
-      <c r="R88" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="S88" s="1" t="inlineStr">
+      <c r="U88" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V88" s="1" t="inlineStr">
         <is>
           <t>40 s (full ablation interval used; background subtracted separately)</t>
         </is>
       </c>
-      <c r="T88" s="1" t="inlineStr">
+      <c r="W88" s="1" t="inlineStr">
         <is>
           <t>N/A (mapping)</t>
         </is>
       </c>
-      <c r="U88" s="1" t="inlineStr">
+      <c r="X88" s="1" t="inlineStr">
         <is>
           <t>45 s on-sample ablation (full ablation interval used for integration)</t>
         </is>
       </c>
-      <c r="V88" s="1" t="inlineStr">
+      <c r="Y88" s="1" t="inlineStr">
         <is>
           <t>~40 s (inferred from typical CetacAnalyte HE protocol; stable signal used)</t>
         </is>
       </c>
-      <c r="W88" s="1" t="inlineStr">
+      <c r="Z88" s="1" t="inlineStr">
         <is>
           <t>~40 s (same)</t>
         </is>
       </c>
-      <c r="X88" s="1" t="inlineStr">
+      <c r="AA88" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
       </c>
-      <c r="Y88" s="1" t="inlineStr">
+      <c r="AB88" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
@@ -9822,68 +10699,81 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L89" s="9" t="n"/>
-      <c r="M89" s="1" t="inlineStr">
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>$.ada:methodParameters[]</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parameter: OutlierFiltering
+  dataType:  schema:propertyValueSpecification
+  readOnly: False
+</t>
+        </is>
+      </c>
+      <c r="O89" s="9" t="n"/>
+      <c r="P89" s="1" t="inlineStr">
         <is>
           <t>N (raster scans; "failed to yield useful Ge abundances" for Klamath Falls noted — implying visual quality control)</t>
         </is>
       </c>
-      <c r="N89" s="1" t="inlineStr">
+      <c r="Q89" s="1" t="inlineStr">
         <is>
           <t>Manual identification and exclusion of P-rich veinlet pixels from olivine averages; anomalous spikes from inclusions excluded per line</t>
         </is>
       </c>
-      <c r="O89" s="1" t="inlineStr">
+      <c r="R89" s="1" t="inlineStr">
         <is>
           <t>Manual inspection; analyses with elevated P, Ca, Co, Ni (phosphate or metal inclusions) excluded; Cr heterogeneities also flagged</t>
         </is>
       </c>
-      <c r="P89" s="1" t="inlineStr">
+      <c r="S89" s="1" t="inlineStr">
         <is>
           <t>Anomalous time steps excluded during manual inspection</t>
         </is>
       </c>
-      <c r="Q89" s="1" t="inlineStr">
+      <c r="T89" s="1" t="inlineStr">
         <is>
           <t>Time steps with enhanced P, Ca, Co, Ni, Zn excluded (inclusions and heterogeneities); Grubb's test applied to EPMA data for outlier detection</t>
         </is>
       </c>
-      <c r="R89" s="1" t="inlineStr">
+      <c r="U89" s="1" t="inlineStr">
         <is>
           <t>Monitoring of Mg, Si, P, S to check for micro-inclusions (sulfides); analyses with elevated inclusion signals excluded entirely</t>
         </is>
       </c>
-      <c r="S89" s="1" t="inlineStr">
+      <c r="V89" s="1" t="inlineStr">
         <is>
           <t>N (no explicit spike filtering described beyond background subtraction)</t>
         </is>
       </c>
-      <c r="T89" s="1" t="inlineStr">
+      <c r="W89" s="1" t="inlineStr">
         <is>
           <t>N (mapping; iolite 3D DRS handles background; no per-pixel spike filtering described)</t>
         </is>
       </c>
-      <c r="U89" s="1" t="inlineStr">
+      <c r="X89" s="1" t="inlineStr">
         <is>
           <t>Homogeneity index (H) applied to test element distribution; Co, Ni, Cu in high-Si glass (GSR-1) identified as near-LOD and flagged; flux blank contributions to pollution elements subtracted</t>
         </is>
       </c>
-      <c r="V89" s="1" t="inlineStr">
+      <c r="Y89" s="1" t="inlineStr">
         <is>
           <t>Micronuggets identified from Au signal spikes in time-resolved spectra; excluded from integration (smooth signals = fully dissolved Au; Fig. 1 shows this criterion)</t>
         </is>
       </c>
-      <c r="W89" s="1" t="inlineStr">
+      <c r="Z89" s="1" t="inlineStr">
         <is>
           <t>Same approach as glass; Au spike identification critical for determining solubility vs. nugget contribution</t>
         </is>
       </c>
-      <c r="X89" s="1" t="inlineStr">
+      <c r="AA89" s="1" t="inlineStr">
         <is>
           <t>N (not explicitly stated; implied by plateau-region selection excluding non-stable intervals) [P4]</t>
         </is>
       </c>
-      <c r="Y89" s="1" t="inlineStr">
+      <c r="AB89" s="1" t="inlineStr">
         <is>
           <t>N (same as silicate protocol) [P4]</t>
         </is>
@@ -9937,68 +10827,78 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L90" s="9" t="n"/>
-      <c r="M90" s="1" t="inlineStr">
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:backgrounCorrection</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>property:blankBackgroundCorrectionMethod dataType: string readOnly: True</t>
+        </is>
+      </c>
+      <c r="O90" s="9" t="n"/>
+      <c r="P90" s="1" t="inlineStr">
         <is>
           <t>Gas blank measured before each raster analysis; mean background subtracted</t>
         </is>
       </c>
-      <c r="N90" s="1" t="inlineStr">
+      <c r="Q90" s="1" t="inlineStr">
         <is>
           <t>Gas blank measured before each ablation line (10 scans of gas blank per mapping line); average background subtracted from each corresponding ablation line</t>
         </is>
       </c>
-      <c r="O90" s="1" t="inlineStr">
+      <c r="R90" s="1" t="inlineStr">
         <is>
           <t>Gas blank measured before each analysis (5 scans); average background value preceding each analysis subtracted from corresponding data</t>
         </is>
       </c>
-      <c r="P90" s="1" t="inlineStr">
+      <c r="S90" s="1" t="inlineStr">
         <is>
           <t>Gas blank measured before each spot analysis (8 scans); average background subtracted</t>
         </is>
       </c>
-      <c r="Q90" s="1" t="inlineStr">
+      <c r="T90" s="1" t="inlineStr">
         <is>
           <t>Gas blank measured before each analysis (laser shutter closed); time steps with background-level signals excluded during data reduction</t>
         </is>
       </c>
-      <c r="R90" s="1" t="inlineStr">
+      <c r="U90" s="1" t="inlineStr">
         <is>
           <t>Gas blank measured before each spot; background period during single spot transient (rapid intensity rise and decay) used for background correction</t>
         </is>
       </c>
-      <c r="S90" s="1" t="inlineStr">
+      <c r="V90" s="1" t="inlineStr">
         <is>
           <t>Background signal measured for 20 s (laser shutter closed) before each 40 s ablation; background mean subtracted per isotope in iolite</t>
         </is>
       </c>
-      <c r="T90" s="1" t="inlineStr">
+      <c r="W90" s="1" t="inlineStr">
         <is>
           <t>Background (1 min) measured at session start; additional 3 measurements of NIST and North Chile used for calibration (background included in regression line for gas blank)</t>
         </is>
       </c>
-      <c r="U90" s="1" t="inlineStr">
+      <c r="X90" s="1" t="inlineStr">
         <is>
           <t>Gas blank measured for 25 s before each ablation; background subtracted per isotope</t>
         </is>
       </c>
-      <c r="V90" s="1" t="inlineStr">
+      <c r="Y90" s="1" t="inlineStr">
         <is>
           <t>N (background subtraction performed but method not explicitly described; implied from standard Agilent/iolite workflow)</t>
         </is>
       </c>
-      <c r="W90" s="1" t="inlineStr">
+      <c r="Z90" s="1" t="inlineStr">
         <is>
           <t>N (same as glass protocol)</t>
         </is>
       </c>
-      <c r="X90" s="1" t="inlineStr">
+      <c r="AA90" s="1" t="inlineStr">
         <is>
           <t>50 s background measurement before each analysis; background subtracted (method not explicitly described beyond counting duration) [P4]</t>
         </is>
       </c>
-      <c r="Y90" s="1" t="inlineStr">
+      <c r="AB90" s="1" t="inlineStr">
         <is>
           <t>50 s background measurement before each analysis (same as silicate protocol) [P4]</t>
         </is>
@@ -10056,68 +10956,81 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L91" s="9" t="n"/>
-      <c r="M91" s="1" t="inlineStr">
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>$.ada:methodParameters[]</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parameter: NonlineraResponseCorrection
+  dataType:  schema:propertyValueSpecification
+  readOnly: False
+</t>
+        </is>
+      </c>
+      <c r="O91" s="9" t="n"/>
+      <c r="P91" s="1" t="inlineStr">
         <is>
           <t>Applied: triple mode detection at 65% duty cycle (pulse counting + analog + Faraday); specific cross-calibration not described</t>
         </is>
       </c>
-      <c r="N91" s="1" t="inlineStr">
+      <c r="Q91" s="1" t="inlineStr">
         <is>
           <t>Applied: triple mode detection; cross-calibration between pulse-counting and analog modes performed</t>
         </is>
       </c>
-      <c r="O91" s="1" t="inlineStr">
+      <c r="R91" s="1" t="inlineStr">
         <is>
           <t>Applied: Run 1 medium resolution with Faraday for major elements; Run 2 low resolution; cross-calibration performed</t>
         </is>
       </c>
-      <c r="P91" s="1" t="inlineStr">
+      <c r="S91" s="1" t="inlineStr">
         <is>
           <t>Applied: triple mode detection</t>
         </is>
       </c>
-      <c r="Q91" s="1" t="inlineStr">
+      <c r="T91" s="1" t="inlineStr">
         <is>
           <t>N (parameters lost)</t>
         </is>
       </c>
-      <c r="R91" s="1" t="inlineStr">
+      <c r="U91" s="1" t="inlineStr">
         <is>
           <t>N (quadrupole X-series 2; single detector mode)</t>
         </is>
       </c>
-      <c r="S91" s="1" t="inlineStr">
+      <c r="V91" s="1" t="inlineStr">
         <is>
           <t>Applied: triple mode detector (pulse counting, analog, Faraday); low relative abundance isotopes chosen for Ni and Fe to allow analog mode measurement of major matrix elements</t>
         </is>
       </c>
-      <c r="T91" s="1" t="inlineStr">
+      <c r="W91" s="1" t="inlineStr">
         <is>
           <t>Applied (same as spot)</t>
         </is>
       </c>
-      <c r="U91" s="1" t="inlineStr">
+      <c r="X91" s="1" t="inlineStr">
         <is>
           <t>Applied: dual detector mode (30 ms / 10 ms dwell alternation)</t>
         </is>
       </c>
-      <c r="V91" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="W91" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="X91" s="1" t="inlineStr">
+      <c r="Y91" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z91" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA91" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
       </c>
-      <c r="Y91" s="1" t="inlineStr">
+      <c r="AB91" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
@@ -10179,68 +11092,85 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L92" s="9" t="n"/>
-      <c r="M92" s="1" t="inlineStr">
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>$.ada:analyteTemplate.ada:analyteColumns[]</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Items marked 'Analyte Specific' in column G of this table become entries in the ada:analyteColumns Array.  </t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>analyteColumn: IsobaricInterferenceCorrection 
+  datatype: Boolean
+  readOnly:True</t>
+        </is>
+      </c>
+      <c r="O92" s="9" t="n"/>
+      <c r="P92" s="1" t="inlineStr">
         <is>
           <t>Yes — ⁹⁹Ru used instead of ¹⁰¹Ru to avoid ⁴⁰Ar⁶¹Ni⁺ interference; isotope selection minimizes other interferences</t>
         </is>
       </c>
-      <c r="N92" s="1" t="inlineStr">
+      <c r="Q92" s="1" t="inlineStr">
         <is>
           <t>Yes — cool plasma conditions (800 W) applied to reduce argide-based interferences (³⁶Ar²⁴Mg⁺ on ⁶⁰Ni; ⁴⁰Ar³¹P⁺ on ⁷¹Ga); oxide-based interferences minimized by dry plasma and tuning; mathematical corrections in some cases (Table C1)</t>
         </is>
       </c>
-      <c r="O92" s="1" t="inlineStr">
+      <c r="R92" s="1" t="inlineStr">
         <is>
           <t>Yes — cool plasma not applicable (normal plasma); argide corrections less critical; oxide interferences monitored; spectral interference list in Table C1</t>
         </is>
       </c>
-      <c r="P92" s="1" t="inlineStr">
+      <c r="S92" s="1" t="inlineStr">
         <is>
           <t>Yes — same instrument settings; interference corrections as per Table C1</t>
         </is>
       </c>
-      <c r="Q92" s="1" t="inlineStr">
+      <c r="T92" s="1" t="inlineStr">
         <is>
           <t>N (parameters lost; medium resolution mode implies interference resolution by mass)</t>
         </is>
       </c>
-      <c r="R92" s="1" t="inlineStr">
+      <c r="U92" s="1" t="inlineStr">
         <is>
           <t>No explicit corrections applied; monitoring of Mg, Si, P, S used to detect and exclude inclusion-contaminated analyses rather than correct for spectral interferences</t>
         </is>
       </c>
-      <c r="S92" s="1" t="inlineStr">
+      <c r="V92" s="1" t="inlineStr">
         <is>
           <t>Yes — isotope selection to minimize interferences (e.g., ⁹⁹Ru instead of ¹⁰¹Ru to avoid ⁴⁰Ar⁶¹Ni⁺; low abundance isotopes for Fe and Ni)</t>
         </is>
       </c>
-      <c r="T92" s="1" t="inlineStr">
+      <c r="W92" s="1" t="inlineStr">
         <is>
           <t>Yes (same as spot protocol)</t>
         </is>
       </c>
-      <c r="U92" s="1" t="inlineStr">
+      <c r="X92" s="1" t="inlineStr">
         <is>
           <t>Yes — fs laser substantially reduces oxide and matrix interferences; flux blank contributions to V, Co, Zn, Ba, La, Ce, Ta, U identified and subtracted</t>
         </is>
       </c>
-      <c r="V92" s="1" t="inlineStr">
+      <c r="Y92" s="1" t="inlineStr">
         <is>
           <t>Yes (fs laser reduces interferences)</t>
         </is>
       </c>
-      <c r="W92" s="1" t="inlineStr">
+      <c r="Z92" s="1" t="inlineStr">
         <is>
           <t>Yes (fs laser reduces interferences)</t>
         </is>
       </c>
-      <c r="X92" s="1" t="inlineStr">
+      <c r="AA92" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
       </c>
-      <c r="Y92" s="1" t="inlineStr">
+      <c r="AB92" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
@@ -10302,68 +11232,85 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L93" s="9" t="n"/>
-      <c r="M93" s="1" t="inlineStr">
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>$.ada:analyteTemplate.ada:analyteColumns[]</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>value is a list of analytes</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>analyteColumn: interferingSpecies 
+  datatype: 
+  readOnly:True</t>
+        </is>
+      </c>
+      <c r="O93" s="9" t="n"/>
+      <c r="P93" s="1" t="inlineStr">
         <is>
           <t>⁴⁰Ar⁶¹Ni⁺ on ¹⁰¹Ru (most abundant Ru isotope → use ⁹⁹Ru instead)</t>
         </is>
       </c>
-      <c r="N93" s="1" t="inlineStr">
+      <c r="Q93" s="1" t="inlineStr">
         <is>
           <t>Per Table C1: ¹²C¹³C⁺ on ²⁵Mg; ¹⁵N¹⁶O⁺ on ³¹P; ²⁹Si¹⁶O⁺ on ⁴⁵Sc; ³⁵Cl¹⁶O⁺ on ⁵¹V; ⁴⁰Ar¹³C⁺ on ⁵³Cr; ⁴⁰Ar¹⁵N⁺ on ⁵⁵Mn; ⁴⁰Ar¹⁶OH⁺ on ⁵⁷Fe; ⁴⁴Ca¹⁶O⁺ and ²⁴Mg³⁶Ar⁺ on ⁶⁰Ni; ³¹P⁴⁰Ar⁺ and ⁵⁵Mn¹⁶O⁺ on ⁷¹Ga; ¹³⁷Ba¹⁶O⁺ on ¹⁵³Eu (most significant interferences in bold)</t>
         </is>
       </c>
-      <c r="O93" s="1" t="inlineStr">
+      <c r="R93" s="1" t="inlineStr">
         <is>
           <t>Same interference list as mapping (Table C1); argide-based interferences less critical without cool plasma</t>
         </is>
       </c>
-      <c r="P93" s="1" t="inlineStr">
+      <c r="S93" s="1" t="inlineStr">
         <is>
           <t>Same interference list (Table C1)</t>
         </is>
       </c>
-      <c r="Q93" s="1" t="inlineStr">
+      <c r="T93" s="1" t="inlineStr">
         <is>
           <t>N (parameters lost; medium resolution resolves most polyatomic interferences)</t>
         </is>
       </c>
-      <c r="R93" s="1" t="inlineStr">
+      <c r="U93" s="1" t="inlineStr">
         <is>
           <t>Sulfide inclusions detectable via ³³S signal; phosphide inclusions via ³¹P; silicate inclusions via ²⁴Mg, ²⁹Si (used to exclude contaminated analyses)</t>
         </is>
       </c>
-      <c r="S93" s="1" t="inlineStr">
+      <c r="V93" s="1" t="inlineStr">
         <is>
           <t>⁴⁰Ar⁶¹Ni⁺ on ¹⁰¹Ru (primary concern) → ⁹⁹Ru used instead; Fe and Ni matrix species on other isotopes minimized by isotope selection</t>
         </is>
       </c>
-      <c r="T93" s="1" t="inlineStr">
+      <c r="W93" s="1" t="inlineStr">
         <is>
           <t>Same as spot protocol</t>
         </is>
       </c>
-      <c r="U93" s="1" t="inlineStr">
+      <c r="X93" s="1" t="inlineStr">
         <is>
           <t>Li₂B₄O₇ flux blank contains V, Co, Zn, Ba, La, Ce, Ta, U at detectable levels; subtracted as blank contribution</t>
         </is>
       </c>
-      <c r="V93" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="W93" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="X93" s="1" t="inlineStr">
+      <c r="Y93" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z93" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA93" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
       </c>
-      <c r="Y93" s="1" t="inlineStr">
+      <c r="AB93" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
@@ -10425,68 +11372,80 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L94" s="9" t="n"/>
-      <c r="M94" s="1" t="inlineStr">
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>$.ada:analyteTemplate.ada:analyteColumns[]</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>analyteColumn: IsobaricInterferenceCorrectionMethod 
+  datatype: Text
+  readOnly:false</t>
+        </is>
+      </c>
+      <c r="O94" s="9" t="n"/>
+      <c r="P94" s="1" t="inlineStr">
         <is>
           <t>Isotope selection: ⁹⁹Ru chosen over ¹⁰¹Ru; other isotopes chosen to minimize interference</t>
         </is>
       </c>
-      <c r="N94" s="1" t="inlineStr">
+      <c r="Q94" s="1" t="inlineStr">
         <is>
           <t>Physical mitigation: cool plasma (800 W RF) reduces ³⁶Ar²⁴Mg⁺ on ⁶⁰Ni, ⁴⁰Ar³¹P⁺ on ⁷¹Ga by &gt;90%; oxide interferences minimized by dry plasma conditions; background subtraction corrects for time-invariant Ar-based interferences; mathematical corrections applied where feasible per Appendix C4</t>
         </is>
       </c>
-      <c r="O94" s="1" t="inlineStr">
+      <c r="R94" s="1" t="inlineStr">
         <is>
           <t>Argide corrections less critical (normal plasma); oxide-based interferences minimized by tuning; same interference list but without cool plasma mitigation</t>
         </is>
       </c>
-      <c r="P94" s="1" t="inlineStr">
+      <c r="S94" s="1" t="inlineStr">
         <is>
           <t>Same approach as mapping; oxide sum normalization partially corrects for matrix-dependent interferences</t>
         </is>
       </c>
-      <c r="Q94" s="1" t="inlineStr">
+      <c r="T94" s="1" t="inlineStr">
         <is>
           <t>Medium mass resolution (M/ΔM ≈ 4000) separates many polyatomic interferences from analyte peaks (e.g., resolves ⁵⁴Fe⁺ from ⁵⁴Cr⁺)</t>
         </is>
       </c>
-      <c r="R94" s="1" t="inlineStr">
+      <c r="U94" s="1" t="inlineStr">
         <is>
           <t>Exclusion-based approach: analyses with elevated Mg, Si, P, S (from silicate, phosphate, or sulfide inclusions) excluded entirely rather than applying mathematical corrections</t>
         </is>
       </c>
-      <c r="S94" s="1" t="inlineStr">
+      <c r="V94" s="1" t="inlineStr">
         <is>
           <t>Isotope selection minimizes interferences; low-abundance isotopes of Fe and Ni chosen for analog mode to prevent detector saturation</t>
         </is>
       </c>
-      <c r="T94" s="1" t="inlineStr">
+      <c r="W94" s="1" t="inlineStr">
         <is>
           <t>Same isotope selection as spot protocol</t>
         </is>
       </c>
-      <c r="U94" s="1" t="inlineStr">
+      <c r="X94" s="1" t="inlineStr">
         <is>
           <t>Flux blank subtraction: blank contribution to each pollution element (V, Co, Zn, Ba, La, Ce, Ta, U) measured in procedure blanks and subtracted; LOQ for pollution elements = blank value + 10SD</t>
         </is>
       </c>
-      <c r="V94" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="W94" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="X94" s="1" t="inlineStr">
+      <c r="Y94" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z94" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA94" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
       </c>
-      <c r="Y94" s="1" t="inlineStr">
+      <c r="AB94" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
@@ -10540,68 +11499,81 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L95" s="9" t="n"/>
-      <c r="M95" s="1" t="inlineStr">
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>$.ada:methodParameters[]</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parameter: MemoryEffectMitigation
+  dataType:  schema:propertyValueSpecification
+  readOnly: False
+</t>
+        </is>
+      </c>
+      <c r="O95" s="9" t="n"/>
+      <c r="P95" s="1" t="inlineStr">
         <is>
           <t>N (washout time between analyses not stated; sequential raster scans)</t>
         </is>
       </c>
-      <c r="N95" s="1" t="inlineStr">
+      <c r="Q95" s="1" t="inlineStr">
         <is>
           <t>Gas blank measured before each ablation line; adequate washout ensured by duty cycle timing</t>
         </is>
       </c>
-      <c r="O95" s="1" t="inlineStr">
+      <c r="R95" s="1" t="inlineStr">
         <is>
           <t>Washout time: 11 s between runs (runs include 400 µm line + blank + washout)</t>
         </is>
       </c>
-      <c r="P95" s="1" t="inlineStr">
+      <c r="S95" s="1" t="inlineStr">
         <is>
           <t>10 s washout time after 20 s spot ablation (specified in acquisition protocol)</t>
         </is>
       </c>
-      <c r="Q95" s="1" t="inlineStr">
+      <c r="T95" s="1" t="inlineStr">
         <is>
           <t>N (parameters lost)</t>
         </is>
       </c>
-      <c r="R95" s="1" t="inlineStr">
+      <c r="U95" s="1" t="inlineStr">
         <is>
           <t>N (single spot analyses; no sequential memory effect described)</t>
         </is>
       </c>
-      <c r="S95" s="1" t="inlineStr">
+      <c r="V95" s="1" t="inlineStr">
         <is>
           <t>N (washout between analyses not explicitly described; sequential spot analyses)</t>
         </is>
       </c>
-      <c r="T95" s="1" t="inlineStr">
+      <c r="W95" s="1" t="inlineStr">
         <is>
           <t>N (mapping; ARIS-equivalent not described; single mapping session)</t>
         </is>
       </c>
-      <c r="U95" s="1" t="inlineStr">
+      <c r="X95" s="1" t="inlineStr">
         <is>
           <t>25 s washout between analyses (25 s gas blank → 45 s ablation → 25 s washout)</t>
         </is>
       </c>
-      <c r="V95" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="W95" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="X95" s="1" t="inlineStr">
+      <c r="Y95" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z95" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA95" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
       </c>
-      <c r="Y95" s="1" t="inlineStr">
+      <c r="AB95" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
@@ -10655,68 +11627,81 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L96" s="9" t="n"/>
-      <c r="M96" s="1" t="inlineStr">
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>$.ada:methodParameters[]</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parameter: postAcquisitionNormalization
+  dataType:  schema:propertyValueSpecification
+  readOnly: False
+</t>
+        </is>
+      </c>
+      <c r="O96" s="9" t="n"/>
+      <c r="P96" s="1" t="inlineStr">
         <is>
           <t>External calibration with iron meteorite and NIST SRM 1263a V-Cr steel standards; no post-acquisition normalization described</t>
         </is>
       </c>
-      <c r="N96" s="1" t="inlineStr">
+      <c r="Q96" s="1" t="inlineStr">
         <is>
           <t>100% oxide sum normalization (MgO+FeO+SiO₂+P₂O₅) applied per pixel after IS-normalized external calibration (equations 3–4 in Appendix C1) to fix final mass balance</t>
         </is>
       </c>
-      <c r="O96" s="1" t="inlineStr">
+      <c r="R96" s="1" t="inlineStr">
         <is>
           <t>Run 1: 100% oxide sum normalization; Run 2: Cr IS from Run 1 applied; no further post-acquisition normalization</t>
         </is>
       </c>
-      <c r="P96" s="1" t="inlineStr">
+      <c r="S96" s="1" t="inlineStr">
         <is>
           <t>100% oxide sum normalization to 100 wt% for phosphate minerals (Appendix C3)</t>
         </is>
       </c>
-      <c r="Q96" s="1" t="inlineStr">
+      <c r="T96" s="1" t="inlineStr">
         <is>
           <t>No post-acquisition normalization; BCR-2g, BHVO-2g, BIR-1g used for calibration; Marjalahti as in-session control</t>
         </is>
       </c>
-      <c r="R96" s="1" t="inlineStr">
+      <c r="U96" s="1" t="inlineStr">
         <is>
           <t>No post-acquisition normalization; calibration curve method using IVB standards provides direct quantification</t>
         </is>
       </c>
-      <c r="S96" s="1" t="inlineStr">
+      <c r="V96" s="1" t="inlineStr">
         <is>
           <t>Fe+Ni+Co=100% sum normalization applied in iolite 3D Trace Elements DRS as final step; yield correction factors applied for NIST SRM 612 relative to North Chile</t>
         </is>
       </c>
-      <c r="T96" s="1" t="inlineStr">
+      <c r="W96" s="1" t="inlineStr">
         <is>
           <t>Fe+Ni+Co=100% normalization (mandatory for multi-phase mapping); same iolite DRS as spot</t>
         </is>
       </c>
-      <c r="U96" s="1" t="inlineStr">
+      <c r="X96" s="1" t="inlineStr">
         <is>
           <t>No post-acquisition normalization beyond IS approach (two IS elements applied element-specifically)</t>
         </is>
       </c>
-      <c r="V96" s="1" t="inlineStr">
+      <c r="Y96" s="1" t="inlineStr">
         <is>
           <t>No post-acquisition normalization beyond IS (Si from EMP)</t>
         </is>
       </c>
-      <c r="W96" s="1" t="inlineStr">
+      <c r="Z96" s="1" t="inlineStr">
         <is>
           <t>No post-acquisition normalization beyond IS (Fe from EMP)</t>
         </is>
       </c>
-      <c r="X96" s="1" t="inlineStr">
+      <c r="AA96" s="1" t="inlineStr">
         <is>
           <t>100% oxide total normalization applied per analysis for silicates and oxides; NIST 610 used for external calibration before and after session [P4]</t>
         </is>
       </c>
-      <c r="Y96" s="1" t="inlineStr">
+      <c r="AB96" s="1" t="inlineStr">
         <is>
           <t>No post-acquisition normalization; EMP CaO applied directly as IS; NIST 610 for external calibration [P4]</t>
         </is>
@@ -10739,9 +11724,6 @@
       <c r="I98" s="5" t="n"/>
       <c r="J98" s="5" t="n"/>
       <c r="K98" s="5" t="n"/>
-      <c r="L98" s="5" t="n"/>
-      <c r="M98" s="5" t="n"/>
-      <c r="N98" s="5" t="n"/>
       <c r="O98" s="5" t="n"/>
       <c r="P98" s="5" t="n"/>
       <c r="Q98" s="5" t="n"/>
@@ -10751,12 +11733,15 @@
       <c r="U98" s="5" t="n"/>
       <c r="V98" s="5" t="n"/>
       <c r="W98" s="5" t="n"/>
-      <c r="X98" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Y98" s="5" t="inlineStr">
+      <c r="X98" s="5" t="n"/>
+      <c r="Y98" s="5" t="n"/>
+      <c r="Z98" s="5" t="n"/>
+      <c r="AA98" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB98" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -10810,68 +11795,83 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L99" s="9" t="n"/>
-      <c r="M99" s="1" t="inlineStr">
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:calibrationStandardName</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>property:primaryCalibrationStandardNameDefault dataType: string readOnly: False</t>
+        </is>
+      </c>
+      <c r="O99" s="9" t="n"/>
+      <c r="P99" s="1" t="inlineStr">
         <is>
           <t>North Chile Filomena (IIAB iron meteorite; Wasson et al. 1989) for Fe/Co/Ni/Cu/Ga/Ge/As/W/Au; Hoba (IVB; Walker et al. 2008) for Ru/Rh/Pd/Re/Os/Ir/Pt; NIST SRM 1263a V-Cr steel (Campbell &amp; Humayun 2005) for V/Cr/Fe/Co/Ni/Cu/As/Mo/W/Au</t>
         </is>
       </c>
-      <c r="N99" s="1" t="inlineStr">
+      <c r="Q99" s="1" t="inlineStr">
         <is>
           <t>Multiple glass GRMs used together for linear regression external calibration: NIST SRM 612, NIST SRM 614, USGS GSD-1G (synthetic), USGS GSE-1G (synthetic), USGS BHVO-2G, USGS BIR-1G (natural basalt glasses)</t>
         </is>
       </c>
-      <c r="O99" s="1" t="inlineStr">
+      <c r="R99" s="1" t="inlineStr">
         <is>
           <t>Same glass GRM set as mapping for Run 1; expanded set additionally includes MPI-DING KL2-G, ML3B-G, StHs6/80-G, T1-G, ATHO-G, BM90/21-G, GOR128-G, GOR132-G for Run 2 trace elements</t>
         </is>
       </c>
-      <c r="P99" s="1" t="inlineStr">
+      <c r="S99" s="1" t="inlineStr">
         <is>
           <t>MPI-DING and USGS glass GRMs (measured at beginning and repeatedly at end of each session; multipoint calibration)</t>
         </is>
       </c>
-      <c r="Q99" s="1" t="inlineStr">
+      <c r="T99" s="1" t="inlineStr">
         <is>
           <t>USGS standard glasses BCR-2g, BHVO-2g, and BIR-1g; preferred values from GeoReM website</t>
         </is>
       </c>
-      <c r="R99" s="1" t="inlineStr">
+      <c r="U99" s="1" t="inlineStr">
         <is>
           <t>Warburton Range (IVB iron meteorite; Walker et al. 2008) — used as primary external standard and for calibration curve method</t>
         </is>
       </c>
-      <c r="S99" s="1" t="inlineStr">
+      <c r="V99" s="1" t="inlineStr">
         <is>
           <t>NIST SRM 612 glass (Jochum et al. 2011) + North Chile Filomena iron meteorite (Wasson et al. 1989) — used together with yield correction in iolite 3D DRS</t>
         </is>
       </c>
-      <c r="T99" s="1" t="inlineStr">
+      <c r="W99" s="1" t="inlineStr">
         <is>
           <t>NIST SRM 612 (Jochum et al. 2011) + North Chile Filomena — same as spot protocol</t>
         </is>
       </c>
-      <c r="U99" s="1" t="inlineStr">
+      <c r="X99" s="1" t="inlineStr">
         <is>
           <t>NIST SRM 612 + NIST SRM 614 (non-matrix-matched external standards); self-made BHVO-2 lithium borate glass (matrix-matched) tested as alternative but NIST 612+614 found sufficient with fs laser</t>
         </is>
       </c>
-      <c r="V99" s="1" t="inlineStr">
+      <c r="Y99" s="1" t="inlineStr">
         <is>
           <t>NIST 610 (primary external standard; Jochum et al. 2011); Si from EMP as IS</t>
         </is>
       </c>
-      <c r="W99" s="1" t="inlineStr">
+      <c r="Z99" s="1" t="inlineStr">
         <is>
           <t>NIST 610 (primary external standard); Fe from EMP as IS</t>
         </is>
       </c>
-      <c r="X99" s="1" t="inlineStr">
+      <c r="AA99" s="1" t="inlineStr">
         <is>
           <t>NIST 610 glass standard [P4]</t>
         </is>
       </c>
-      <c r="Y99" s="1" t="inlineStr">
+      <c r="AB99" s="1" t="inlineStr">
         <is>
           <t>NIST 610 glass standard [P4]</t>
         </is>
@@ -10929,68 +11929,83 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L100" s="9" t="n"/>
-      <c r="M100" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N100" s="1" t="inlineStr">
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>$MethodDefinition.ada:secondaryReferenceMaterial</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>property:secondaryReferenceMaterialsDefault dataType: string readOnly: False</t>
+        </is>
+      </c>
+      <c r="O100" s="9" t="n"/>
+      <c r="P100" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q100" s="1" t="inlineStr">
         <is>
           <t>MPI-DING glasses: GOR132-G, StHs6/80-G, T1-G; USGS: BCR-2G, BHVO-2G — measured as unknowns alongside samples and compared to GeoReM preferred values (Table 1 and Section 3.3)</t>
         </is>
       </c>
-      <c r="O100" s="1" t="inlineStr">
+      <c r="R100" s="1" t="inlineStr">
         <is>
           <t>Same GRM set measured as unknowns for accuracy assessment</t>
         </is>
       </c>
-      <c r="P100" s="1" t="inlineStr">
+      <c r="S100" s="1" t="inlineStr">
         <is>
           <t>Same MPI-DING and USGS glasses measured as unknowns for accuracy assessment</t>
         </is>
       </c>
-      <c r="Q100" s="1" t="inlineStr">
+      <c r="T100" s="1" t="inlineStr">
         <is>
           <t>BCR-2G, BHVO-2G, BIR-1G processed as unknowns alongside samples (same standards as calibration — in-session validation)</t>
         </is>
       </c>
-      <c r="R100" s="1" t="inlineStr">
+      <c r="U100" s="1" t="inlineStr">
         <is>
           <t>Tawallah Valley (IVB iron meteorite; Walker et al. 2008) — measured as secondary/check standard alongside unknowns</t>
         </is>
       </c>
-      <c r="S100" s="1" t="inlineStr">
+      <c r="V100" s="1" t="inlineStr">
         <is>
           <t>North Chile Filomena measured as unknown on different days over 4 months to assess intermediate precision (Table 3 and Fig. 2)</t>
         </is>
       </c>
-      <c r="T100" s="1" t="inlineStr">
+      <c r="W100" s="1" t="inlineStr">
         <is>
           <t>North Chile and NIST SRM 612 measured before and after mapping session as QC materials</t>
         </is>
       </c>
-      <c r="U100" s="1" t="inlineStr">
+      <c r="X100" s="1" t="inlineStr">
         <is>
           <t>AC-E (granite, CRPG), GSR-1 (granite, NRCG), JB-1b (basalt, GSJ), GSR-3 (basalt, NRCG), AGV-2 (andesite, USGS), W-2A (diabase, USGS) — 6 GRMs covering mafic to felsic rock types analyzed as unknowns; also NWA14526 (lunar basalt) and NWA13190 (shergottite) compared with SN-ICP-MS</t>
         </is>
       </c>
-      <c r="V100" s="1" t="inlineStr">
+      <c r="Y100" s="1" t="inlineStr">
         <is>
           <t>NIST SRM 612 and BCR-2G (monitoring standards measured in same sessions)</t>
         </is>
       </c>
-      <c r="W100" s="1" t="inlineStr">
+      <c r="Z100" s="1" t="inlineStr">
         <is>
           <t>NIST SRM 612 and BCR-2G (same monitoring standard set as glass protocol)</t>
         </is>
       </c>
-      <c r="X100" s="1" t="inlineStr">
+      <c r="AA100" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
       </c>
-      <c r="Y100" s="1" t="inlineStr">
+      <c r="AB100" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
@@ -11052,68 +12067,80 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L101" s="9" t="n"/>
-      <c r="M101" s="1" t="inlineStr">
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>$.ada:analyteTemplate.ada:analyteColumns[]</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>analyteColumn: detectionLimit 
+  datatype: Text
+  readOnly:true</t>
+        </is>
+      </c>
+      <c r="O101" s="9" t="n"/>
+      <c r="P101" s="1" t="inlineStr">
         <is>
           <t>LODs not formally reported; all concentrations above detection limits except noted (Cr in some irons below LOD)</t>
         </is>
       </c>
-      <c r="N101" s="1" t="inlineStr">
+      <c r="Q101" s="1" t="inlineStr">
         <is>
           <t>LODs reported in Table E1 (Appendix E) for 2D mapping: average of all individual pixel LODs (Na=1, Nb=10 per Longerich et al. 1996)</t>
         </is>
       </c>
-      <c r="O101" s="1" t="inlineStr">
+      <c r="R101" s="1" t="inlineStr">
         <is>
           <t>LODs reported in Table 1 for line scan + spot trace elements: Na=24, Nb=5 per Longerich et al. 1996; LOQ = 10SD criterion</t>
         </is>
       </c>
-      <c r="P101" s="1" t="inlineStr">
+      <c r="S101" s="1" t="inlineStr">
         <is>
           <t>N (LODs not separately reported for phosphate analyses)</t>
         </is>
       </c>
-      <c r="Q101" s="1" t="inlineStr">
+      <c r="T101" s="1" t="inlineStr">
         <is>
           <t>N (LODs not stated; concentrations reported for all nuclides above background)</t>
         </is>
       </c>
-      <c r="R101" s="1" t="inlineStr">
+      <c r="U101" s="1" t="inlineStr">
         <is>
           <t>N (LODs not formally stated)</t>
         </is>
       </c>
-      <c r="S101" s="1" t="inlineStr">
+      <c r="V101" s="1" t="inlineStr">
         <is>
           <t>LODs in µg g⁻¹ (median from Table 3): As 2, Au 0.1, Co 2, Cr 19, Cu 0.8, Fe 5300, Ga 0.1, Ge 0.2, Ir 0.04, Ni 60, Os 0.09, Pd 0.06, Pt 0.4, Re 0.02, Rh 0.05, Ru 0.3, W 0.09; calculated per Longerich et al. (1996) in iolite 4</t>
         </is>
       </c>
-      <c r="T101" s="1" t="inlineStr">
+      <c r="W101" s="1" t="inlineStr">
         <is>
           <t>N (LODs not separately reported for mapping)</t>
         </is>
       </c>
-      <c r="U101" s="1" t="inlineStr">
+      <c r="X101" s="1" t="inlineStr">
         <is>
           <t>LODs for 32 elements in Li-borate glass BHVO-2: 0.005–23.5 µg g⁻¹ (dilution-limited; much higher than undiluted glass LODs); LODs for NIST 610: 0.007–0.45 µg g⁻¹; LOQ = 3.3 × LOD (Pettke 2012) for most elements; LOQ for pollution elements = blank + 10SD (Gold Book IUPAC)</t>
         </is>
       </c>
-      <c r="V101" s="1" t="inlineStr">
+      <c r="Y101" s="1" t="inlineStr">
         <is>
           <t>Detection limits for Au ~0.01 ppm; Cu ~0.1 ppm in silicate melt (stated in paper)</t>
         </is>
       </c>
-      <c r="W101" s="1" t="inlineStr">
+      <c r="Z101" s="1" t="inlineStr">
         <is>
           <t>N (detection limits for sulfide not stated; only silicate melt detection limits given as Au ~0.01 ppm, Cu ~0.1 ppm)</t>
         </is>
       </c>
-      <c r="X101" s="1" t="inlineStr">
+      <c r="AA101" s="1" t="inlineStr">
         <is>
           <t>Referenced in Table 3 and Table S1; specific values not directly stated in main text; REE in olivines below detection limits at 24–32 µm conditions [P4, P7, P11]</t>
         </is>
       </c>
-      <c r="Y101" s="1" t="inlineStr">
+      <c r="AB101" s="1" t="inlineStr">
         <is>
           <t>Referenced in Table 3 and Table S1; specific values not directly stated in main text; merrillite REE at 14–414 ppm range above detection [P4, P12]</t>
         </is>
@@ -11167,68 +12194,80 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L102" s="9" t="n"/>
-      <c r="M102" s="1" t="inlineStr">
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>$.ada:analyteTemplate.ada:analyteColumns[]</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>analyteColumn: detectionLimitMethod
+  datatype: Text
+  readOnly:true</t>
+        </is>
+      </c>
+      <c r="O102" s="9" t="n"/>
+      <c r="P102" s="1" t="inlineStr">
         <is>
           <t>N (not formally stated)</t>
         </is>
       </c>
-      <c r="N102" s="1" t="inlineStr">
+      <c r="Q102" s="1" t="inlineStr">
         <is>
           <t>Longerich et al. (1996): LOD = (3SD/S) × √(1/Nb + 1/Na)</t>
         </is>
       </c>
-      <c r="O102" s="1" t="inlineStr">
+      <c r="R102" s="1" t="inlineStr">
         <is>
           <t>Longerich et al. (1996); LOQ = 10SD criterion (same equation)</t>
         </is>
       </c>
-      <c r="P102" s="1" t="inlineStr">
+      <c r="S102" s="1" t="inlineStr">
         <is>
           <t>N (not formally stated)</t>
         </is>
       </c>
-      <c r="Q102" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="R102" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="S102" s="1" t="inlineStr">
+      <c r="T102" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U102" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V102" s="1" t="inlineStr">
         <is>
           <t>Longerich et al. (1996) — implemented in iolite 4; sample-individual LOD calculated per analysis</t>
         </is>
       </c>
-      <c r="T102" s="1" t="inlineStr">
+      <c r="W102" s="1" t="inlineStr">
         <is>
           <t>N (LODs not separately reported for mapping)</t>
         </is>
       </c>
-      <c r="U102" s="1" t="inlineStr">
+      <c r="X102" s="1" t="inlineStr">
         <is>
           <t>Pettke (2012) for most elements: LOD = (3.29 × √(Rbkg × DT × ...) + 2.71) / (Nan × DT × S); LOQ for pollution elements = blank value + 10SD (IUPAC Gold Book)</t>
         </is>
       </c>
-      <c r="V102" s="1" t="inlineStr">
+      <c r="Y102" s="1" t="inlineStr">
         <is>
           <t>N (stated as "detection limits" without specific formula)</t>
         </is>
       </c>
-      <c r="W102" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="X102" s="1" t="inlineStr">
+      <c r="Z102" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA102" s="1" t="inlineStr">
         <is>
           <t>N (method not stated) [P4]</t>
         </is>
       </c>
-      <c r="Y102" s="1" t="inlineStr">
+      <c r="AB102" s="1" t="inlineStr">
         <is>
           <t>N (method not stated) [P4]</t>
         </is>
@@ -11282,37 +12321,34 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L103" s="9" t="n"/>
-      <c r="M103" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N103" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O103" s="1" t="inlineStr">
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>$.ada:analyteTemplate.ada:analyteColumns[]</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>analyteColumn: limitOfQuantification 
+  datatype: Text
+  readOnly:true</t>
+        </is>
+      </c>
+      <c r="O103" s="9" t="n"/>
+      <c r="P103" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q103" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R103" s="1" t="inlineStr">
         <is>
           <t>LOQ = 10SD of background counts (10σ criterion; Chernonozhkin et al. 2021)</t>
         </is>
       </c>
-      <c r="P103" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q103" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="R103" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="S103" s="1" t="inlineStr">
         <is>
           <t>N</t>
@@ -11325,25 +12361,40 @@
       </c>
       <c r="U103" s="1" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V103" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W103" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X103" s="1" t="inlineStr">
+        <is>
           <t>LOQ = 3.3 × LOD per Pettke (2012) for most elements; LOQ = blank value + 10SD per IUPAC Gold Book for pollution elements (V, Co, Zn, Ba, La, Ce, Ta, U) where blank contribution is significant</t>
         </is>
       </c>
-      <c r="V103" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="W103" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="X103" s="1" t="inlineStr">
+      <c r="Y103" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z103" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA103" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
       </c>
-      <c r="Y103" s="1" t="inlineStr">
+      <c r="AB103" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
@@ -11405,68 +12456,83 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L104" s="9" t="n"/>
-      <c r="M104" s="1" t="inlineStr">
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>$.ada:analyteTemplate.ada:analyteColumns[]</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>analyteColumn: withinSessionReproducibility
+  datatype: Text
+  readOnly:true
+analyteColumn: withinSessionReproducibilityMethod
+  datatype: Text
+  readOnly:true</t>
+        </is>
+      </c>
+      <c r="O104" s="9" t="n"/>
+      <c r="P104" s="1" t="inlineStr">
         <is>
           <t>N (within-session precision not formally assessed; standard deviation across raster scans reported per element)</t>
         </is>
       </c>
-      <c r="N104" s="1" t="inlineStr">
+      <c r="Q104" s="1" t="inlineStr">
         <is>
           <t>Intermediate precision for mapping: most elements at ≥10 µg g⁻¹: 5–15% RSD; elements &lt;10 µg g⁻¹: 5–30% RSD; assessed from repeated GRM mapping in 8 sessions over 1 year (n=8 for each element)</t>
         </is>
       </c>
-      <c r="O104" s="1" t="inlineStr">
+      <c r="R104" s="1" t="inlineStr">
         <is>
           <t>LOD calculated per analysis (Na=24, Nb=5); precision not formally reported as separate metric</t>
         </is>
       </c>
-      <c r="P104" s="1" t="inlineStr">
+      <c r="S104" s="1" t="inlineStr">
         <is>
           <t>N (precision not formally reported for phosphate analyses)</t>
         </is>
       </c>
-      <c r="Q104" s="1" t="inlineStr">
+      <c r="T104" s="1" t="inlineStr">
         <is>
           <t>N (within-session precision not formally assessed)</t>
         </is>
       </c>
-      <c r="R104" s="1" t="inlineStr">
+      <c r="U104" s="1" t="inlineStr">
         <is>
           <t>Analytical uncertainties: 2SE of individual spot measurements reported alongside data</t>
         </is>
       </c>
-      <c r="S104" s="1" t="inlineStr">
+      <c r="V104" s="1" t="inlineStr">
         <is>
           <t>RSD &lt;15% for most elements in Arraias meteorite under repeatability conditions (n=20 spot analyses); Cr: 20%, Ir: 16%, Os: 20% RSD; assessed by repeated analysis of same meteorite in one session</t>
         </is>
       </c>
-      <c r="T104" s="1" t="inlineStr">
+      <c r="W104" s="1" t="inlineStr">
         <is>
           <t>N (within-session precision for mapping not separately assessed)</t>
         </is>
       </c>
-      <c r="U104" s="1" t="inlineStr">
+      <c r="X104" s="1" t="inlineStr">
         <is>
           <t>Analytical precision (RSD) within 10% for most of 32 trace elements in 6 silicate GRMs (verified by homogeneity index assessment across 9 spots per disk)</t>
         </is>
       </c>
-      <c r="V104" s="1" t="inlineStr">
+      <c r="Y104" s="1" t="inlineStr">
         <is>
           <t>N (within-session precision not separately reported)</t>
         </is>
       </c>
-      <c r="W104" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="X104" s="1" t="inlineStr">
+      <c r="Z104" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA104" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
       </c>
-      <c r="Y104" s="1" t="inlineStr">
+      <c r="AB104" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
@@ -11528,22 +12594,22 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L105" s="9" t="n"/>
-      <c r="M105" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N105" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O105" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>$.ada:analyteTemplate.ada:analyteColumns[]</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>analyteColumn: betweenSessionReproducibility
+  datatype: Text
+  readOnly:true
+analyteColumn: betweenSessionReproducibilityMethod
+  datatype: Text
+  readOnly:true</t>
+        </is>
+      </c>
+      <c r="O105" s="9" t="n"/>
       <c r="P105" s="1" t="inlineStr">
         <is>
           <t>N</t>
@@ -11561,24 +12627,24 @@
       </c>
       <c r="S105" s="1" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T105" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U105" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V105" s="1" t="inlineStr">
+        <is>
           <t>Intermediate precision: RSD ≤20% for most elements assessed over multiple days on North Chile iron meteorite measured as unknown (n multiple days over 4 months)</t>
         </is>
       </c>
-      <c r="T105" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="U105" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V105" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="W105" s="1" t="inlineStr">
         <is>
           <t>N</t>
@@ -11586,10 +12652,25 @@
       </c>
       <c r="X105" s="1" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Y105" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Z105" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA105" s="1" t="inlineStr">
+        <is>
           <t>N (not stated) [P4]</t>
         </is>
       </c>
-      <c r="Y105" s="1" t="inlineStr">
+      <c r="AB105" s="1" t="inlineStr">
         <is>
           <t>N (not stated) [P4]</t>
         </is>
@@ -11651,68 +12732,83 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L106" s="9" t="n"/>
-      <c r="M106" s="1" t="inlineStr">
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>$.ada:analyteTemplate.ada:analyteColumns[]</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>analyteColumn: analyticalAccuracy 
+  datatype: Text
+  readOnly:true
+analyteColumn: analyticalAccuracyMethod 
+  datatype: Text
+  readOnly:true</t>
+        </is>
+      </c>
+      <c r="O106" s="9" t="n"/>
+      <c r="P106" s="1" t="inlineStr">
         <is>
           <t>LA-ICP-MS concentrations agreed with NAA within ±40% for most elements (LA relative to NAA); within ±10% for Ni, Co, Ga; differences in W (4.39 vs 1.06 ng g⁻¹ for Cerro del Inca by LA vs INAA) and Au/As up to 30% — attributed to heterogeneous sampling scale difference between techniques</t>
         </is>
       </c>
-      <c r="N106" s="1" t="inlineStr">
+      <c r="Q106" s="1" t="inlineStr">
         <is>
           <t>No systematic bias demonstrated; MgO+FeO+SiO₂+P₂O₅ oxide sums after mapping varied 95–99 wt% (average near 100%); LA-ICP-MS Fa# values compared to EMPA values for 8 PMG (Fig. 5A shows good agreement)</t>
         </is>
       </c>
-      <c r="O106" s="1" t="inlineStr">
+      <c r="R106" s="1" t="inlineStr">
         <is>
           <t>Trace element accuracy verified against literature INAA and EPMA data; major elements verified by comparison with EMPA results from same section</t>
         </is>
       </c>
-      <c r="P106" s="1" t="inlineStr">
+      <c r="S106" s="1" t="inlineStr">
         <is>
           <t>N (accuracy assessment not separately stated for phosphate analyses)</t>
         </is>
       </c>
-      <c r="Q106" s="1" t="inlineStr">
+      <c r="T106" s="1" t="inlineStr">
         <is>
           <t>Sc: good agreement with Davis (1977) INAA values within measurement scatter; overall accuracy verified by comparison with literature INAA and SIMS data; Marjalahti used as in-session control (Mn deviation from reference value noted as 4.2% above Ryder 1984)</t>
         </is>
       </c>
-      <c r="R106" s="1" t="inlineStr">
+      <c r="U106" s="1" t="inlineStr">
         <is>
           <t>N (accuracy formally assessed by comparison with internal standard; absolute accuracy not separately reported)</t>
         </is>
       </c>
-      <c r="S106" s="1" t="inlineStr">
+      <c r="V106" s="1" t="inlineStr">
         <is>
           <t>Results for 9 known iron meteorites: &gt;75% of published values within LA-ICP-MS result ± 2s (two standard deviations); relative differences mostly within ±20% (Fig. 2); specific discrepancies: Ir in Arraias +40%, Ir in Nossa Senhora +64%, Co and Ga in Campo del Cielo (heterogeneity issues); trend lines slope 0.87–1.17 with R² = 0.97–1.0</t>
         </is>
       </c>
-      <c r="T106" s="1" t="inlineStr">
+      <c r="W106" s="1" t="inlineStr">
         <is>
           <t>N (mapping accuracy not separately assessed from spot protocol)</t>
         </is>
       </c>
-      <c r="U106" s="1" t="inlineStr">
+      <c r="X106" s="1" t="inlineStr">
         <is>
           <t>Analytical results within 10% of reference values for most of 32 trace elements in 6 GRMs (mafic to felsic); precision (RSD) within 10% for most elements; lunar basalt (NWA14526) and shergottite (NWA13190) results compared with SN-ICP-MS and found reliable</t>
         </is>
       </c>
-      <c r="V106" s="1" t="inlineStr">
+      <c r="Y106" s="1" t="inlineStr">
         <is>
           <t>Au and Cu fully dissolved in most glasses (smooth signals); Au results consistent with Au solubility trends from literature; comparison with SN-ICP-MS (solution) for two extraterrestrial samples confirms reliability</t>
         </is>
       </c>
-      <c r="W106" s="1" t="inlineStr">
+      <c r="Z106" s="1" t="inlineStr">
         <is>
           <t>Sulfide Au and Cu concentrations consistent with strong positive correlation with log fS₂ (Fig. 5A) confirming thermodynamic equilibrium; partitioning coefficients Dsulfide/melt consistent with literature (Li et al. 2019, 2021)</t>
         </is>
       </c>
-      <c r="X106" s="1" t="inlineStr">
+      <c r="AA106" s="1" t="inlineStr">
         <is>
           <t>For silicates: oxide-sum normalization agrees within &lt;10% with EMP-based IS method (internal cross-check, not a separate QC standard) [P4]</t>
         </is>
       </c>
-      <c r="Y106" s="1" t="inlineStr">
+      <c r="AB106" s="1" t="inlineStr">
         <is>
           <t>N (no accuracy assessment stated for phosphate protocol) [P4]</t>
         </is>
@@ -11763,68 +12859,85 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L108" s="9" t="n"/>
-      <c r="M108" s="1" t="inlineStr">
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>$.schema:description</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>method Property: schema:description accepts free-text narrative; additional notes can extend it or be distributed to the most relevant workflow step's schema:description.</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>method property : description
+  datatype: text
+  readOnly:false</t>
+        </is>
+      </c>
+      <c r="O108" s="9" t="n"/>
+      <c r="P108" s="1" t="inlineStr">
         <is>
           <t>Raster scans used for main element dataset (23 elements); separate spot analyses on 5 irons for more precise Ge abundances (150 µm spot, 50 Hz, 20 s); two different analysis modes represent distinct protocols but are reported in same paper</t>
         </is>
       </c>
-      <c r="N108" s="1" t="inlineStr">
+      <c r="Q108" s="1" t="inlineStr">
         <is>
           <t>Pallasite olivine 2D mapping in cool plasma mode (800 W) is a core methodological innovation; total of 8 PMG meteorites mapped; P-rich veinlets excluded from olivine averages; Fa# values verified against EMPA (Fig. 5A)</t>
         </is>
       </c>
-      <c r="O108" s="1" t="inlineStr">
+      <c r="R108" s="1" t="inlineStr">
         <is>
           <t>Multi-run sequential design is the key methodological innovation: Run 1 (major elements, 30 µm, MR) provides Cr IS for Run 2 (trace elements, 130 µm, LR); pre-ablation pass removes surface contamination before Run 1</t>
         </is>
       </c>
-      <c r="P108" s="1" t="inlineStr">
+      <c r="S108" s="1" t="inlineStr">
         <is>
           <t>Phosphate phase identification used LA-ICP-MS data combined with EMPA and µXRF (Fig. D9); merrillite, stanfieldite, farringtonite distinguished by REE patterns; oxide sum normalization applied to phosphate (not olivine IS approach)</t>
         </is>
       </c>
-      <c r="Q108" s="1" t="inlineStr">
+      <c r="T108" s="1" t="inlineStr">
         <is>
           <t>Many instrument parameters lost during extended lab shutdown; 75 µm spot size in medium resolution mode on sector-field ICP-MS is unusual combination for olivine trace elements; 25 Mg IS from EPMA is standard approach</t>
         </is>
       </c>
-      <c r="R108" s="1" t="inlineStr">
+      <c r="U108" s="1" t="inlineStr">
         <is>
           <t>fs laser (260 nm Ti:sapphire) essential for HSE measurement in metal (reduces elemental fractionation and matrix effects); IVB iron meteorite standards (Warburton Range + Tawallah Valley) as matrix-matched standards for iron meteorite metal</t>
         </is>
       </c>
-      <c r="S108" s="1" t="inlineStr">
+      <c r="V108" s="1" t="inlineStr">
         <is>
           <t>Key innovations: (1) use of two measurement standards (NIST SRM 612 + North Chile) with yield correction in iolite 3D DRS; (2) Fe+Ni+Co=100% normalization eliminates need for EPMA IS; Cr results not quantitative due to argide interferences</t>
         </is>
       </c>
-      <c r="T108" s="1" t="inlineStr">
+      <c r="W108" s="1" t="inlineStr">
         <is>
           <t>Elemental mapping used as classification tool even without prior knowledge of structural variations (kamacite vs. plessite); demonstrates LA-ICP-MS mapping applicability for iron meteorite classification</t>
         </is>
       </c>
-      <c r="U108" s="1" t="inlineStr">
+      <c r="X108" s="1" t="inlineStr">
         <is>
           <t>Target: bulk trace element analysis of extraterrestrial samples using only 10 mg; Li-borate flux fusion (35:1 dilution) with fs laser — first reported use of fs laser for flux fusion glass analysis; non-matrix-matched external standards demonstrated accurate with fs laser</t>
         </is>
       </c>
-      <c r="V108" s="1" t="inlineStr">
+      <c r="Y108" s="1" t="inlineStr">
         <is>
           <t>Analysis of quenched experimental glasses from high-pressure (1 GPa) piston-cylinder experiments; Au and Cu solubility measurements; smooth time-resolved signals indicate fully dissolved Au (no micronuggets)</t>
         </is>
       </c>
-      <c r="W108" s="1" t="inlineStr">
+      <c r="Z108" s="1" t="inlineStr">
         <is>
           <t>Analysis of quenched experimental pyrrhotite (Fe₁₋ₓS) from same piston-cylinder experiments; 20 µm spot required due to small grain size (5–50 µm); same instrument and analytical session as glass protocol</t>
         </is>
       </c>
-      <c r="X108" s="1" t="inlineStr">
+      <c r="AA108" s="1" t="inlineStr">
         <is>
           <t>Paper broadly follows Udry et al. (2012) and Pernet-Fisher et al. (2014) for procedure; two IS approaches used for different mineral phases (oxide-sum for silicates; EMP CaO for phosphate); 90 µm spot used on some olivines to evaluate whether low REE signals result from insufficient sampling volume [P4]</t>
         </is>
       </c>
-      <c r="Y108" s="1" t="inlineStr">
+      <c r="AB108" s="1" t="inlineStr">
         <is>
           <t>N/A — see silicate column for general notes [P4]</t>
         </is>
